--- a/data/profit_data/粗利データ.xlsx
+++ b/data/profit_data/粗利データ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v221\企画課共有$\4.経営企画係フォルダー\★経営企画★\②業績評価\⑦小林先生案件\粗利データ（web版ダッシュボード用）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E543E4C-8139-4FA4-BE5A-62477B3CE465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D396B78F-19DC-4C89-AF58-7EF1EA0A645E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26250" windowHeight="14400" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -524,13 +524,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FED16C5-0FF1-DB48-A3CC-8F51D282E1B6}">
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="4" customFormat="1">
+    <row r="1" spans="1:25" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -603,8 +603,11 @@
       <c r="X1" s="3">
         <v>46054</v>
       </c>
+      <c r="Y1" s="3">
+        <v>46082</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -677,8 +680,11 @@
       <c r="X2" s="5">
         <v>30576.212</v>
       </c>
+      <c r="Y2" s="5">
+        <v>20118.510999999999</v>
+      </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -751,8 +757,11 @@
       <c r="X3" s="5">
         <v>13243.213</v>
       </c>
+      <c r="Y3" s="5">
+        <v>21266.275000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -825,8 +834,11 @@
       <c r="X4" s="5">
         <v>73724.601999999999</v>
       </c>
+      <c r="Y4" s="5">
+        <v>82350.62</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -899,8 +911,11 @@
       <c r="X5" s="5">
         <v>108069.474</v>
       </c>
+      <c r="Y5" s="5">
+        <v>118283.914</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -973,8 +988,11 @@
       <c r="X6" s="5">
         <v>18505.195</v>
       </c>
+      <c r="Y6" s="5">
+        <v>21943.607</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1047,8 +1065,11 @@
       <c r="X7" s="5">
         <v>19366.940999999999</v>
       </c>
+      <c r="Y7" s="5">
+        <v>23877.724999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1121,8 +1142,11 @@
       <c r="X8" s="5">
         <v>35906.491999999998</v>
       </c>
+      <c r="Y8" s="5">
+        <v>34057.243999999999</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1195,8 +1219,11 @@
       <c r="X9" s="5">
         <v>88547.392000000007</v>
       </c>
+      <c r="Y9" s="5">
+        <v>102220.90300000001</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1269,8 +1296,11 @@
       <c r="X10" s="5">
         <v>69993.459000000003</v>
       </c>
+      <c r="Y10" s="5">
+        <v>72565.914000000004</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1343,8 +1373,11 @@
       <c r="X11" s="5">
         <v>129271.361</v>
       </c>
+      <c r="Y11" s="5">
+        <v>142046.41200000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1417,8 +1450,11 @@
       <c r="X12" s="5">
         <v>167738.715</v>
       </c>
+      <c r="Y12" s="5">
+        <v>178754.23199999999</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1491,8 +1527,11 @@
       <c r="X13" s="5">
         <v>20750.776000000002</v>
       </c>
+      <c r="Y13" s="5">
+        <v>25064.962</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -1565,8 +1604,11 @@
       <c r="X14" s="5">
         <v>42111.72</v>
       </c>
+      <c r="Y14" s="5">
+        <v>43709.27</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1639,8 +1681,11 @@
       <c r="X15" s="5">
         <v>168845.42</v>
       </c>
+      <c r="Y15" s="5">
+        <v>183645.84899999999</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1713,8 +1758,11 @@
       <c r="X16" s="5">
         <v>111903.337</v>
       </c>
+      <c r="Y16" s="5">
+        <v>124331.003</v>
+      </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1787,8 +1835,11 @@
       <c r="X17" s="5">
         <v>40860.165999999997</v>
       </c>
+      <c r="Y17" s="5">
+        <v>47041.031000000003</v>
+      </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1861,8 +1912,11 @@
       <c r="X18" s="5">
         <v>54972.487999999998</v>
       </c>
+      <c r="Y18" s="5">
+        <v>57789.296999999999</v>
+      </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1935,8 +1989,11 @@
       <c r="X19" s="5">
         <v>107212.9</v>
       </c>
+      <c r="Y19" s="5">
+        <v>105585.988</v>
+      </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -2009,8 +2066,11 @@
       <c r="X20" s="5">
         <v>36959.656000000003</v>
       </c>
+      <c r="Y20" s="5">
+        <v>42509.733</v>
+      </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -2083,8 +2143,11 @@
       <c r="X21" s="5">
         <v>95364.982000000004</v>
       </c>
+      <c r="Y21" s="5">
+        <v>109675.09699999999</v>
+      </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -2157,8 +2220,11 @@
       <c r="X22" s="5">
         <v>32541.040000000001</v>
       </c>
+      <c r="Y22" s="5">
+        <v>39730.83</v>
+      </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -2231,8 +2297,11 @@
       <c r="X23" s="5">
         <v>91790.073000000004</v>
       </c>
+      <c r="Y23" s="5">
+        <v>97317.096999999994</v>
+      </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -2305,8 +2374,11 @@
       <c r="X24" s="5">
         <v>1213.6610000000001</v>
       </c>
+      <c r="Y24" s="5">
+        <v>1257.336</v>
+      </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -2379,8 +2451,11 @@
       <c r="X25" s="5">
         <v>48990.275999999998</v>
       </c>
+      <c r="Y25" s="5">
+        <v>59117.004999999997</v>
+      </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2452,6 +2527,9 @@
       </c>
       <c r="X26" s="5">
         <v>36854.908000000003</v>
+      </c>
+      <c r="Y26" s="5">
+        <v>40318.211000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data/profit_data/粗利データ.xlsx
+++ b/data/profit_data/粗利データ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v221\企画課共有$\4.経営企画係フォルダー\★経営企画★\②業績評価\⑦小林先生案件\粗利データ（web版ダッシュボード用）\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D396B78F-19DC-4C89-AF58-7EF1EA0A645E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6167619-96AF-4B4C-8AE1-BF6CD9D66023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{550DB2E5-88A1-DB4A-A686-6CCA736E9165}"/>
   </bookViews>
@@ -524,13 +524,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FED16C5-0FF1-DB48-A3CC-8F51D282E1B6}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="4" customFormat="1">
+    <row r="1" spans="1:26" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -606,8 +606,11 @@
       <c r="Y1" s="3">
         <v>46082</v>
       </c>
+      <c r="Z1" s="3">
+        <v>46113</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,8 +686,11 @@
       <c r="Y2" s="5">
         <v>20118.510999999999</v>
       </c>
+      <c r="Z2" s="5">
+        <v>44078.955000000002</v>
+      </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -760,8 +766,11 @@
       <c r="Y3" s="5">
         <v>21266.275000000001</v>
       </c>
+      <c r="Z3" s="5">
+        <v>13164.186</v>
+      </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -837,8 +846,11 @@
       <c r="Y4" s="5">
         <v>82350.62</v>
       </c>
+      <c r="Z4" s="5">
+        <v>72378.411999999997</v>
+      </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -914,8 +926,11 @@
       <c r="Y5" s="5">
         <v>118283.914</v>
       </c>
+      <c r="Z5" s="5">
+        <v>120988.731</v>
+      </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +1006,11 @@
       <c r="Y6" s="5">
         <v>21943.607</v>
       </c>
+      <c r="Z6" s="5">
+        <v>20733.151999999998</v>
+      </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1068,8 +1086,11 @@
       <c r="Y7" s="5">
         <v>23877.724999999999</v>
       </c>
+      <c r="Z7" s="5">
+        <v>29740.565999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1145,8 +1166,11 @@
       <c r="Y8" s="5">
         <v>34057.243999999999</v>
       </c>
+      <c r="Z8" s="5">
+        <v>36636.256000000001</v>
+      </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1222,8 +1246,11 @@
       <c r="Y9" s="5">
         <v>102220.90300000001</v>
       </c>
+      <c r="Z9" s="5">
+        <v>117687.842</v>
+      </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1299,8 +1326,11 @@
       <c r="Y10" s="5">
         <v>72565.914000000004</v>
       </c>
+      <c r="Z10" s="5">
+        <v>69308.399000000005</v>
+      </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1376,8 +1406,11 @@
       <c r="Y11" s="5">
         <v>142046.41200000001</v>
       </c>
+      <c r="Z11" s="5">
+        <v>139342.25200000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1453,8 +1486,11 @@
       <c r="Y12" s="5">
         <v>178754.23199999999</v>
       </c>
+      <c r="Z12" s="5">
+        <v>198727.894</v>
+      </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1530,8 +1566,11 @@
       <c r="Y13" s="5">
         <v>25064.962</v>
       </c>
+      <c r="Z13" s="5">
+        <v>14995.745999999999</v>
+      </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -1607,8 +1646,11 @@
       <c r="Y14" s="5">
         <v>43709.27</v>
       </c>
+      <c r="Z14" s="5">
+        <v>45551.22</v>
+      </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:26">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1684,8 +1726,11 @@
       <c r="Y15" s="5">
         <v>183645.84899999999</v>
       </c>
+      <c r="Z15" s="5">
+        <v>182573.10200000001</v>
+      </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:26">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1761,8 +1806,11 @@
       <c r="Y16" s="5">
         <v>124331.003</v>
       </c>
+      <c r="Z16" s="5">
+        <v>112083.065</v>
+      </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:26">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1838,8 +1886,11 @@
       <c r="Y17" s="5">
         <v>47041.031000000003</v>
       </c>
+      <c r="Z17" s="5">
+        <v>46033.894999999997</v>
+      </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:26">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1915,8 +1966,11 @@
       <c r="Y18" s="5">
         <v>57789.296999999999</v>
       </c>
+      <c r="Z18" s="5">
+        <v>53182.574000000001</v>
+      </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:26">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1992,8 +2046,11 @@
       <c r="Y19" s="5">
         <v>105585.988</v>
       </c>
+      <c r="Z19" s="5">
+        <v>112555.44500000001</v>
+      </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:26">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -2069,8 +2126,11 @@
       <c r="Y20" s="5">
         <v>42509.733</v>
       </c>
+      <c r="Z20" s="5">
+        <v>42157.387999999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:26">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -2146,8 +2206,11 @@
       <c r="Y21" s="5">
         <v>109675.09699999999</v>
       </c>
+      <c r="Z21" s="5">
+        <v>122593.88400000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:26">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -2223,8 +2286,11 @@
       <c r="Y22" s="5">
         <v>39730.83</v>
       </c>
+      <c r="Z22" s="5">
+        <v>41339.277000000002</v>
+      </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:26">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -2300,8 +2366,11 @@
       <c r="Y23" s="5">
         <v>97317.096999999994</v>
       </c>
+      <c r="Z23" s="5">
+        <v>73058.240999999995</v>
+      </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:26">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -2377,8 +2446,11 @@
       <c r="Y24" s="5">
         <v>1257.336</v>
       </c>
+      <c r="Z24" s="5">
+        <v>1278.374</v>
+      </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:26">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -2454,8 +2526,11 @@
       <c r="Y25" s="5">
         <v>59117.004999999997</v>
       </c>
+      <c r="Z25" s="5">
+        <v>56286.14</v>
+      </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:26">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2530,6 +2605,9 @@
       </c>
       <c r="Y26" s="5">
         <v>40318.211000000003</v>
+      </c>
+      <c r="Z26" s="5">
+        <v>40508.228999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/profit_data/粗利データ.xlsx
+++ b/data/profit_data/粗利データ.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/genie/dev/ai-apps/Dashboard/data/profit_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\ntmc2025\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452FD9F3-E363-B248-8A2B-E458E669C939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7910FA7D-771F-4A78-910F-AFF95CEFD219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="660" windowWidth="31300" windowHeight="25460" xr2:uid="{F791F907-76C8-5841-8D51-B0125034DCF5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F791F907-76C8-5841-8D51-B0125034DCF5}"/>
   </bookViews>
   <sheets>
     <sheet name="入院" sheetId="1" r:id="rId1"/>
     <sheet name="外来" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -105,7 +116,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -563,7 +577,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -690,8 +704,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -701,8 +718,20 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -735,6 +764,7 @@
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="桁区切り" xfId="42" builtinId="6"/>
     <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
@@ -1076,4179 +1106,7946 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D0397E-55AA-0C4B-A296-09B774CEF910}">
-  <dimension ref="A1:Z26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <dimension ref="A1:AX28"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="2" max="7" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="3">
+        <v>44652</v>
+      </c>
+      <c r="C1" s="3">
+        <v>44682</v>
+      </c>
+      <c r="D1" s="3">
+        <v>44713</v>
+      </c>
+      <c r="E1" s="3">
+        <v>44743</v>
+      </c>
+      <c r="F1" s="3">
+        <v>44774</v>
+      </c>
+      <c r="G1" s="3">
+        <v>44805</v>
+      </c>
+      <c r="H1" s="3">
+        <v>44835</v>
+      </c>
+      <c r="I1" s="3">
+        <v>44866</v>
+      </c>
+      <c r="J1" s="3">
+        <v>44896</v>
+      </c>
+      <c r="K1" s="3">
+        <v>44927</v>
+      </c>
+      <c r="L1" s="3">
+        <v>44958</v>
+      </c>
+      <c r="M1" s="3">
+        <v>44986</v>
+      </c>
+      <c r="N1" s="3">
+        <v>45017</v>
+      </c>
+      <c r="O1" s="3">
+        <v>45047</v>
+      </c>
+      <c r="P1" s="3">
+        <v>45078</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>45108</v>
+      </c>
+      <c r="R1" s="3">
+        <v>45139</v>
+      </c>
+      <c r="S1" s="3">
+        <v>45170</v>
+      </c>
+      <c r="T1" s="3">
+        <v>45200</v>
+      </c>
+      <c r="U1" s="3">
+        <v>45231</v>
+      </c>
+      <c r="V1" s="3">
+        <v>45261</v>
+      </c>
+      <c r="W1" s="3">
+        <v>45292</v>
+      </c>
+      <c r="X1" s="3">
+        <v>45323</v>
+      </c>
+      <c r="Y1" s="3">
+        <v>45352</v>
+      </c>
+      <c r="Z1" s="1">
         <v>45383</v>
       </c>
-      <c r="C1" s="1">
+      <c r="AA1" s="1">
         <v>45413</v>
       </c>
-      <c r="D1" s="1">
+      <c r="AB1" s="1">
         <v>45444</v>
       </c>
-      <c r="E1" s="1">
+      <c r="AC1" s="1">
         <v>45474</v>
       </c>
-      <c r="F1" s="1">
+      <c r="AD1" s="1">
         <v>45505</v>
       </c>
-      <c r="G1" s="1">
+      <c r="AE1" s="1">
         <v>45536</v>
       </c>
-      <c r="H1" s="1">
+      <c r="AF1" s="1">
         <v>45566</v>
       </c>
-      <c r="I1" s="1">
+      <c r="AG1" s="1">
         <v>45597</v>
       </c>
-      <c r="J1" s="1">
+      <c r="AH1" s="1">
         <v>45627</v>
       </c>
-      <c r="K1" s="1">
+      <c r="AI1" s="1">
         <v>45658</v>
       </c>
-      <c r="L1" s="1">
+      <c r="AJ1" s="1">
         <v>45689</v>
       </c>
-      <c r="M1" s="1">
+      <c r="AK1" s="1">
         <v>45717</v>
       </c>
-      <c r="N1" s="1">
+      <c r="AL1" s="1">
         <v>45748</v>
       </c>
-      <c r="O1" s="1">
+      <c r="AM1" s="1">
         <v>45778</v>
       </c>
-      <c r="P1" s="1">
+      <c r="AN1" s="1">
         <v>45809</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="AO1" s="1">
         <v>45839</v>
       </c>
-      <c r="R1" s="1">
+      <c r="AP1" s="1">
         <v>45870</v>
       </c>
-      <c r="S1" s="1">
+      <c r="AQ1" s="1">
         <v>45901</v>
       </c>
-      <c r="T1" s="1">
+      <c r="AR1" s="1">
         <v>45931</v>
       </c>
-      <c r="U1" s="1">
+      <c r="AS1" s="1">
         <v>45962</v>
       </c>
-      <c r="V1" s="1">
+      <c r="AT1" s="1">
         <v>45992</v>
       </c>
-      <c r="W1" s="1">
+      <c r="AU1" s="1">
         <v>46023</v>
       </c>
-      <c r="X1" s="1">
+      <c r="AV1" s="1">
         <v>46054</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="AW1" s="1">
         <v>46082</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="AX1" s="1">
         <v>46113</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
+        <v>35940.014000000003</v>
+      </c>
+      <c r="C2" s="6">
+        <v>31434.064999999999</v>
+      </c>
+      <c r="D2" s="6">
+        <v>28279.507000000001</v>
+      </c>
+      <c r="E2" s="6">
+        <v>26336.190999999999</v>
+      </c>
+      <c r="F2" s="6">
+        <v>26533.226999999999</v>
+      </c>
+      <c r="G2" s="6">
+        <v>34946.035000000003</v>
+      </c>
+      <c r="H2" s="6">
+        <v>21965.002</v>
+      </c>
+      <c r="I2" s="6">
+        <v>31052.595000000001</v>
+      </c>
+      <c r="J2" s="6">
+        <v>24351.865000000002</v>
+      </c>
+      <c r="K2" s="6">
+        <v>16954.487000000001</v>
+      </c>
+      <c r="L2" s="6">
+        <v>31007.481</v>
+      </c>
+      <c r="M2" s="6">
+        <v>17488.420999999998</v>
+      </c>
+      <c r="N2" s="6">
+        <v>17813.16</v>
+      </c>
+      <c r="O2" s="6">
+        <v>28284.574000000001</v>
+      </c>
+      <c r="P2" s="6">
+        <v>37094.843000000001</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>28315.508999999998</v>
+      </c>
+      <c r="R2" s="6">
+        <v>12307.59</v>
+      </c>
+      <c r="S2" s="6">
+        <v>18665.580000000002</v>
+      </c>
+      <c r="T2" s="6">
+        <v>25003.451000000001</v>
+      </c>
+      <c r="U2" s="6">
+        <v>35047.504000000001</v>
+      </c>
+      <c r="V2" s="6">
+        <v>24179.453000000001</v>
+      </c>
+      <c r="W2" s="6">
+        <v>17014.348000000002</v>
+      </c>
+      <c r="X2" s="6">
+        <v>16082.994000000001</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>27669.271000000001</v>
+      </c>
+      <c r="Z2" s="2">
         <v>32541</v>
       </c>
-      <c r="C2" s="2">
+      <c r="AA2" s="2">
         <v>32113</v>
       </c>
-      <c r="D2" s="2">
+      <c r="AB2" s="2">
         <v>25048</v>
       </c>
-      <c r="E2" s="2">
+      <c r="AC2" s="2">
         <v>40716</v>
       </c>
-      <c r="F2" s="2">
+      <c r="AD2" s="2">
         <v>22229</v>
       </c>
-      <c r="G2" s="2">
+      <c r="AE2" s="2">
         <v>18274</v>
       </c>
-      <c r="H2" s="2">
+      <c r="AF2" s="2">
         <v>18865</v>
       </c>
-      <c r="I2" s="2">
+      <c r="AG2" s="2">
         <v>37362</v>
       </c>
-      <c r="J2" s="2">
+      <c r="AH2" s="2">
         <v>27313</v>
       </c>
-      <c r="K2" s="2">
+      <c r="AI2" s="2">
         <v>26476</v>
       </c>
-      <c r="L2" s="2">
+      <c r="AJ2" s="2">
         <v>13551</v>
       </c>
-      <c r="M2" s="2">
+      <c r="AK2" s="2">
         <v>47099</v>
       </c>
-      <c r="N2" s="2">
+      <c r="AL2" s="2">
         <v>44593</v>
       </c>
-      <c r="O2" s="2">
+      <c r="AM2" s="2">
         <v>35378</v>
       </c>
-      <c r="P2" s="2">
+      <c r="AN2" s="2">
         <v>29598</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="AO2" s="2">
         <v>32371</v>
       </c>
-      <c r="R2" s="2">
+      <c r="AP2" s="2">
         <v>27167</v>
       </c>
-      <c r="S2" s="2">
+      <c r="AQ2" s="2">
         <v>19475</v>
       </c>
-      <c r="T2" s="2">
+      <c r="AR2" s="2">
         <v>17850</v>
       </c>
-      <c r="U2" s="2">
+      <c r="AS2" s="2">
         <v>28273</v>
       </c>
-      <c r="V2" s="2">
+      <c r="AT2" s="2">
         <v>35611</v>
       </c>
-      <c r="W2" s="2">
+      <c r="AU2" s="2">
         <v>33220</v>
       </c>
-      <c r="X2" s="2">
+      <c r="AV2" s="2">
         <v>27871</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="AW2" s="2">
         <v>17996</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="AX2" s="2">
         <v>42249</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="6">
+        <v>4244.482</v>
+      </c>
+      <c r="C3" s="6">
+        <v>5781.0259999999998</v>
+      </c>
+      <c r="D3" s="6">
+        <v>9734.393</v>
+      </c>
+      <c r="E3" s="6">
+        <v>4259.665</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2737.0430000000001</v>
+      </c>
+      <c r="G3" s="6">
+        <v>4030.3679999999999</v>
+      </c>
+      <c r="H3" s="6">
+        <v>4747.826</v>
+      </c>
+      <c r="I3" s="6">
+        <v>3520.1779999999999</v>
+      </c>
+      <c r="J3" s="6">
+        <v>4437.1379999999999</v>
+      </c>
+      <c r="K3" s="6">
+        <v>8190.3280000000004</v>
+      </c>
+      <c r="L3" s="6">
+        <v>10856.218000000001</v>
+      </c>
+      <c r="M3" s="6">
+        <v>7965.42</v>
+      </c>
+      <c r="N3" s="6">
+        <v>8863.018</v>
+      </c>
+      <c r="O3" s="6">
+        <v>7406.6310000000003</v>
+      </c>
+      <c r="P3" s="6">
+        <v>19540.352999999999</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>20948.199000000001</v>
+      </c>
+      <c r="R3" s="6">
+        <v>17159.364000000001</v>
+      </c>
+      <c r="S3" s="6">
+        <v>15025.991</v>
+      </c>
+      <c r="T3" s="6">
+        <v>13790.574000000001</v>
+      </c>
+      <c r="U3" s="6">
+        <v>20228.898000000001</v>
+      </c>
+      <c r="V3" s="6">
+        <v>14659.74</v>
+      </c>
+      <c r="W3" s="6">
+        <v>8774.6679999999997</v>
+      </c>
+      <c r="X3" s="6">
+        <v>14722.7</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>9142.1139999999996</v>
+      </c>
+      <c r="Z3" s="2">
         <v>16235</v>
       </c>
-      <c r="C3" s="2">
+      <c r="AA3" s="2">
         <v>19551</v>
       </c>
-      <c r="D3" s="2">
+      <c r="AB3" s="2">
         <v>13691</v>
       </c>
-      <c r="E3" s="2">
+      <c r="AC3" s="2">
         <v>14364</v>
       </c>
-      <c r="F3" s="2">
+      <c r="AD3" s="2">
         <v>10783</v>
       </c>
-      <c r="G3" s="2">
+      <c r="AE3" s="2">
         <v>9014</v>
       </c>
-      <c r="H3" s="2">
+      <c r="AF3" s="2">
         <v>18373</v>
       </c>
-      <c r="I3" s="2">
+      <c r="AG3" s="2">
         <v>11540</v>
       </c>
-      <c r="J3" s="2">
+      <c r="AH3" s="2">
         <v>5702</v>
       </c>
-      <c r="K3" s="2">
+      <c r="AI3" s="2">
         <v>8716</v>
       </c>
-      <c r="L3" s="2">
+      <c r="AJ3" s="2">
         <v>9793</v>
       </c>
-      <c r="M3" s="2">
+      <c r="AK3" s="2">
         <v>11361</v>
       </c>
-      <c r="N3" s="2">
+      <c r="AL3" s="2">
         <v>20997</v>
       </c>
-      <c r="O3" s="2">
+      <c r="AM3" s="2">
         <v>13206</v>
       </c>
-      <c r="P3" s="2">
+      <c r="AN3" s="2">
         <v>13648</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="AO3" s="2">
         <v>18044</v>
       </c>
-      <c r="R3" s="2">
+      <c r="AP3" s="2">
         <v>14518</v>
       </c>
-      <c r="S3" s="2">
+      <c r="AQ3" s="2">
         <v>14036</v>
       </c>
-      <c r="T3" s="2">
+      <c r="AR3" s="2">
         <v>8451</v>
       </c>
-      <c r="U3" s="2">
+      <c r="AS3" s="2">
         <v>11778</v>
       </c>
-      <c r="V3" s="2">
+      <c r="AT3" s="2">
         <v>12045</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AU3" s="2">
         <v>12518</v>
       </c>
-      <c r="X3" s="2">
+      <c r="AV3" s="2">
         <v>10553</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="AW3" s="2">
         <v>18360</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="AX3" s="2">
         <v>10902</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="6">
+        <v>35092.947</v>
+      </c>
+      <c r="C4" s="6">
+        <v>25124.842000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>21870.277999999998</v>
+      </c>
+      <c r="E4" s="6">
+        <v>19568.25</v>
+      </c>
+      <c r="F4" s="6">
+        <v>31330.1</v>
+      </c>
+      <c r="G4" s="6">
+        <v>30018.306</v>
+      </c>
+      <c r="H4" s="6">
+        <v>42327.258999999998</v>
+      </c>
+      <c r="I4" s="6">
+        <v>35531.712</v>
+      </c>
+      <c r="J4" s="6">
+        <v>35159.286999999997</v>
+      </c>
+      <c r="K4" s="6">
+        <v>38352.89</v>
+      </c>
+      <c r="L4" s="6">
+        <v>34128.178</v>
+      </c>
+      <c r="M4" s="6">
+        <v>31792.030999999999</v>
+      </c>
+      <c r="N4" s="6">
+        <v>32870.701999999997</v>
+      </c>
+      <c r="O4" s="6">
+        <v>30000.411</v>
+      </c>
+      <c r="P4" s="6">
+        <v>40182.637000000002</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>53798.038</v>
+      </c>
+      <c r="R4" s="6">
+        <v>46787.053999999996</v>
+      </c>
+      <c r="S4" s="6">
+        <v>30248.437999999998</v>
+      </c>
+      <c r="T4" s="6">
+        <v>35403.718000000001</v>
+      </c>
+      <c r="U4" s="6">
+        <v>29069.743999999999</v>
+      </c>
+      <c r="V4" s="6">
+        <v>28484.518</v>
+      </c>
+      <c r="W4" s="6">
+        <v>38396.016000000003</v>
+      </c>
+      <c r="X4" s="6">
+        <v>41352.349000000002</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>43193.139000000003</v>
+      </c>
+      <c r="Z4" s="2">
         <v>46443</v>
       </c>
-      <c r="C4" s="2">
+      <c r="AA4" s="2">
         <v>43733</v>
       </c>
-      <c r="D4" s="2">
+      <c r="AB4" s="2">
         <v>63998</v>
       </c>
-      <c r="E4" s="2">
+      <c r="AC4" s="2">
         <v>43384</v>
       </c>
-      <c r="F4" s="2">
+      <c r="AD4" s="2">
         <v>45400</v>
       </c>
-      <c r="G4" s="2">
+      <c r="AE4" s="2">
         <v>60220</v>
       </c>
-      <c r="H4" s="2">
+      <c r="AF4" s="2">
         <v>52385</v>
       </c>
-      <c r="I4" s="2">
+      <c r="AG4" s="2">
         <v>45112</v>
       </c>
-      <c r="J4" s="2">
+      <c r="AH4" s="2">
         <v>52194</v>
       </c>
-      <c r="K4" s="2">
+      <c r="AI4" s="2">
         <v>43285</v>
       </c>
-      <c r="L4" s="2">
+      <c r="AJ4" s="2">
         <v>61514</v>
       </c>
-      <c r="M4" s="2">
+      <c r="AK4" s="2">
         <v>68640</v>
       </c>
-      <c r="N4" s="2">
+      <c r="AL4" s="2">
         <v>77586</v>
       </c>
-      <c r="O4" s="2">
+      <c r="AM4" s="2">
         <v>66324</v>
       </c>
-      <c r="P4" s="2">
+      <c r="AN4" s="2">
         <v>73489</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="AO4" s="2">
         <v>74439</v>
       </c>
-      <c r="R4" s="2">
+      <c r="AP4" s="2">
         <v>60399</v>
       </c>
-      <c r="S4" s="2">
+      <c r="AQ4" s="2">
         <v>49870</v>
       </c>
-      <c r="T4" s="2">
+      <c r="AR4" s="2">
         <v>59376</v>
       </c>
-      <c r="U4" s="2">
+      <c r="AS4" s="2">
         <v>65647</v>
       </c>
-      <c r="V4" s="2">
+      <c r="AT4" s="2">
         <v>66043</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AU4" s="2">
         <v>60908</v>
       </c>
-      <c r="X4" s="2">
+      <c r="AV4" s="2">
         <v>55328</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="AW4" s="2">
         <v>61892</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="AX4" s="2">
         <v>53761</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="6">
+        <v>86639.311000000002</v>
+      </c>
+      <c r="C5" s="6">
+        <v>71176.191000000006</v>
+      </c>
+      <c r="D5" s="6">
+        <v>87477.248000000007</v>
+      </c>
+      <c r="E5" s="6">
+        <v>77809.623000000007</v>
+      </c>
+      <c r="F5" s="6">
+        <v>50096.372000000003</v>
+      </c>
+      <c r="G5" s="6">
+        <v>68566.903999999995</v>
+      </c>
+      <c r="H5" s="6">
+        <v>73617.661999999997</v>
+      </c>
+      <c r="I5" s="6">
+        <v>97351.741999999998</v>
+      </c>
+      <c r="J5" s="6">
+        <v>77046.167000000001</v>
+      </c>
+      <c r="K5" s="6">
+        <v>81044.101999999999</v>
+      </c>
+      <c r="L5" s="6">
+        <v>84069.58</v>
+      </c>
+      <c r="M5" s="6">
+        <v>92107.815000000002</v>
+      </c>
+      <c r="N5" s="6">
+        <v>109535.807</v>
+      </c>
+      <c r="O5" s="6">
+        <v>87380.906000000003</v>
+      </c>
+      <c r="P5" s="6">
+        <v>80409.092999999993</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>81898.221999999994</v>
+      </c>
+      <c r="R5" s="6">
+        <v>65029.616999999998</v>
+      </c>
+      <c r="S5" s="6">
+        <v>50817.334000000003</v>
+      </c>
+      <c r="T5" s="6">
+        <v>96002.702000000005</v>
+      </c>
+      <c r="U5" s="6">
+        <v>77213.444000000003</v>
+      </c>
+      <c r="V5" s="6">
+        <v>72593.528000000006</v>
+      </c>
+      <c r="W5" s="6">
+        <v>100473.704</v>
+      </c>
+      <c r="X5" s="6">
+        <v>81801.244999999995</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>81540.221000000005</v>
+      </c>
+      <c r="Z5" s="2">
         <v>98947</v>
       </c>
-      <c r="C5" s="2">
+      <c r="AA5" s="2">
         <v>93447</v>
       </c>
-      <c r="D5" s="2">
+      <c r="AB5" s="2">
         <v>90611</v>
       </c>
-      <c r="E5" s="2">
+      <c r="AC5" s="2">
         <v>84317</v>
       </c>
-      <c r="F5" s="2">
+      <c r="AD5" s="2">
         <v>85470</v>
       </c>
-      <c r="G5" s="2">
+      <c r="AE5" s="2">
         <v>82673</v>
       </c>
-      <c r="H5" s="2">
+      <c r="AF5" s="2">
         <v>86034</v>
       </c>
-      <c r="I5" s="2">
+      <c r="AG5" s="2">
         <v>97585</v>
       </c>
-      <c r="J5" s="2">
+      <c r="AH5" s="2">
         <v>93042</v>
       </c>
-      <c r="K5" s="2">
+      <c r="AI5" s="2">
         <v>85392</v>
       </c>
-      <c r="L5" s="2">
+      <c r="AJ5" s="2">
         <v>95816</v>
       </c>
-      <c r="M5" s="2">
+      <c r="AK5" s="2">
         <v>92939</v>
       </c>
-      <c r="N5" s="2">
+      <c r="AL5" s="2">
         <v>92759</v>
       </c>
-      <c r="O5" s="2">
+      <c r="AM5" s="2">
         <v>93653</v>
       </c>
-      <c r="P5" s="2">
+      <c r="AN5" s="2">
         <v>83929</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="AO5" s="2">
         <v>94867</v>
       </c>
-      <c r="R5" s="2">
+      <c r="AP5" s="2">
         <v>112191</v>
       </c>
-      <c r="S5" s="2">
+      <c r="AQ5" s="2">
         <v>85732</v>
       </c>
-      <c r="T5" s="2">
+      <c r="AR5" s="2">
         <v>101527</v>
       </c>
-      <c r="U5" s="2">
+      <c r="AS5" s="2">
         <v>102533</v>
       </c>
-      <c r="V5" s="2">
+      <c r="AT5" s="2">
         <v>99018</v>
       </c>
-      <c r="W5" s="2">
+      <c r="AU5" s="2">
         <v>98389</v>
       </c>
-      <c r="X5" s="2">
+      <c r="AV5" s="2">
         <v>88392</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="AW5" s="2">
         <v>95184</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="AX5" s="2">
         <v>96041</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="6">
+        <v>5070.6959999999999</v>
+      </c>
+      <c r="C6" s="6">
+        <v>8336.9259999999995</v>
+      </c>
+      <c r="D6" s="6">
+        <v>11726.523999999999</v>
+      </c>
+      <c r="E6" s="6">
+        <v>12395.75</v>
+      </c>
+      <c r="F6" s="6">
+        <v>10614.556</v>
+      </c>
+      <c r="G6" s="6">
+        <v>8490.8330000000005</v>
+      </c>
+      <c r="H6" s="6">
+        <v>12980.388000000001</v>
+      </c>
+      <c r="I6" s="6">
+        <v>10443.73</v>
+      </c>
+      <c r="J6" s="6">
+        <v>10642.224</v>
+      </c>
+      <c r="K6" s="6">
+        <v>11398.697</v>
+      </c>
+      <c r="L6" s="6">
+        <v>7626.4489999999996</v>
+      </c>
+      <c r="M6" s="6">
+        <v>6698.3919999999998</v>
+      </c>
+      <c r="N6" s="6">
+        <v>6245.0140000000001</v>
+      </c>
+      <c r="O6" s="6">
+        <v>8945.3639999999996</v>
+      </c>
+      <c r="P6" s="6">
+        <v>9510.0429999999997</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>8876.4560000000001</v>
+      </c>
+      <c r="R6" s="6">
+        <v>8177.4229999999998</v>
+      </c>
+      <c r="S6" s="6">
+        <v>6903.4549999999999</v>
+      </c>
+      <c r="T6" s="6">
+        <v>6582.7460000000001</v>
+      </c>
+      <c r="U6" s="6">
+        <v>4943.74</v>
+      </c>
+      <c r="V6" s="6">
+        <v>8093.2370000000001</v>
+      </c>
+      <c r="W6" s="6">
+        <v>8429.5120000000006</v>
+      </c>
+      <c r="X6" s="6">
+        <v>6928.2820000000002</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>5679.8119999999999</v>
+      </c>
+      <c r="Z6" s="2">
         <v>5055</v>
       </c>
-      <c r="C6" s="2">
+      <c r="AA6" s="2">
         <v>6570</v>
       </c>
-      <c r="D6" s="2">
+      <c r="AB6" s="2">
         <v>6230</v>
       </c>
-      <c r="E6" s="2">
+      <c r="AC6" s="2">
         <v>10049</v>
       </c>
-      <c r="F6" s="2">
+      <c r="AD6" s="2">
         <v>11281</v>
       </c>
-      <c r="G6" s="2">
+      <c r="AE6" s="2">
         <v>9551</v>
       </c>
-      <c r="H6" s="2">
+      <c r="AF6" s="2">
         <v>11252</v>
       </c>
-      <c r="I6" s="2">
+      <c r="AG6" s="2">
         <v>9735</v>
       </c>
-      <c r="J6" s="2">
+      <c r="AH6" s="2">
         <v>11138</v>
       </c>
-      <c r="K6" s="2">
+      <c r="AI6" s="2">
         <v>6716</v>
       </c>
-      <c r="L6" s="2">
+      <c r="AJ6" s="2">
         <v>8950</v>
       </c>
-      <c r="M6" s="2">
+      <c r="AK6" s="2">
         <v>15410</v>
       </c>
-      <c r="N6" s="2">
+      <c r="AL6" s="2">
         <v>9829</v>
       </c>
-      <c r="O6" s="2">
+      <c r="AM6" s="2">
         <v>8407</v>
       </c>
-      <c r="P6" s="2">
+      <c r="AN6" s="2">
         <v>9378</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="AO6" s="2">
         <v>12858</v>
       </c>
-      <c r="R6" s="2">
+      <c r="AP6" s="2">
         <v>13601</v>
       </c>
-      <c r="S6" s="2">
+      <c r="AQ6" s="2">
         <v>15405</v>
       </c>
-      <c r="T6" s="2">
+      <c r="AR6" s="2">
         <v>16462</v>
       </c>
-      <c r="U6" s="2">
+      <c r="AS6" s="2">
         <v>13743</v>
       </c>
-      <c r="V6" s="2">
+      <c r="AT6" s="2">
         <v>8679</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AU6" s="2">
         <v>9485</v>
       </c>
-      <c r="X6" s="2">
+      <c r="AV6" s="2">
         <v>10383</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AW6" s="2">
         <v>14435</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AX6" s="2">
         <v>11508</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="6">
+        <v>1597.03</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3474.453</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2356.88</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3163.83</v>
+      </c>
+      <c r="F7" s="6">
+        <v>4173.8450000000003</v>
+      </c>
+      <c r="G7" s="6">
+        <v>4385.46</v>
+      </c>
+      <c r="H7" s="6">
+        <v>5929.31</v>
+      </c>
+      <c r="I7" s="6">
+        <v>6016.13</v>
+      </c>
+      <c r="J7" s="6">
+        <v>5967.49</v>
+      </c>
+      <c r="K7" s="6">
+        <v>2322.0050000000001</v>
+      </c>
+      <c r="L7" s="6">
+        <v>3350.6750000000002</v>
+      </c>
+      <c r="M7" s="6">
+        <v>4043.56</v>
+      </c>
+      <c r="N7" s="6">
+        <v>4711.9780000000001</v>
+      </c>
+      <c r="O7" s="6">
+        <v>10117.871999999999</v>
+      </c>
+      <c r="P7" s="6">
+        <v>4904.2950000000001</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>9151.6299999999992</v>
+      </c>
+      <c r="R7" s="6">
+        <v>8025.8149999999996</v>
+      </c>
+      <c r="S7" s="6">
+        <v>8258.0409999999993</v>
+      </c>
+      <c r="T7" s="6">
+        <v>7484.165</v>
+      </c>
+      <c r="U7" s="6">
+        <v>9589.2620000000006</v>
+      </c>
+      <c r="V7" s="6">
+        <v>6266.5659999999998</v>
+      </c>
+      <c r="W7" s="6">
+        <v>5774.9840000000004</v>
+      </c>
+      <c r="X7" s="6">
+        <v>4463.17</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>6425.14</v>
+      </c>
+      <c r="Z7" s="2">
         <v>5499</v>
       </c>
-      <c r="C7" s="2">
+      <c r="AA7" s="2">
         <v>4811</v>
       </c>
-      <c r="D7" s="2">
+      <c r="AB7" s="2">
         <v>6846</v>
       </c>
-      <c r="E7" s="2">
+      <c r="AC7" s="2">
         <v>6608</v>
       </c>
-      <c r="F7" s="2">
+      <c r="AD7" s="2">
         <v>11807</v>
       </c>
-      <c r="G7" s="2">
+      <c r="AE7" s="2">
         <v>8255</v>
       </c>
-      <c r="H7" s="2">
+      <c r="AF7" s="2">
         <v>10698</v>
       </c>
-      <c r="I7" s="2">
+      <c r="AG7" s="2">
         <v>9699</v>
       </c>
-      <c r="J7" s="2">
+      <c r="AH7" s="2">
         <v>13048</v>
       </c>
-      <c r="K7" s="2">
+      <c r="AI7" s="2">
         <v>9310</v>
       </c>
-      <c r="L7" s="2">
+      <c r="AJ7" s="2">
         <v>11590</v>
       </c>
-      <c r="M7" s="2">
+      <c r="AK7" s="2">
         <v>7835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="AL7" s="2">
         <v>9794</v>
       </c>
-      <c r="O7" s="2">
+      <c r="AM7" s="2">
         <v>7057</v>
       </c>
-      <c r="P7" s="2">
+      <c r="AN7" s="2">
         <v>6586</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="AO7" s="2">
         <v>11027</v>
       </c>
-      <c r="R7" s="2">
+      <c r="AP7" s="2">
         <v>10978</v>
       </c>
-      <c r="S7" s="2">
+      <c r="AQ7" s="2">
         <v>11816</v>
       </c>
-      <c r="T7" s="2">
+      <c r="AR7" s="2">
         <v>10917</v>
       </c>
-      <c r="U7" s="2">
+      <c r="AS7" s="2">
         <v>9721</v>
       </c>
-      <c r="V7" s="2">
+      <c r="AT7" s="2">
         <v>15937</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AU7" s="2">
         <v>12431</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AV7" s="2">
         <v>10700</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AW7" s="2">
         <v>13847</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AX7" s="2">
         <v>20891</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="6">
+        <v>18359.348000000002</v>
+      </c>
+      <c r="C8" s="6">
+        <v>15628.361000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>21532.748</v>
+      </c>
+      <c r="E8" s="6">
+        <v>23605.54</v>
+      </c>
+      <c r="F8" s="6">
+        <v>22882.830999999998</v>
+      </c>
+      <c r="G8" s="6">
+        <v>23435.518</v>
+      </c>
+      <c r="H8" s="6">
+        <v>21498.670999999998</v>
+      </c>
+      <c r="I8" s="6">
+        <v>19192.428</v>
+      </c>
+      <c r="J8" s="6">
+        <v>19273.73</v>
+      </c>
+      <c r="K8" s="6">
+        <v>12384.620999999999</v>
+      </c>
+      <c r="L8" s="6">
+        <v>18034.962</v>
+      </c>
+      <c r="M8" s="6">
+        <v>21593.575000000001</v>
+      </c>
+      <c r="N8" s="6">
+        <v>14651.052</v>
+      </c>
+      <c r="O8" s="6">
+        <v>18416.3</v>
+      </c>
+      <c r="P8" s="6">
+        <v>22205.089</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>15818.102000000001</v>
+      </c>
+      <c r="R8" s="6">
+        <v>23965.024000000001</v>
+      </c>
+      <c r="S8" s="6">
+        <v>28655.817999999999</v>
+      </c>
+      <c r="T8" s="6">
+        <v>31645.044999999998</v>
+      </c>
+      <c r="U8" s="6">
+        <v>20030.615000000002</v>
+      </c>
+      <c r="V8" s="6">
+        <v>27065.109</v>
+      </c>
+      <c r="W8" s="6">
+        <v>28295.789000000001</v>
+      </c>
+      <c r="X8" s="6">
+        <v>22096.843000000001</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>25928.969000000001</v>
+      </c>
+      <c r="Z8" s="2">
         <v>21203</v>
       </c>
-      <c r="C8" s="2">
+      <c r="AA8" s="2">
         <v>19262</v>
       </c>
-      <c r="D8" s="2">
+      <c r="AB8" s="2">
         <v>18585</v>
       </c>
-      <c r="E8" s="2">
+      <c r="AC8" s="2">
         <v>25493</v>
       </c>
-      <c r="F8" s="2">
+      <c r="AD8" s="2">
         <v>30048</v>
       </c>
-      <c r="G8" s="2">
+      <c r="AE8" s="2">
         <v>20660</v>
       </c>
-      <c r="H8" s="2">
+      <c r="AF8" s="2">
         <v>30104</v>
       </c>
-      <c r="I8" s="2">
+      <c r="AG8" s="2">
         <v>26814</v>
       </c>
-      <c r="J8" s="2">
+      <c r="AH8" s="2">
         <v>34129</v>
       </c>
-      <c r="K8" s="2">
+      <c r="AI8" s="2">
         <v>25919</v>
       </c>
-      <c r="L8" s="2">
+      <c r="AJ8" s="2">
         <v>26001</v>
       </c>
-      <c r="M8" s="2">
+      <c r="AK8" s="2">
         <v>28028</v>
       </c>
-      <c r="N8" s="2">
+      <c r="AL8" s="2">
         <v>29990</v>
       </c>
-      <c r="O8" s="2">
+      <c r="AM8" s="2">
         <v>26588</v>
       </c>
-      <c r="P8" s="2">
+      <c r="AN8" s="2">
         <v>23277</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="AO8" s="2">
         <v>26726</v>
       </c>
-      <c r="R8" s="2">
+      <c r="AP8" s="2">
         <v>27322</v>
       </c>
-      <c r="S8" s="2">
+      <c r="AQ8" s="2">
         <v>30006</v>
       </c>
-      <c r="T8" s="2">
+      <c r="AR8" s="2">
         <v>31389</v>
       </c>
-      <c r="U8" s="2">
+      <c r="AS8" s="2">
         <v>22933</v>
       </c>
-      <c r="V8" s="2">
+      <c r="AT8" s="2">
         <v>26472</v>
       </c>
-      <c r="W8" s="2">
+      <c r="AU8" s="2">
         <v>25632</v>
       </c>
-      <c r="X8" s="2">
+      <c r="AV8" s="2">
         <v>27504</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="AW8" s="2">
         <v>25036</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="AX8" s="2">
         <v>25825</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="6">
+        <v>66655.797999999995</v>
+      </c>
+      <c r="C9" s="6">
+        <v>61251.112999999998</v>
+      </c>
+      <c r="D9" s="6">
+        <v>48214.131999999998</v>
+      </c>
+      <c r="E9" s="6">
+        <v>71357.046000000002</v>
+      </c>
+      <c r="F9" s="6">
+        <v>73842.248999999996</v>
+      </c>
+      <c r="G9" s="6">
+        <v>59891.472000000002</v>
+      </c>
+      <c r="H9" s="6">
+        <v>59633.538</v>
+      </c>
+      <c r="I9" s="6">
+        <v>64262.137000000002</v>
+      </c>
+      <c r="J9" s="6">
+        <v>67653.126000000004</v>
+      </c>
+      <c r="K9" s="6">
+        <v>53065.66</v>
+      </c>
+      <c r="L9" s="6">
+        <v>39867.589999999997</v>
+      </c>
+      <c r="M9" s="6">
+        <v>50702.173000000003</v>
+      </c>
+      <c r="N9" s="6">
+        <v>57688.434999999998</v>
+      </c>
+      <c r="O9" s="6">
+        <v>60259.27</v>
+      </c>
+      <c r="P9" s="6">
+        <v>60411.303</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>61659.656000000003</v>
+      </c>
+      <c r="R9" s="6">
+        <v>59322.466999999997</v>
+      </c>
+      <c r="S9" s="6">
+        <v>61405.476999999999</v>
+      </c>
+      <c r="T9" s="6">
+        <v>61329.523999999998</v>
+      </c>
+      <c r="U9" s="6">
+        <v>70855.180999999997</v>
+      </c>
+      <c r="V9" s="6">
+        <v>68676.051999999996</v>
+      </c>
+      <c r="W9" s="6">
+        <v>76203.793000000005</v>
+      </c>
+      <c r="X9" s="6">
+        <v>56055.875999999997</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>66783.142000000007</v>
+      </c>
+      <c r="Z9" s="2">
         <v>59823</v>
       </c>
-      <c r="C9" s="2">
+      <c r="AA9" s="2">
         <v>59137</v>
       </c>
-      <c r="D9" s="2">
+      <c r="AB9" s="2">
         <v>68406</v>
       </c>
-      <c r="E9" s="2">
+      <c r="AC9" s="2">
         <v>75096</v>
       </c>
-      <c r="F9" s="2">
+      <c r="AD9" s="2">
         <v>65875</v>
       </c>
-      <c r="G9" s="2">
+      <c r="AE9" s="2">
         <v>68858</v>
       </c>
-      <c r="H9" s="2">
+      <c r="AF9" s="2">
         <v>81164</v>
       </c>
-      <c r="I9" s="2">
+      <c r="AG9" s="2">
         <v>64814</v>
       </c>
-      <c r="J9" s="2">
+      <c r="AH9" s="2">
         <v>73534</v>
       </c>
-      <c r="K9" s="2">
+      <c r="AI9" s="2">
         <v>85811</v>
       </c>
-      <c r="L9" s="2">
+      <c r="AJ9" s="2">
         <v>71120</v>
       </c>
-      <c r="M9" s="2">
+      <c r="AK9" s="2">
         <v>88862</v>
       </c>
-      <c r="N9" s="2">
+      <c r="AL9" s="2">
         <v>78556</v>
       </c>
-      <c r="O9" s="2">
+      <c r="AM9" s="2">
         <v>86451</v>
       </c>
-      <c r="P9" s="2">
+      <c r="AN9" s="2">
         <v>82719</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="AO9" s="2">
         <v>71939</v>
       </c>
-      <c r="R9" s="2">
+      <c r="AP9" s="2">
         <v>81208</v>
       </c>
-      <c r="S9" s="2">
+      <c r="AQ9" s="2">
         <v>81722</v>
       </c>
-      <c r="T9" s="2">
+      <c r="AR9" s="2">
         <v>79837</v>
       </c>
-      <c r="U9" s="2">
+      <c r="AS9" s="2">
         <v>73278</v>
       </c>
-      <c r="V9" s="2">
+      <c r="AT9" s="2">
         <v>88404</v>
       </c>
-      <c r="W9" s="2">
+      <c r="AU9" s="2">
         <v>63757</v>
       </c>
-      <c r="X9" s="2">
+      <c r="AV9" s="2">
         <v>66366</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="AW9" s="2">
         <v>73488</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="AX9" s="2">
         <v>89902</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="6">
+        <v>28302.959999999999</v>
+      </c>
+      <c r="C10" s="6">
+        <v>26538.601999999999</v>
+      </c>
+      <c r="D10" s="6">
+        <v>34442.625999999997</v>
+      </c>
+      <c r="E10" s="6">
+        <v>34098</v>
+      </c>
+      <c r="F10" s="6">
+        <v>24478.878000000001</v>
+      </c>
+      <c r="G10" s="6">
+        <v>26254.482</v>
+      </c>
+      <c r="H10" s="6">
+        <v>26899.686000000002</v>
+      </c>
+      <c r="I10" s="6">
+        <v>31945.047999999999</v>
+      </c>
+      <c r="J10" s="6">
+        <v>23328.328000000001</v>
+      </c>
+      <c r="K10" s="6">
+        <v>23543.776000000002</v>
+      </c>
+      <c r="L10" s="6">
+        <v>23850.045999999998</v>
+      </c>
+      <c r="M10" s="6">
+        <v>23609.516</v>
+      </c>
+      <c r="N10" s="6">
+        <v>24856.87</v>
+      </c>
+      <c r="O10" s="6">
+        <v>26804.968000000001</v>
+      </c>
+      <c r="P10" s="6">
+        <v>25141.252</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>21430.734</v>
+      </c>
+      <c r="R10" s="6">
+        <v>23410.848000000002</v>
+      </c>
+      <c r="S10" s="6">
+        <v>23989.117999999999</v>
+      </c>
+      <c r="T10" s="6">
+        <v>21035.862000000001</v>
+      </c>
+      <c r="U10" s="6">
+        <v>17662.526000000002</v>
+      </c>
+      <c r="V10" s="6">
+        <v>16598.990000000002</v>
+      </c>
+      <c r="W10" s="6">
+        <v>28429.198</v>
+      </c>
+      <c r="X10" s="6">
+        <v>24922.596000000001</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>25236.741999999998</v>
+      </c>
+      <c r="Z10" s="2">
         <v>23813</v>
       </c>
-      <c r="C10" s="2">
+      <c r="AA10" s="2">
         <v>23310</v>
       </c>
-      <c r="D10" s="2">
+      <c r="AB10" s="2">
         <v>33402</v>
       </c>
-      <c r="E10" s="2">
+      <c r="AC10" s="2">
         <v>32101</v>
       </c>
-      <c r="F10" s="2">
+      <c r="AD10" s="2">
         <v>33568</v>
       </c>
-      <c r="G10" s="2">
+      <c r="AE10" s="2">
         <v>31893</v>
       </c>
-      <c r="H10" s="2">
+      <c r="AF10" s="2">
         <v>33425</v>
       </c>
-      <c r="I10" s="2">
+      <c r="AG10" s="2">
         <v>31894</v>
       </c>
-      <c r="J10" s="2">
+      <c r="AH10" s="2">
         <v>32588</v>
       </c>
-      <c r="K10" s="2">
+      <c r="AI10" s="2">
         <v>41535</v>
       </c>
-      <c r="L10" s="2">
+      <c r="AJ10" s="2">
         <v>26767</v>
       </c>
-      <c r="M10" s="2">
+      <c r="AK10" s="2">
         <v>33045</v>
       </c>
-      <c r="N10" s="2">
+      <c r="AL10" s="2">
         <v>36070</v>
       </c>
-      <c r="O10" s="2">
+      <c r="AM10" s="2">
         <v>32235</v>
       </c>
-      <c r="P10" s="2">
+      <c r="AN10" s="2">
         <v>35830</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="AO10" s="2">
         <v>37647</v>
       </c>
-      <c r="R10" s="2">
+      <c r="AP10" s="2">
         <v>25665</v>
       </c>
-      <c r="S10" s="2">
+      <c r="AQ10" s="2">
         <v>29628</v>
       </c>
-      <c r="T10" s="2">
+      <c r="AR10" s="2">
         <v>30614</v>
       </c>
-      <c r="U10" s="2">
+      <c r="AS10" s="2">
         <v>32630</v>
       </c>
-      <c r="V10" s="2">
+      <c r="AT10" s="2">
         <v>31888</v>
       </c>
-      <c r="W10" s="2">
+      <c r="AU10" s="2">
         <v>38300</v>
       </c>
-      <c r="X10" s="2">
+      <c r="AV10" s="2">
         <v>34651</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="AW10" s="2">
         <v>37934</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AX10" s="2">
         <v>33444</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="6">
+        <v>87294.771999999997</v>
+      </c>
+      <c r="C11" s="6">
+        <v>86041.64</v>
+      </c>
+      <c r="D11" s="6">
+        <v>94072.635999999999</v>
+      </c>
+      <c r="E11" s="6">
+        <v>98185.595000000001</v>
+      </c>
+      <c r="F11" s="6">
+        <v>89900.695000000007</v>
+      </c>
+      <c r="G11" s="6">
+        <v>78487.790999999997</v>
+      </c>
+      <c r="H11" s="6">
+        <v>84183.34</v>
+      </c>
+      <c r="I11" s="6">
+        <v>94797.540999999997</v>
+      </c>
+      <c r="J11" s="6">
+        <v>98932.68</v>
+      </c>
+      <c r="K11" s="6">
+        <v>96055.691999999995</v>
+      </c>
+      <c r="L11" s="6">
+        <v>108041.47500000001</v>
+      </c>
+      <c r="M11" s="6">
+        <v>108943.13400000001</v>
+      </c>
+      <c r="N11" s="6">
+        <v>78075.524000000005</v>
+      </c>
+      <c r="O11" s="6">
+        <v>98122.717000000004</v>
+      </c>
+      <c r="P11" s="6">
+        <v>90564.248000000007</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>84347.691999999995</v>
+      </c>
+      <c r="R11" s="6">
+        <v>83930.743000000002</v>
+      </c>
+      <c r="S11" s="6">
+        <v>91674.195999999996</v>
+      </c>
+      <c r="T11" s="6">
+        <v>86491.731</v>
+      </c>
+      <c r="U11" s="6">
+        <v>95877.631999999998</v>
+      </c>
+      <c r="V11" s="6">
+        <v>83230.569000000003</v>
+      </c>
+      <c r="W11" s="6">
+        <v>78980.482000000004</v>
+      </c>
+      <c r="X11" s="6">
+        <v>88239.096000000005</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>102205.11199999999</v>
+      </c>
+      <c r="Z11" s="2">
         <v>100834</v>
       </c>
-      <c r="C11" s="2">
+      <c r="AA11" s="2">
         <v>97156</v>
       </c>
-      <c r="D11" s="2">
+      <c r="AB11" s="2">
         <v>91899</v>
       </c>
-      <c r="E11" s="2">
+      <c r="AC11" s="2">
         <v>105076</v>
       </c>
-      <c r="F11" s="2">
+      <c r="AD11" s="2">
         <v>91147</v>
       </c>
-      <c r="G11" s="2">
+      <c r="AE11" s="2">
         <v>98881</v>
       </c>
-      <c r="H11" s="2">
+      <c r="AF11" s="2">
         <v>104277</v>
       </c>
-      <c r="I11" s="2">
+      <c r="AG11" s="2">
         <v>105656</v>
       </c>
-      <c r="J11" s="2">
+      <c r="AH11" s="2">
         <v>98123</v>
       </c>
-      <c r="K11" s="2">
+      <c r="AI11" s="2">
         <v>101493</v>
       </c>
-      <c r="L11" s="2">
+      <c r="AJ11" s="2">
         <v>116372</v>
       </c>
-      <c r="M11" s="2">
+      <c r="AK11" s="2">
         <v>113039</v>
       </c>
-      <c r="N11" s="2">
+      <c r="AL11" s="2">
         <v>114030</v>
       </c>
-      <c r="O11" s="2">
+      <c r="AM11" s="2">
         <v>113049</v>
       </c>
-      <c r="P11" s="2">
+      <c r="AN11" s="2">
         <v>110889</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="AO11" s="2">
         <v>103806</v>
       </c>
-      <c r="R11" s="2">
+      <c r="AP11" s="2">
         <v>125946</v>
       </c>
-      <c r="S11" s="2">
+      <c r="AQ11" s="2">
         <v>110345</v>
       </c>
-      <c r="T11" s="2">
+      <c r="AR11" s="2">
         <v>127687</v>
       </c>
-      <c r="U11" s="2">
+      <c r="AS11" s="2">
         <v>107534</v>
       </c>
-      <c r="V11" s="2">
+      <c r="AT11" s="2">
         <v>113883</v>
       </c>
-      <c r="W11" s="2">
+      <c r="AU11" s="2">
         <v>110527</v>
       </c>
-      <c r="X11" s="2">
+      <c r="AV11" s="2">
         <v>112145</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="AW11" s="2">
         <v>122695</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="AX11" s="2">
         <v>121828</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="6">
+        <v>117768.876</v>
+      </c>
+      <c r="C12" s="6">
+        <v>117548.14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>117486.965</v>
+      </c>
+      <c r="E12" s="6">
+        <v>170396.46100000001</v>
+      </c>
+      <c r="F12" s="6">
+        <v>174618.59</v>
+      </c>
+      <c r="G12" s="6">
+        <v>145721.08900000001</v>
+      </c>
+      <c r="H12" s="6">
+        <v>148072.484</v>
+      </c>
+      <c r="I12" s="6">
+        <v>148343.503</v>
+      </c>
+      <c r="J12" s="6">
+        <v>125875.223</v>
+      </c>
+      <c r="K12" s="6">
+        <v>159479.04800000001</v>
+      </c>
+      <c r="L12" s="6">
+        <v>125611.038</v>
+      </c>
+      <c r="M12" s="6">
+        <v>134209.84599999999</v>
+      </c>
+      <c r="N12" s="6">
+        <v>118939.664</v>
+      </c>
+      <c r="O12" s="6">
+        <v>110898.54700000001</v>
+      </c>
+      <c r="P12" s="6">
+        <v>124813.895</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>137669.49299999999</v>
+      </c>
+      <c r="R12" s="6">
+        <v>165379.77100000001</v>
+      </c>
+      <c r="S12" s="6">
+        <v>151444.068</v>
+      </c>
+      <c r="T12" s="6">
+        <v>125361.807</v>
+      </c>
+      <c r="U12" s="6">
+        <v>127375.061</v>
+      </c>
+      <c r="V12" s="6">
+        <v>148950.93799999999</v>
+      </c>
+      <c r="W12" s="6">
+        <v>164304.98699999999</v>
+      </c>
+      <c r="X12" s="6">
+        <v>160524.731</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>159248.978</v>
+      </c>
+      <c r="Z12" s="2">
         <v>135302</v>
       </c>
-      <c r="C12" s="2">
+      <c r="AA12" s="2">
         <v>129164</v>
       </c>
-      <c r="D12" s="2">
+      <c r="AB12" s="2">
         <v>127958</v>
       </c>
-      <c r="E12" s="2">
+      <c r="AC12" s="2">
         <v>162454</v>
       </c>
-      <c r="F12" s="2">
+      <c r="AD12" s="2">
         <v>166950</v>
       </c>
-      <c r="G12" s="2">
+      <c r="AE12" s="2">
         <v>153282</v>
       </c>
-      <c r="H12" s="2">
+      <c r="AF12" s="2">
         <v>145452</v>
       </c>
-      <c r="I12" s="2">
+      <c r="AG12" s="2">
         <v>143240</v>
       </c>
-      <c r="J12" s="2">
+      <c r="AH12" s="2">
         <v>150259</v>
       </c>
-      <c r="K12" s="2">
+      <c r="AI12" s="2">
         <v>187657</v>
       </c>
-      <c r="L12" s="2">
+      <c r="AJ12" s="2">
         <v>161207</v>
       </c>
-      <c r="M12" s="2">
+      <c r="AK12" s="2">
         <v>165893</v>
       </c>
-      <c r="N12" s="2">
+      <c r="AL12" s="2">
         <v>163048</v>
       </c>
-      <c r="O12" s="2">
+      <c r="AM12" s="2">
         <v>162068</v>
       </c>
-      <c r="P12" s="2">
+      <c r="AN12" s="2">
         <v>144870</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="AO12" s="2">
         <v>175435</v>
       </c>
-      <c r="R12" s="2">
+      <c r="AP12" s="2">
         <v>191408</v>
       </c>
-      <c r="S12" s="2">
+      <c r="AQ12" s="2">
         <v>163764</v>
       </c>
-      <c r="T12" s="2">
+      <c r="AR12" s="2">
         <v>162535</v>
       </c>
-      <c r="U12" s="2">
+      <c r="AS12" s="2">
         <v>150173</v>
       </c>
-      <c r="V12" s="2">
+      <c r="AT12" s="2">
         <v>166498</v>
       </c>
-      <c r="W12" s="2">
+      <c r="AU12" s="2">
         <v>194061</v>
       </c>
-      <c r="X12" s="2">
+      <c r="AV12" s="2">
         <v>158045</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="AW12" s="2">
         <v>167922</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="AX12" s="2">
         <v>187536</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="6">
+        <v>21054.34</v>
+      </c>
+      <c r="C13" s="6">
+        <v>18483.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>14474.036</v>
+      </c>
+      <c r="E13" s="6">
+        <v>18891.617999999999</v>
+      </c>
+      <c r="F13" s="6">
+        <v>21805.050999999999</v>
+      </c>
+      <c r="G13" s="6">
+        <v>16124.621999999999</v>
+      </c>
+      <c r="H13" s="6">
+        <v>12425.084000000001</v>
+      </c>
+      <c r="I13" s="6">
+        <v>22372.651999999998</v>
+      </c>
+      <c r="J13" s="6">
+        <v>17679.48</v>
+      </c>
+      <c r="K13" s="6">
+        <v>19074.657999999999</v>
+      </c>
+      <c r="L13" s="6">
+        <v>16097.308000000001</v>
+      </c>
+      <c r="M13" s="6">
+        <v>19199.655999999999</v>
+      </c>
+      <c r="N13" s="6">
+        <v>14050.776</v>
+      </c>
+      <c r="O13" s="6">
+        <v>10755.462</v>
+      </c>
+      <c r="P13" s="6">
+        <v>12360.868</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>12868.800999999999</v>
+      </c>
+      <c r="R13" s="6">
+        <v>19109.831999999999</v>
+      </c>
+      <c r="S13" s="6">
+        <v>21307.01</v>
+      </c>
+      <c r="T13" s="6">
+        <v>17024.635999999999</v>
+      </c>
+      <c r="U13" s="6">
+        <v>19754.849999999999</v>
+      </c>
+      <c r="V13" s="6">
+        <v>16952.594000000001</v>
+      </c>
+      <c r="W13" s="6">
+        <v>18464.977999999999</v>
+      </c>
+      <c r="X13" s="6">
+        <v>17569.583999999999</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>18005.754000000001</v>
+      </c>
+      <c r="Z13" s="2">
         <v>16212</v>
       </c>
-      <c r="C13" s="2">
+      <c r="AA13" s="2">
         <v>13462</v>
       </c>
-      <c r="D13" s="2">
+      <c r="AB13" s="2">
         <v>16928</v>
       </c>
-      <c r="E13" s="2">
+      <c r="AC13" s="2">
         <v>17054</v>
       </c>
-      <c r="F13" s="2">
+      <c r="AD13" s="2">
         <v>16974</v>
       </c>
-      <c r="G13" s="2">
+      <c r="AE13" s="2">
         <v>8173</v>
       </c>
-      <c r="H13" s="2">
+      <c r="AF13" s="2">
         <v>13317</v>
       </c>
-      <c r="I13" s="2">
+      <c r="AG13" s="2">
         <v>16956</v>
       </c>
-      <c r="J13" s="2">
+      <c r="AH13" s="2">
         <v>31887</v>
       </c>
-      <c r="K13" s="2">
+      <c r="AI13" s="2">
         <v>24661</v>
       </c>
-      <c r="L13" s="2">
+      <c r="AJ13" s="2">
         <v>23561</v>
       </c>
-      <c r="M13" s="2">
+      <c r="AK13" s="2">
         <v>19868</v>
       </c>
-      <c r="N13" s="2">
+      <c r="AL13" s="2">
         <v>17698</v>
       </c>
-      <c r="O13" s="2">
+      <c r="AM13" s="2">
         <v>17416</v>
       </c>
-      <c r="P13" s="2">
+      <c r="AN13" s="2">
         <v>19169</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="AO13" s="2">
         <v>17164</v>
       </c>
-      <c r="R13" s="2">
+      <c r="AP13" s="2">
         <v>15384</v>
       </c>
-      <c r="S13" s="2">
+      <c r="AQ13" s="2">
         <v>19984</v>
       </c>
-      <c r="T13" s="2">
+      <c r="AR13" s="2">
         <v>14333</v>
       </c>
-      <c r="U13" s="2">
+      <c r="AS13" s="2">
         <v>16115</v>
       </c>
-      <c r="V13" s="2">
+      <c r="AT13" s="2">
         <v>13644</v>
       </c>
-      <c r="W13" s="2">
+      <c r="AU13" s="2">
         <v>15675</v>
       </c>
-      <c r="X13" s="2">
+      <c r="AV13" s="2">
         <v>18597</v>
       </c>
-      <c r="Y13" s="2">
+      <c r="AW13" s="2">
         <v>21676</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="AX13" s="2">
         <v>12709</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>-6</v>
-      </c>
-      <c r="C14">
-        <v>-2</v>
-      </c>
-      <c r="D14">
-        <v>-5</v>
-      </c>
-      <c r="E14">
+      <c r="B14" s="6">
+        <v>-6.31</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.09</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-9.8000000000000007</v>
+      </c>
+      <c r="F14" s="6">
+        <v>-4.91</v>
+      </c>
+      <c r="G14" s="6">
+        <v>-6.67</v>
+      </c>
+      <c r="H14" s="6">
+        <v>-8.33</v>
+      </c>
+      <c r="I14" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="J14" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="K14" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="L14" s="6">
         <v>0</v>
       </c>
-      <c r="F14">
-        <v>-14</v>
-      </c>
-      <c r="G14">
-        <v>-9</v>
-      </c>
-      <c r="H14">
-        <v>-6</v>
-      </c>
-      <c r="I14">
-        <v>-10</v>
-      </c>
-      <c r="J14">
-        <v>-5</v>
-      </c>
-      <c r="K14">
-        <v>-9</v>
-      </c>
-      <c r="L14">
-        <v>-4</v>
-      </c>
-      <c r="M14">
+      <c r="M14" s="6">
+        <v>-5.88</v>
+      </c>
+      <c r="N14" s="6">
         <v>0</v>
       </c>
-      <c r="N14">
-        <v>-15</v>
-      </c>
-      <c r="O14">
-        <v>-8</v>
-      </c>
-      <c r="P14">
-        <v>-15</v>
-      </c>
-      <c r="Q14">
-        <v>-5</v>
-      </c>
-      <c r="R14">
-        <v>-3</v>
-      </c>
-      <c r="S14">
+      <c r="O14" s="6">
+        <v>-3.59</v>
+      </c>
+      <c r="P14" s="6">
+        <v>-6.14</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="R14" s="6">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="S14" s="6">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>-16</v>
-      </c>
-      <c r="U14">
-        <v>-2</v>
-      </c>
-      <c r="V14">
-        <v>-8</v>
-      </c>
-      <c r="W14">
-        <v>-5</v>
-      </c>
-      <c r="X14">
-        <v>-10</v>
-      </c>
-      <c r="Y14">
-        <v>-3</v>
+      <c r="T14" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="U14" s="6">
+        <v>-2.5299999999999998</v>
+      </c>
+      <c r="V14" s="6">
+        <v>0</v>
+      </c>
+      <c r="W14" s="6">
+        <v>-5.87</v>
+      </c>
+      <c r="X14" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>-0.62</v>
       </c>
       <c r="Z14">
         <v>-6</v>
       </c>
+      <c r="AA14">
+        <v>-2</v>
+      </c>
+      <c r="AB14">
+        <v>-5</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>-14</v>
+      </c>
+      <c r="AE14">
+        <v>-9</v>
+      </c>
+      <c r="AF14">
+        <v>-6</v>
+      </c>
+      <c r="AG14">
+        <v>-10</v>
+      </c>
+      <c r="AH14">
+        <v>-5</v>
+      </c>
+      <c r="AI14">
+        <v>-9</v>
+      </c>
+      <c r="AJ14">
+        <v>-4</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>-15</v>
+      </c>
+      <c r="AM14">
+        <v>-8</v>
+      </c>
+      <c r="AN14">
+        <v>-15</v>
+      </c>
+      <c r="AO14">
+        <v>-5</v>
+      </c>
+      <c r="AP14">
+        <v>-3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>-16</v>
+      </c>
+      <c r="AS14">
+        <v>-2</v>
+      </c>
+      <c r="AT14">
+        <v>-8</v>
+      </c>
+      <c r="AU14">
+        <v>-5</v>
+      </c>
+      <c r="AV14">
+        <v>-10</v>
+      </c>
+      <c r="AW14">
+        <v>-3</v>
+      </c>
+      <c r="AX14">
+        <v>-6</v>
+      </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="6">
+        <v>119458.133</v>
+      </c>
+      <c r="C15" s="6">
+        <v>134793.63500000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>127028.935</v>
+      </c>
+      <c r="E15" s="6">
+        <v>105852.962</v>
+      </c>
+      <c r="F15" s="6">
+        <v>93438.894</v>
+      </c>
+      <c r="G15" s="6">
+        <v>97273.351999999999</v>
+      </c>
+      <c r="H15" s="6">
+        <v>115167.53200000001</v>
+      </c>
+      <c r="I15" s="6">
+        <v>99934.335000000006</v>
+      </c>
+      <c r="J15" s="6">
+        <v>85215.048999999999</v>
+      </c>
+      <c r="K15" s="6">
+        <v>95036.88</v>
+      </c>
+      <c r="L15" s="6">
+        <v>105922.749</v>
+      </c>
+      <c r="M15" s="6">
+        <v>137851.141</v>
+      </c>
+      <c r="N15" s="6">
+        <v>129485.007</v>
+      </c>
+      <c r="O15" s="6">
+        <v>116372.51</v>
+      </c>
+      <c r="P15" s="6">
+        <v>130370.391</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>138201.99799999999</v>
+      </c>
+      <c r="R15" s="6">
+        <v>118691.65700000001</v>
+      </c>
+      <c r="S15" s="6">
+        <v>116980.636</v>
+      </c>
+      <c r="T15" s="6">
+        <v>112633.768</v>
+      </c>
+      <c r="U15" s="6">
+        <v>104221.04399999999</v>
+      </c>
+      <c r="V15" s="6">
+        <v>126262.288</v>
+      </c>
+      <c r="W15" s="6">
+        <v>113708.56</v>
+      </c>
+      <c r="X15" s="6">
+        <v>117212.803</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>112340.493</v>
+      </c>
+      <c r="Z15" s="2">
         <v>121696</v>
       </c>
-      <c r="C15" s="2">
+      <c r="AA15" s="2">
         <v>116525</v>
       </c>
-      <c r="D15" s="2">
+      <c r="AB15" s="2">
         <v>128048</v>
       </c>
-      <c r="E15" s="2">
+      <c r="AC15" s="2">
         <v>130158</v>
       </c>
-      <c r="F15" s="2">
+      <c r="AD15" s="2">
         <v>141968</v>
       </c>
-      <c r="G15" s="2">
+      <c r="AE15" s="2">
         <v>131610</v>
       </c>
-      <c r="H15" s="2">
+      <c r="AF15" s="2">
         <v>141444</v>
       </c>
-      <c r="I15" s="2">
+      <c r="AG15" s="2">
         <v>138183</v>
       </c>
-      <c r="J15" s="2">
+      <c r="AH15" s="2">
         <v>159948</v>
       </c>
-      <c r="K15" s="2">
+      <c r="AI15" s="2">
         <v>146657</v>
       </c>
-      <c r="L15" s="2">
+      <c r="AJ15" s="2">
         <v>141788</v>
       </c>
-      <c r="M15" s="2">
+      <c r="AK15" s="2">
         <v>155350</v>
       </c>
-      <c r="N15" s="2">
+      <c r="AL15" s="2">
         <v>164860</v>
       </c>
-      <c r="O15" s="2">
+      <c r="AM15" s="2">
         <v>143364</v>
       </c>
-      <c r="P15" s="2">
+      <c r="AN15" s="2">
         <v>144844</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="AO15" s="2">
         <v>156509</v>
       </c>
-      <c r="R15" s="2">
+      <c r="AP15" s="2">
         <v>163843</v>
       </c>
-      <c r="S15" s="2">
+      <c r="AQ15" s="2">
         <v>131847</v>
       </c>
-      <c r="T15" s="2">
+      <c r="AR15" s="2">
         <v>152612</v>
       </c>
-      <c r="U15" s="2">
+      <c r="AS15" s="2">
         <v>151607</v>
       </c>
-      <c r="V15" s="2">
+      <c r="AT15" s="2">
         <v>165998</v>
       </c>
-      <c r="W15" s="2">
+      <c r="AU15" s="2">
         <v>153023</v>
       </c>
-      <c r="X15" s="2">
+      <c r="AV15" s="2">
         <v>155178</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="AW15" s="2">
         <v>165732</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="AX15" s="2">
         <v>166101</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="6">
+        <v>76386.971999999994</v>
+      </c>
+      <c r="C16" s="6">
+        <v>69578.107999999993</v>
+      </c>
+      <c r="D16" s="6">
+        <v>80355.756999999998</v>
+      </c>
+      <c r="E16" s="6">
+        <v>75948.793999999994</v>
+      </c>
+      <c r="F16" s="6">
+        <v>81297.705000000002</v>
+      </c>
+      <c r="G16" s="6">
+        <v>76555.587</v>
+      </c>
+      <c r="H16" s="6">
+        <v>73790.240999999995</v>
+      </c>
+      <c r="I16" s="6">
+        <v>92653.794999999998</v>
+      </c>
+      <c r="J16" s="6">
+        <v>99751.967999999993</v>
+      </c>
+      <c r="K16" s="6">
+        <v>75242.5</v>
+      </c>
+      <c r="L16" s="6">
+        <v>66787.94</v>
+      </c>
+      <c r="M16" s="6">
+        <v>76387.245999999999</v>
+      </c>
+      <c r="N16" s="6">
+        <v>78765.587</v>
+      </c>
+      <c r="O16" s="6">
+        <v>75885.849000000002</v>
+      </c>
+      <c r="P16" s="6">
+        <v>78065.148000000001</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>81871.869000000006</v>
+      </c>
+      <c r="R16" s="6">
+        <v>86467.18</v>
+      </c>
+      <c r="S16" s="6">
+        <v>73973.784</v>
+      </c>
+      <c r="T16" s="6">
+        <v>82230.073000000004</v>
+      </c>
+      <c r="U16" s="6">
+        <v>70708.222999999998</v>
+      </c>
+      <c r="V16" s="6">
+        <v>63579.245999999999</v>
+      </c>
+      <c r="W16" s="6">
+        <v>65565.164000000004</v>
+      </c>
+      <c r="X16" s="6">
+        <v>85867.784</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>78613.668000000005</v>
+      </c>
+      <c r="Z16" s="2">
         <v>69655</v>
       </c>
-      <c r="C16" s="2">
+      <c r="AA16" s="2">
         <v>82255</v>
       </c>
-      <c r="D16" s="2">
+      <c r="AB16" s="2">
         <v>104155</v>
       </c>
-      <c r="E16" s="2">
+      <c r="AC16" s="2">
         <v>81236</v>
       </c>
-      <c r="F16" s="2">
+      <c r="AD16" s="2">
         <v>81697</v>
       </c>
-      <c r="G16" s="2">
+      <c r="AE16" s="2">
         <v>93168</v>
       </c>
-      <c r="H16" s="2">
+      <c r="AF16" s="2">
         <v>93425</v>
       </c>
-      <c r="I16" s="2">
+      <c r="AG16" s="2">
         <v>85344</v>
       </c>
-      <c r="J16" s="2">
+      <c r="AH16" s="2">
         <v>82216</v>
       </c>
-      <c r="K16" s="2">
+      <c r="AI16" s="2">
         <v>89833</v>
       </c>
-      <c r="L16" s="2">
+      <c r="AJ16" s="2">
         <v>73995</v>
       </c>
-      <c r="M16" s="2">
+      <c r="AK16" s="2">
         <v>85867</v>
       </c>
-      <c r="N16" s="2">
+      <c r="AL16" s="2">
         <v>88880</v>
       </c>
-      <c r="O16" s="2">
+      <c r="AM16" s="2">
         <v>85772</v>
       </c>
-      <c r="P16" s="2">
+      <c r="AN16" s="2">
         <v>78756</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="AO16" s="2">
         <v>100551</v>
       </c>
-      <c r="R16" s="2">
+      <c r="AP16" s="2">
         <v>88815</v>
       </c>
-      <c r="S16" s="2">
+      <c r="AQ16" s="2">
         <v>88868</v>
       </c>
-      <c r="T16" s="2">
+      <c r="AR16" s="2">
         <v>103916</v>
       </c>
-      <c r="U16" s="2">
+      <c r="AS16" s="2">
         <v>93104</v>
       </c>
-      <c r="V16" s="2">
+      <c r="AT16" s="2">
         <v>92374</v>
       </c>
-      <c r="W16" s="2">
+      <c r="AU16" s="2">
         <v>98338</v>
       </c>
-      <c r="X16" s="2">
+      <c r="AV16" s="2">
         <v>87377</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="AW16" s="2">
         <v>96139</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="AX16" s="2">
         <v>85374</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="6">
+        <v>20397.07</v>
+      </c>
+      <c r="C17" s="6">
+        <v>24075.805</v>
+      </c>
+      <c r="D17" s="6">
+        <v>28429.772000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <v>29084.743999999999</v>
+      </c>
+      <c r="F17" s="6">
+        <v>21846.352999999999</v>
+      </c>
+      <c r="G17" s="6">
+        <v>26132.014999999999</v>
+      </c>
+      <c r="H17" s="6">
+        <v>24164.951000000001</v>
+      </c>
+      <c r="I17" s="6">
+        <v>29924.023000000001</v>
+      </c>
+      <c r="J17" s="6">
+        <v>25206.064999999999</v>
+      </c>
+      <c r="K17" s="6">
+        <v>43432.133999999998</v>
+      </c>
+      <c r="L17" s="6">
+        <v>45638.879000000001</v>
+      </c>
+      <c r="M17" s="6">
+        <v>40009.281000000003</v>
+      </c>
+      <c r="N17" s="6">
+        <v>28165.17</v>
+      </c>
+      <c r="O17" s="6">
+        <v>41290.338000000003</v>
+      </c>
+      <c r="P17" s="6">
+        <v>27631.031999999999</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>32980.381000000001</v>
+      </c>
+      <c r="R17" s="6">
+        <v>23814.399000000001</v>
+      </c>
+      <c r="S17" s="6">
+        <v>22386.98</v>
+      </c>
+      <c r="T17" s="6">
+        <v>21270.148000000001</v>
+      </c>
+      <c r="U17" s="6">
+        <v>36585.411</v>
+      </c>
+      <c r="V17" s="6">
+        <v>33150.184999999998</v>
+      </c>
+      <c r="W17" s="6">
+        <v>28244.445</v>
+      </c>
+      <c r="X17" s="6">
+        <v>19193.493999999999</v>
+      </c>
+      <c r="Y17" s="6">
+        <v>18430.645</v>
+      </c>
+      <c r="Z17" s="2">
         <v>28374</v>
       </c>
-      <c r="C17" s="2">
+      <c r="AA17" s="2">
         <v>35915</v>
       </c>
-      <c r="D17" s="2">
+      <c r="AB17" s="2">
         <v>38553</v>
       </c>
-      <c r="E17" s="2">
+      <c r="AC17" s="2">
         <v>36619</v>
       </c>
-      <c r="F17" s="2">
+      <c r="AD17" s="2">
         <v>19316</v>
       </c>
-      <c r="G17" s="2">
+      <c r="AE17" s="2">
         <v>15153</v>
       </c>
-      <c r="H17" s="2">
+      <c r="AF17" s="2">
         <v>21623</v>
       </c>
-      <c r="I17" s="2">
+      <c r="AG17" s="2">
         <v>32029</v>
       </c>
-      <c r="J17" s="2">
+      <c r="AH17" s="2">
         <v>22011</v>
       </c>
-      <c r="K17" s="2">
+      <c r="AI17" s="2">
         <v>24210</v>
       </c>
-      <c r="L17" s="2">
+      <c r="AJ17" s="2">
         <v>25213</v>
       </c>
-      <c r="M17" s="2">
+      <c r="AK17" s="2">
         <v>24711</v>
       </c>
-      <c r="N17" s="2">
+      <c r="AL17" s="2">
         <v>34970</v>
       </c>
-      <c r="O17" s="2">
+      <c r="AM17" s="2">
         <v>37220</v>
       </c>
-      <c r="P17" s="2">
+      <c r="AN17" s="2">
         <v>38511</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="AO17" s="2">
         <v>41492</v>
       </c>
-      <c r="R17" s="2">
+      <c r="AP17" s="2">
         <v>48567</v>
       </c>
-      <c r="S17" s="2">
+      <c r="AQ17" s="2">
         <v>43061</v>
       </c>
-      <c r="T17" s="2">
+      <c r="AR17" s="2">
         <v>40816</v>
       </c>
-      <c r="U17" s="2">
+      <c r="AS17" s="2">
         <v>41718</v>
       </c>
-      <c r="V17" s="2">
+      <c r="AT17" s="2">
         <v>39828</v>
       </c>
-      <c r="W17" s="2">
+      <c r="AU17" s="2">
         <v>38976</v>
       </c>
-      <c r="X17" s="2">
+      <c r="AV17" s="2">
         <v>38218</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="AW17" s="2">
         <v>43668</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="AX17" s="2">
         <v>42977</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="6">
+        <v>25938.77</v>
+      </c>
+      <c r="C18" s="6">
+        <v>23762.047999999999</v>
+      </c>
+      <c r="D18" s="6">
+        <v>32510.81</v>
+      </c>
+      <c r="E18" s="6">
+        <v>33626.6</v>
+      </c>
+      <c r="F18" s="6">
+        <v>28958.338</v>
+      </c>
+      <c r="G18" s="6">
+        <v>28953.42</v>
+      </c>
+      <c r="H18" s="6">
+        <v>30468.07</v>
+      </c>
+      <c r="I18" s="6">
+        <v>31307.18</v>
+      </c>
+      <c r="J18" s="6">
+        <v>27973.280999999999</v>
+      </c>
+      <c r="K18" s="6">
+        <v>29648.024000000001</v>
+      </c>
+      <c r="L18" s="6">
+        <v>29748.171999999999</v>
+      </c>
+      <c r="M18" s="6">
+        <v>30802.673999999999</v>
+      </c>
+      <c r="N18" s="6">
+        <v>30707.530999999999</v>
+      </c>
+      <c r="O18" s="6">
+        <v>33378.686000000002</v>
+      </c>
+      <c r="P18" s="6">
+        <v>33032.114000000001</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>25359.583999999999</v>
+      </c>
+      <c r="R18" s="6">
+        <v>30907.954000000002</v>
+      </c>
+      <c r="S18" s="6">
+        <v>36605.421000000002</v>
+      </c>
+      <c r="T18" s="6">
+        <v>32089.853999999999</v>
+      </c>
+      <c r="U18" s="6">
+        <v>29419.81</v>
+      </c>
+      <c r="V18" s="6">
+        <v>36950.904000000002</v>
+      </c>
+      <c r="W18" s="6">
+        <v>34036.716</v>
+      </c>
+      <c r="X18" s="6">
+        <v>37297.525999999998</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>34329.81</v>
+      </c>
+      <c r="Z18" s="2">
         <v>41290</v>
       </c>
-      <c r="C18" s="2">
+      <c r="AA18" s="2">
         <v>45742</v>
       </c>
-      <c r="D18" s="2">
+      <c r="AB18" s="2">
         <v>39736</v>
       </c>
-      <c r="E18" s="2">
+      <c r="AC18" s="2">
         <v>32105</v>
       </c>
-      <c r="F18" s="2">
+      <c r="AD18" s="2">
         <v>35671</v>
       </c>
-      <c r="G18" s="2">
+      <c r="AE18" s="2">
         <v>39228</v>
       </c>
-      <c r="H18" s="2">
+      <c r="AF18" s="2">
         <v>42458</v>
       </c>
-      <c r="I18" s="2">
+      <c r="AG18" s="2">
         <v>39084</v>
       </c>
-      <c r="J18" s="2">
+      <c r="AH18" s="2">
         <v>45833</v>
       </c>
-      <c r="K18" s="2">
+      <c r="AI18" s="2">
         <v>36208</v>
       </c>
-      <c r="L18" s="2">
+      <c r="AJ18" s="2">
         <v>31634</v>
       </c>
-      <c r="M18" s="2">
+      <c r="AK18" s="2">
         <v>37966</v>
       </c>
-      <c r="N18" s="2">
+      <c r="AL18" s="2">
         <v>37337</v>
       </c>
-      <c r="O18" s="2">
+      <c r="AM18" s="2">
         <v>39888</v>
       </c>
-      <c r="P18" s="2">
+      <c r="AN18" s="2">
         <v>36152</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="AO18" s="2">
         <v>40246</v>
       </c>
-      <c r="R18" s="2">
+      <c r="AP18" s="2">
         <v>33940</v>
       </c>
-      <c r="S18" s="2">
+      <c r="AQ18" s="2">
         <v>29128</v>
       </c>
-      <c r="T18" s="2">
+      <c r="AR18" s="2">
         <v>38975</v>
       </c>
-      <c r="U18" s="2">
+      <c r="AS18" s="2">
         <v>36509</v>
       </c>
-      <c r="V18" s="2">
+      <c r="AT18" s="2">
         <v>35230</v>
       </c>
-      <c r="W18" s="2">
+      <c r="AU18" s="2">
         <v>34546</v>
       </c>
-      <c r="X18" s="2">
+      <c r="AV18" s="2">
         <v>31190</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="AW18" s="2">
         <v>28714</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="AX18" s="2">
         <v>27398</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="6">
+        <v>78135.524000000005</v>
+      </c>
+      <c r="C19" s="6">
+        <v>87393.941999999995</v>
+      </c>
+      <c r="D19" s="6">
+        <v>94462.75</v>
+      </c>
+      <c r="E19" s="6">
+        <v>90842.884999999995</v>
+      </c>
+      <c r="F19" s="6">
+        <v>78081.630999999994</v>
+      </c>
+      <c r="G19" s="6">
+        <v>87786.880000000005</v>
+      </c>
+      <c r="H19" s="6">
+        <v>93205.907999999996</v>
+      </c>
+      <c r="I19" s="6">
+        <v>76128.932000000001</v>
+      </c>
+      <c r="J19" s="6">
+        <v>73428.495999999999</v>
+      </c>
+      <c r="K19" s="6">
+        <v>64758.62</v>
+      </c>
+      <c r="L19" s="6">
+        <v>68768.474000000002</v>
+      </c>
+      <c r="M19" s="6">
+        <v>92462.76</v>
+      </c>
+      <c r="N19" s="6">
+        <v>66090.66</v>
+      </c>
+      <c r="O19" s="6">
+        <v>77068.755999999994</v>
+      </c>
+      <c r="P19" s="6">
+        <v>87295.648000000001</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>79174.043999999994</v>
+      </c>
+      <c r="R19" s="6">
+        <v>73938.600999999995</v>
+      </c>
+      <c r="S19" s="6">
+        <v>69084.035000000003</v>
+      </c>
+      <c r="T19" s="6">
+        <v>57422.567999999999</v>
+      </c>
+      <c r="U19" s="6">
+        <v>73339.804000000004</v>
+      </c>
+      <c r="V19" s="6">
+        <v>71257.838000000003</v>
+      </c>
+      <c r="W19" s="6">
+        <v>73661.63</v>
+      </c>
+      <c r="X19" s="6">
+        <v>72956.676000000007</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>74265.368000000002</v>
+      </c>
+      <c r="Z19" s="2">
         <v>85802</v>
       </c>
-      <c r="C19" s="2">
+      <c r="AA19" s="2">
         <v>81192</v>
       </c>
-      <c r="D19" s="2">
+      <c r="AB19" s="2">
         <v>74770</v>
       </c>
-      <c r="E19" s="2">
+      <c r="AC19" s="2">
         <v>80630</v>
       </c>
-      <c r="F19" s="2">
+      <c r="AD19" s="2">
         <v>95237</v>
       </c>
-      <c r="G19" s="2">
+      <c r="AE19" s="2">
         <v>84864</v>
       </c>
-      <c r="H19" s="2">
+      <c r="AF19" s="2">
         <v>85326</v>
       </c>
-      <c r="I19" s="2">
+      <c r="AG19" s="2">
         <v>75899</v>
       </c>
-      <c r="J19" s="2">
+      <c r="AH19" s="2">
         <v>83650</v>
       </c>
-      <c r="K19" s="2">
+      <c r="AI19" s="2">
         <v>78697</v>
       </c>
-      <c r="L19" s="2">
+      <c r="AJ19" s="2">
         <v>64224</v>
       </c>
-      <c r="M19" s="2">
+      <c r="AK19" s="2">
         <v>80353</v>
       </c>
-      <c r="N19" s="2">
+      <c r="AL19" s="2">
         <v>85392</v>
       </c>
-      <c r="O19" s="2">
+      <c r="AM19" s="2">
         <v>103120</v>
       </c>
-      <c r="P19" s="2">
+      <c r="AN19" s="2">
         <v>101589</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="AO19" s="2">
         <v>98672</v>
       </c>
-      <c r="R19" s="2">
+      <c r="AP19" s="2">
         <v>80317</v>
       </c>
-      <c r="S19" s="2">
+      <c r="AQ19" s="2">
         <v>68806</v>
       </c>
-      <c r="T19" s="2">
+      <c r="AR19" s="2">
         <v>89926</v>
       </c>
-      <c r="U19" s="2">
+      <c r="AS19" s="2">
         <v>76103</v>
       </c>
-      <c r="V19" s="2">
+      <c r="AT19" s="2">
         <v>85759</v>
       </c>
-      <c r="W19" s="2">
+      <c r="AU19" s="2">
         <v>100520</v>
       </c>
-      <c r="X19" s="2">
+      <c r="AV19" s="2">
         <v>84944</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="AW19" s="2">
         <v>76967</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="AX19" s="2">
         <v>85695</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="6">
+        <v>11258.286</v>
+      </c>
+      <c r="C20" s="6">
+        <v>14568.286</v>
+      </c>
+      <c r="D20" s="6">
+        <v>13791.18</v>
+      </c>
+      <c r="E20" s="6">
+        <v>10506.082</v>
+      </c>
+      <c r="F20" s="6">
+        <v>9425.0059999999994</v>
+      </c>
+      <c r="G20" s="6">
+        <v>14792.291999999999</v>
+      </c>
+      <c r="H20" s="6">
+        <v>14697.94</v>
+      </c>
+      <c r="I20" s="6">
+        <v>9874.51</v>
+      </c>
+      <c r="J20" s="6">
+        <v>9389.4040000000005</v>
+      </c>
+      <c r="K20" s="6">
+        <v>9216.8850000000002</v>
+      </c>
+      <c r="L20" s="6">
+        <v>16463.982</v>
+      </c>
+      <c r="M20" s="6">
+        <v>12491.72</v>
+      </c>
+      <c r="N20" s="6">
+        <v>11729.79</v>
+      </c>
+      <c r="O20" s="6">
+        <v>15217.09</v>
+      </c>
+      <c r="P20" s="6">
+        <v>24899.664000000001</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>23255.74</v>
+      </c>
+      <c r="R20" s="6">
+        <v>22320.460999999999</v>
+      </c>
+      <c r="S20" s="6">
+        <v>21072.61</v>
+      </c>
+      <c r="T20" s="6">
+        <v>29400.536</v>
+      </c>
+      <c r="U20" s="6">
+        <v>22462.312000000002</v>
+      </c>
+      <c r="V20" s="6">
+        <v>28491.574000000001</v>
+      </c>
+      <c r="W20" s="6">
+        <v>16676.298999999999</v>
+      </c>
+      <c r="X20" s="6">
+        <v>23871.225999999999</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>10458.357</v>
+      </c>
+      <c r="Z20" s="2">
         <v>12070</v>
       </c>
-      <c r="C20" s="2">
+      <c r="AA20" s="2">
         <v>16018</v>
       </c>
-      <c r="D20" s="2">
+      <c r="AB20" s="2">
         <v>17967</v>
       </c>
-      <c r="E20" s="2">
+      <c r="AC20" s="2">
         <v>15922</v>
       </c>
-      <c r="F20" s="2">
+      <c r="AD20" s="2">
         <v>12663</v>
       </c>
-      <c r="G20" s="2">
+      <c r="AE20" s="2">
         <v>16116</v>
       </c>
-      <c r="H20" s="2">
+      <c r="AF20" s="2">
         <v>20845</v>
       </c>
-      <c r="I20" s="2">
+      <c r="AG20" s="2">
         <v>22852</v>
       </c>
-      <c r="J20" s="2">
+      <c r="AH20" s="2">
         <v>25411</v>
       </c>
-      <c r="K20" s="2">
+      <c r="AI20" s="2">
         <v>20584</v>
       </c>
-      <c r="L20" s="2">
+      <c r="AJ20" s="2">
         <v>23770</v>
       </c>
-      <c r="M20" s="2">
+      <c r="AK20" s="2">
         <v>22524</v>
       </c>
-      <c r="N20" s="2">
+      <c r="AL20" s="2">
         <v>23511</v>
       </c>
-      <c r="O20" s="2">
+      <c r="AM20" s="2">
         <v>23719</v>
       </c>
-      <c r="P20" s="2">
+      <c r="AN20" s="2">
         <v>14196</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="AO20" s="2">
         <v>26908</v>
       </c>
-      <c r="R20" s="2">
+      <c r="AP20" s="2">
         <v>24473</v>
       </c>
-      <c r="S20" s="2">
+      <c r="AQ20" s="2">
         <v>25154</v>
       </c>
-      <c r="T20" s="2">
+      <c r="AR20" s="2">
         <v>18809</v>
       </c>
-      <c r="U20" s="2">
+      <c r="AS20" s="2">
         <v>17306</v>
       </c>
-      <c r="V20" s="2">
+      <c r="AT20" s="2">
         <v>18084</v>
       </c>
-      <c r="W20" s="2">
+      <c r="AU20" s="2">
         <v>16572</v>
       </c>
-      <c r="X20" s="2">
+      <c r="AV20" s="2">
         <v>23937</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="AW20" s="2">
         <v>28012</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="AX20" s="2">
         <v>28004</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="6">
+        <v>89611.258000000002</v>
+      </c>
+      <c r="C21" s="6">
+        <v>74680.672000000006</v>
+      </c>
+      <c r="D21" s="6">
+        <v>81055.558000000005</v>
+      </c>
+      <c r="E21" s="6">
+        <v>100164.25599999999</v>
+      </c>
+      <c r="F21" s="6">
+        <v>98487.08</v>
+      </c>
+      <c r="G21" s="6">
+        <v>87829.38</v>
+      </c>
+      <c r="H21" s="6">
+        <v>95571.229000000007</v>
+      </c>
+      <c r="I21" s="6">
+        <v>82079.046000000002</v>
+      </c>
+      <c r="J21" s="6">
+        <v>86613.381999999998</v>
+      </c>
+      <c r="K21" s="6">
+        <v>81749.865000000005</v>
+      </c>
+      <c r="L21" s="6">
+        <v>71378.486000000004</v>
+      </c>
+      <c r="M21" s="6">
+        <v>83836.712</v>
+      </c>
+      <c r="N21" s="6">
+        <v>82370.191999999995</v>
+      </c>
+      <c r="O21" s="6">
+        <v>88718.680999999997</v>
+      </c>
+      <c r="P21" s="6">
+        <v>92913.760999999999</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>82854.42</v>
+      </c>
+      <c r="R21" s="6">
+        <v>89447.796000000002</v>
+      </c>
+      <c r="S21" s="6">
+        <v>82317.877999999997</v>
+      </c>
+      <c r="T21" s="6">
+        <v>90958.38</v>
+      </c>
+      <c r="U21" s="6">
+        <v>88332.601999999999</v>
+      </c>
+      <c r="V21" s="6">
+        <v>90517.995999999999</v>
+      </c>
+      <c r="W21" s="6">
+        <v>96074.51</v>
+      </c>
+      <c r="X21" s="6">
+        <v>81732.884999999995</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>83911.035999999993</v>
+      </c>
+      <c r="Z21" s="2">
         <v>85745</v>
       </c>
-      <c r="C21" s="2">
+      <c r="AA21" s="2">
         <v>80702</v>
       </c>
-      <c r="D21" s="2">
+      <c r="AB21" s="2">
         <v>100159</v>
       </c>
-      <c r="E21" s="2">
+      <c r="AC21" s="2">
         <v>85180</v>
       </c>
-      <c r="F21" s="2">
+      <c r="AD21" s="2">
         <v>108741</v>
       </c>
-      <c r="G21" s="2">
+      <c r="AE21" s="2">
         <v>97070</v>
       </c>
-      <c r="H21" s="2">
+      <c r="AF21" s="2">
         <v>101598</v>
       </c>
-      <c r="I21" s="2">
+      <c r="AG21" s="2">
         <v>97367</v>
       </c>
-      <c r="J21" s="2">
+      <c r="AH21" s="2">
         <v>103577</v>
       </c>
-      <c r="K21" s="2">
+      <c r="AI21" s="2">
         <v>90182</v>
       </c>
-      <c r="L21" s="2">
+      <c r="AJ21" s="2">
         <v>83101</v>
       </c>
-      <c r="M21" s="2">
+      <c r="AK21" s="2">
         <v>83659</v>
       </c>
-      <c r="N21" s="2">
+      <c r="AL21" s="2">
         <v>92646</v>
       </c>
-      <c r="O21" s="2">
+      <c r="AM21" s="2">
         <v>96974</v>
       </c>
-      <c r="P21" s="2">
+      <c r="AN21" s="2">
         <v>91957</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="AO21" s="2">
         <v>97785</v>
       </c>
-      <c r="R21" s="2">
+      <c r="AP21" s="2">
         <v>100092</v>
       </c>
-      <c r="S21" s="2">
+      <c r="AQ21" s="2">
         <v>100556</v>
       </c>
-      <c r="T21" s="2">
+      <c r="AR21" s="2">
         <v>114289</v>
       </c>
-      <c r="U21" s="2">
+      <c r="AS21" s="2">
         <v>97480</v>
       </c>
-      <c r="V21" s="2">
+      <c r="AT21" s="2">
         <v>100098</v>
       </c>
-      <c r="W21" s="2">
+      <c r="AU21" s="2">
         <v>99532</v>
       </c>
-      <c r="X21" s="2">
+      <c r="AV21" s="2">
         <v>77672</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="AW21" s="2">
         <v>88343</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="AX21" s="2">
         <v>102666</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="6">
+        <v>13934.380999999999</v>
+      </c>
+      <c r="C22" s="6">
+        <v>13358.27</v>
+      </c>
+      <c r="D22" s="6">
+        <v>16501.55</v>
+      </c>
+      <c r="E22" s="6">
+        <v>28415.05</v>
+      </c>
+      <c r="F22" s="6">
+        <v>23810.294000000002</v>
+      </c>
+      <c r="G22" s="6">
+        <v>26273.975999999999</v>
+      </c>
+      <c r="H22" s="6">
+        <v>25043.280999999999</v>
+      </c>
+      <c r="I22" s="6">
+        <v>26585.705999999998</v>
+      </c>
+      <c r="J22" s="6">
+        <v>22699.276000000002</v>
+      </c>
+      <c r="K22" s="6">
+        <v>25897.059000000001</v>
+      </c>
+      <c r="L22" s="6">
+        <v>24061.052</v>
+      </c>
+      <c r="M22" s="6">
+        <v>25542.751</v>
+      </c>
+      <c r="N22" s="6">
+        <v>28862.65</v>
+      </c>
+      <c r="O22" s="6">
+        <v>37111.199999999997</v>
+      </c>
+      <c r="P22" s="6">
+        <v>44249.625999999997</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>41557.178</v>
+      </c>
+      <c r="R22" s="6">
+        <v>30002.175999999999</v>
+      </c>
+      <c r="S22" s="6">
+        <v>27424.593000000001</v>
+      </c>
+      <c r="T22" s="6">
+        <v>31403.553</v>
+      </c>
+      <c r="U22" s="6">
+        <v>28206.52</v>
+      </c>
+      <c r="V22" s="6">
+        <v>34402.58</v>
+      </c>
+      <c r="W22" s="6">
+        <v>26645.521000000001</v>
+      </c>
+      <c r="X22" s="6">
+        <v>25197.344000000001</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>34383.947</v>
+      </c>
+      <c r="Z22" s="2">
         <v>38523</v>
       </c>
-      <c r="C22" s="2">
+      <c r="AA22" s="2">
         <v>29519</v>
       </c>
-      <c r="D22" s="2">
+      <c r="AB22" s="2">
         <v>36693</v>
       </c>
-      <c r="E22" s="2">
+      <c r="AC22" s="2">
         <v>43472</v>
       </c>
-      <c r="F22" s="2">
+      <c r="AD22" s="2">
         <v>41675</v>
       </c>
-      <c r="G22" s="2">
+      <c r="AE22" s="2">
         <v>44676</v>
       </c>
-      <c r="H22" s="2">
+      <c r="AF22" s="2">
         <v>50734</v>
       </c>
-      <c r="I22" s="2">
+      <c r="AG22" s="2">
         <v>40608</v>
       </c>
-      <c r="J22" s="2">
+      <c r="AH22" s="2">
         <v>41156</v>
       </c>
-      <c r="K22" s="2">
+      <c r="AI22" s="2">
         <v>37920</v>
       </c>
-      <c r="L22" s="2">
+      <c r="AJ22" s="2">
         <v>36234</v>
       </c>
-      <c r="M22" s="2">
+      <c r="AK22" s="2">
         <v>35474</v>
       </c>
-      <c r="N22" s="2">
+      <c r="AL22" s="2">
         <v>39554</v>
       </c>
-      <c r="O22" s="2">
+      <c r="AM22" s="2">
         <v>40058</v>
       </c>
-      <c r="P22" s="2">
+      <c r="AN22" s="2">
         <v>37765</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="AO22" s="2">
         <v>38278</v>
       </c>
-      <c r="R22" s="2">
+      <c r="AP22" s="2">
         <v>35493</v>
       </c>
-      <c r="S22" s="2">
+      <c r="AQ22" s="2">
         <v>37568</v>
       </c>
-      <c r="T22" s="2">
+      <c r="AR22" s="2">
         <v>44681</v>
       </c>
-      <c r="U22" s="2">
+      <c r="AS22" s="2">
         <v>41802</v>
       </c>
-      <c r="V22" s="2">
+      <c r="AT22" s="2">
         <v>36111</v>
       </c>
-      <c r="W22" s="2">
+      <c r="AU22" s="2">
         <v>40927</v>
       </c>
-      <c r="X22" s="2">
+      <c r="AV22" s="2">
         <v>28395</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="AW22" s="2">
         <v>34333</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AX22" s="2">
         <v>36768</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="6">
+        <v>89838.009000000005</v>
+      </c>
+      <c r="C23" s="6">
+        <v>78678.84</v>
+      </c>
+      <c r="D23" s="6">
+        <v>71094.464000000007</v>
+      </c>
+      <c r="E23" s="6">
+        <v>86901.959000000003</v>
+      </c>
+      <c r="F23" s="6">
+        <v>140599.128</v>
+      </c>
+      <c r="G23" s="6">
+        <v>97446.126000000004</v>
+      </c>
+      <c r="H23" s="6">
+        <v>82900.873000000007</v>
+      </c>
+      <c r="I23" s="6">
+        <v>76942.557000000001</v>
+      </c>
+      <c r="J23" s="6">
+        <v>92851.930999999997</v>
+      </c>
+      <c r="K23" s="6">
+        <v>101219.694</v>
+      </c>
+      <c r="L23" s="6">
+        <v>94508.301000000007</v>
+      </c>
+      <c r="M23" s="6">
+        <v>89559.873999999996</v>
+      </c>
+      <c r="N23" s="6">
+        <v>76600.656000000003</v>
+      </c>
+      <c r="O23" s="6">
+        <v>82725.17</v>
+      </c>
+      <c r="P23" s="6">
+        <v>81934.108999999997</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>82971.149999999994</v>
+      </c>
+      <c r="R23" s="6">
+        <v>105299.13</v>
+      </c>
+      <c r="S23" s="6">
+        <v>106887.50900000001</v>
+      </c>
+      <c r="T23" s="6">
+        <v>97993.744000000006</v>
+      </c>
+      <c r="U23" s="6">
+        <v>78349.778999999995</v>
+      </c>
+      <c r="V23" s="6">
+        <v>82657.744999999995</v>
+      </c>
+      <c r="W23" s="6">
+        <v>78426.717999999993</v>
+      </c>
+      <c r="X23" s="6">
+        <v>82291.005999999994</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>90597.569000000003</v>
+      </c>
+      <c r="Z23" s="2">
         <v>71026</v>
       </c>
-      <c r="C23" s="2">
+      <c r="AA23" s="2">
         <v>67822</v>
       </c>
-      <c r="D23" s="2">
+      <c r="AB23" s="2">
         <v>62373</v>
       </c>
-      <c r="E23" s="2">
+      <c r="AC23" s="2">
         <v>69043</v>
       </c>
-      <c r="F23" s="2">
+      <c r="AD23" s="2">
         <v>85006</v>
       </c>
-      <c r="G23" s="2">
+      <c r="AE23" s="2">
         <v>94086</v>
       </c>
-      <c r="H23" s="2">
+      <c r="AF23" s="2">
         <v>91449</v>
       </c>
-      <c r="I23" s="2">
+      <c r="AG23" s="2">
         <v>75801</v>
       </c>
-      <c r="J23" s="2">
+      <c r="AH23" s="2">
         <v>103200</v>
       </c>
-      <c r="K23" s="2">
+      <c r="AI23" s="2">
         <v>101038</v>
       </c>
-      <c r="L23" s="2">
+      <c r="AJ23" s="2">
         <v>72924</v>
       </c>
-      <c r="M23" s="2">
+      <c r="AK23" s="2">
         <v>90508</v>
       </c>
-      <c r="N23" s="2">
+      <c r="AL23" s="2">
         <v>81472</v>
       </c>
-      <c r="O23" s="2">
+      <c r="AM23" s="2">
         <v>85426</v>
       </c>
-      <c r="P23" s="2">
+      <c r="AN23" s="2">
         <v>71061</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="AO23" s="2">
         <v>70361</v>
       </c>
-      <c r="R23" s="2">
+      <c r="AP23" s="2">
         <v>90736</v>
       </c>
-      <c r="S23" s="2">
+      <c r="AQ23" s="2">
         <v>95193</v>
       </c>
-      <c r="T23" s="2">
+      <c r="AR23" s="2">
         <v>107313</v>
       </c>
-      <c r="U23" s="2">
+      <c r="AS23" s="2">
         <v>96490</v>
       </c>
-      <c r="V23" s="2">
+      <c r="AT23" s="2">
         <v>84141</v>
       </c>
-      <c r="W23" s="2">
+      <c r="AU23" s="2">
         <v>94094</v>
       </c>
-      <c r="X23" s="2">
+      <c r="AV23" s="2">
         <v>87365</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="AW23" s="2">
         <v>93270</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="AX23" s="2">
         <v>68203</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="6">
+        <v>23532.400000000001</v>
+      </c>
+      <c r="C24" s="6">
+        <v>26557.631000000001</v>
+      </c>
+      <c r="D24" s="6">
+        <v>27104.502</v>
+      </c>
+      <c r="E24" s="6">
+        <v>28640.598999999998</v>
+      </c>
+      <c r="F24" s="6">
+        <v>24240.628000000001</v>
+      </c>
+      <c r="G24" s="6">
+        <v>27845.079000000002</v>
+      </c>
+      <c r="H24" s="6">
+        <v>27729.121999999999</v>
+      </c>
+      <c r="I24" s="6">
+        <v>26119.522000000001</v>
+      </c>
+      <c r="J24" s="6">
+        <v>23507.781999999999</v>
+      </c>
+      <c r="K24" s="6">
+        <v>16216.951999999999</v>
+      </c>
+      <c r="L24" s="6">
+        <v>6142.2659999999996</v>
+      </c>
+      <c r="M24" s="6">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
+        <v>-12.14</v>
+      </c>
+      <c r="O24" s="6">
+        <v>-23.46</v>
+      </c>
+      <c r="P24" s="6">
+        <v>-53.52</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-141.83000000000001</v>
+      </c>
+      <c r="R24" s="6">
+        <v>-0.7</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-34.25</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-26.77</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-5.09</v>
+      </c>
+      <c r="V24" s="6">
+        <v>-10.11</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-10.23</v>
+      </c>
+      <c r="X24" s="6">
+        <v>-2.7</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>-12.37</v>
+      </c>
+      <c r="Z24">
         <v>-10</v>
       </c>
-      <c r="C24">
+      <c r="AA24">
         <v>-27</v>
       </c>
-      <c r="D24">
+      <c r="AB24">
         <v>-31</v>
       </c>
-      <c r="E24">
+      <c r="AC24">
         <v>-27</v>
       </c>
-      <c r="F24">
+      <c r="AD24">
         <v>-35</v>
       </c>
-      <c r="G24">
+      <c r="AE24">
         <v>-20</v>
       </c>
-      <c r="H24">
+      <c r="AF24">
         <v>-13</v>
       </c>
-      <c r="I24">
+      <c r="AG24">
         <v>-37</v>
       </c>
-      <c r="J24">
+      <c r="AH24">
         <v>-16</v>
       </c>
-      <c r="K24">
+      <c r="AI24">
         <v>-41</v>
       </c>
-      <c r="L24">
+      <c r="AJ24">
         <v>-55</v>
       </c>
-      <c r="M24">
+      <c r="AK24">
         <v>-38</v>
       </c>
-      <c r="N24">
+      <c r="AL24">
         <v>-92</v>
       </c>
-      <c r="O24">
+      <c r="AM24">
         <v>-51</v>
       </c>
-      <c r="P24">
+      <c r="AN24">
         <v>-105</v>
       </c>
-      <c r="Q24">
+      <c r="AO24">
         <v>-57</v>
       </c>
-      <c r="R24">
+      <c r="AP24">
         <v>-71</v>
       </c>
-      <c r="S24">
+      <c r="AQ24">
         <v>-41</v>
       </c>
-      <c r="T24">
+      <c r="AR24">
         <v>-31</v>
       </c>
-      <c r="U24">
+      <c r="AS24">
         <v>-33</v>
       </c>
-      <c r="V24">
+      <c r="AT24">
         <v>-109</v>
       </c>
-      <c r="W24">
+      <c r="AU24">
         <v>-29</v>
       </c>
-      <c r="X24">
+      <c r="AV24">
         <v>-23</v>
       </c>
-      <c r="Y24">
+      <c r="AW24">
         <v>-35</v>
       </c>
-      <c r="Z24">
+      <c r="AX24">
         <v>-18</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="6">
+        <v>27790.050999999999</v>
+      </c>
+      <c r="C25" s="6">
+        <v>26887.261999999999</v>
+      </c>
+      <c r="D25" s="6">
+        <v>28659.041000000001</v>
+      </c>
+      <c r="E25" s="6">
+        <v>23955.903999999999</v>
+      </c>
+      <c r="F25" s="6">
+        <v>28003.567999999999</v>
+      </c>
+      <c r="G25" s="6">
+        <v>30617.576000000001</v>
+      </c>
+      <c r="H25" s="6">
+        <v>30460.757000000001</v>
+      </c>
+      <c r="I25" s="6">
+        <v>30723.09</v>
+      </c>
+      <c r="J25" s="6">
+        <v>34539.06</v>
+      </c>
+      <c r="K25" s="6">
+        <v>24173.815999999999</v>
+      </c>
+      <c r="L25" s="6">
+        <v>29081.942999999999</v>
+      </c>
+      <c r="M25" s="6">
+        <v>37987.815000000002</v>
+      </c>
+      <c r="N25" s="6">
+        <v>31779.253000000001</v>
+      </c>
+      <c r="O25" s="6">
+        <v>30073.402999999998</v>
+      </c>
+      <c r="P25" s="6">
+        <v>40855.099000000002</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>39404.677000000003</v>
+      </c>
+      <c r="R25" s="6">
+        <v>31735.062999999998</v>
+      </c>
+      <c r="S25" s="6">
+        <v>36793.353999999999</v>
+      </c>
+      <c r="T25" s="6">
+        <v>25565.684000000001</v>
+      </c>
+      <c r="U25" s="6">
+        <v>27877.873</v>
+      </c>
+      <c r="V25" s="6">
+        <v>36385.116999999998</v>
+      </c>
+      <c r="W25" s="6">
+        <v>35778.902000000002</v>
+      </c>
+      <c r="X25" s="6">
+        <v>35136.552000000003</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>40191.779000000002</v>
+      </c>
+      <c r="Z25" s="2">
         <v>37688</v>
       </c>
-      <c r="C25" s="2">
+      <c r="AA25" s="2">
         <v>40172</v>
       </c>
-      <c r="D25" s="2">
+      <c r="AB25" s="2">
         <v>25180</v>
       </c>
-      <c r="E25" s="2">
+      <c r="AC25" s="2">
         <v>34617</v>
       </c>
-      <c r="F25" s="2">
+      <c r="AD25" s="2">
         <v>39174</v>
       </c>
-      <c r="G25" s="2">
+      <c r="AE25" s="2">
         <v>35522</v>
       </c>
-      <c r="H25" s="2">
+      <c r="AF25" s="2">
         <v>34190</v>
       </c>
-      <c r="I25" s="2">
+      <c r="AG25" s="2">
         <v>38914</v>
       </c>
-      <c r="J25" s="2">
+      <c r="AH25" s="2">
         <v>36571</v>
       </c>
-      <c r="K25" s="2">
+      <c r="AI25" s="2">
         <v>27555</v>
       </c>
-      <c r="L25" s="2">
+      <c r="AJ25" s="2">
         <v>24026</v>
       </c>
-      <c r="M25" s="2">
+      <c r="AK25" s="2">
         <v>27807</v>
       </c>
-      <c r="N25" s="2">
+      <c r="AL25" s="2">
         <v>28902</v>
       </c>
-      <c r="O25" s="2">
+      <c r="AM25" s="2">
         <v>27282</v>
       </c>
-      <c r="P25" s="2">
+      <c r="AN25" s="2">
         <v>30178</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="AO25" s="2">
         <v>33929</v>
       </c>
-      <c r="R25" s="2">
+      <c r="AP25" s="2">
         <v>33971</v>
       </c>
-      <c r="S25" s="2">
+      <c r="AQ25" s="2">
         <v>38989</v>
       </c>
-      <c r="T25" s="2">
+      <c r="AR25" s="2">
         <v>44440</v>
       </c>
-      <c r="U25" s="2">
+      <c r="AS25" s="2">
         <v>31725</v>
       </c>
-      <c r="V25" s="2">
+      <c r="AT25" s="2">
         <v>41840</v>
       </c>
-      <c r="W25" s="2">
+      <c r="AU25" s="2">
         <v>34149</v>
       </c>
-      <c r="X25" s="2">
+      <c r="AV25" s="2">
         <v>34589</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="AW25" s="2">
         <v>41561</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="AX25" s="2">
         <v>39540</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="6">
+        <v>27221.257000000001</v>
+      </c>
+      <c r="C26" s="6">
+        <v>33645.807000000001</v>
+      </c>
+      <c r="D26" s="6">
+        <v>35720.07</v>
+      </c>
+      <c r="E26" s="6">
+        <v>32727.164000000001</v>
+      </c>
+      <c r="F26" s="6">
+        <v>33552.400999999998</v>
+      </c>
+      <c r="G26" s="6">
+        <v>33065.279000000002</v>
+      </c>
+      <c r="H26" s="6">
+        <v>31179.752</v>
+      </c>
+      <c r="I26" s="6">
+        <v>20250.683000000001</v>
+      </c>
+      <c r="J26" s="6">
+        <v>22183.874</v>
+      </c>
+      <c r="K26" s="6">
+        <v>33361.212</v>
+      </c>
+      <c r="L26" s="6">
+        <v>30431.260999999999</v>
+      </c>
+      <c r="M26" s="6">
+        <v>31099.656999999999</v>
+      </c>
+      <c r="N26" s="6">
+        <v>26536.844000000001</v>
+      </c>
+      <c r="O26" s="6">
+        <v>30963.401999999998</v>
+      </c>
+      <c r="P26" s="6">
+        <v>33698.896999999997</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>38294.351999999999</v>
+      </c>
+      <c r="R26" s="6">
+        <v>34872.228000000003</v>
+      </c>
+      <c r="S26" s="6">
+        <v>22714.222000000002</v>
+      </c>
+      <c r="T26" s="6">
+        <v>28140.212</v>
+      </c>
+      <c r="U26" s="6">
+        <v>33828.815999999999</v>
+      </c>
+      <c r="V26" s="6">
+        <v>31625.853999999999</v>
+      </c>
+      <c r="W26" s="6">
+        <v>37233.332999999999</v>
+      </c>
+      <c r="X26" s="6">
+        <v>34531.262000000002</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>25306.357</v>
+      </c>
+      <c r="Z26" s="2">
         <v>39017</v>
       </c>
-      <c r="C26" s="2">
+      <c r="AA26" s="2">
         <v>45886</v>
       </c>
-      <c r="D26" s="2">
+      <c r="AB26" s="2">
         <v>38616</v>
       </c>
-      <c r="E26" s="2">
+      <c r="AC26" s="2">
         <v>29145</v>
       </c>
-      <c r="F26" s="2">
+      <c r="AD26" s="2">
         <v>39798</v>
       </c>
-      <c r="G26" s="2">
+      <c r="AE26" s="2">
         <v>40827</v>
       </c>
-      <c r="H26" s="2">
+      <c r="AF26" s="2">
         <v>36814</v>
       </c>
-      <c r="I26" s="2">
+      <c r="AG26" s="2">
         <v>40099</v>
       </c>
-      <c r="J26" s="2">
+      <c r="AH26" s="2">
         <v>32243</v>
       </c>
-      <c r="K26" s="2">
+      <c r="AI26" s="2">
         <v>42475</v>
       </c>
-      <c r="L26" s="2">
+      <c r="AJ26" s="2">
         <v>47463</v>
       </c>
-      <c r="M26" s="2">
+      <c r="AK26" s="2">
         <v>42503</v>
       </c>
-      <c r="N26" s="2">
+      <c r="AL26" s="2">
         <v>30968</v>
       </c>
-      <c r="O26" s="2">
+      <c r="AM26" s="2">
         <v>28554</v>
       </c>
-      <c r="P26" s="2">
+      <c r="AN26" s="2">
         <v>33545</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="AO26" s="2">
         <v>22907</v>
       </c>
-      <c r="R26" s="2">
+      <c r="AP26" s="2">
         <v>32869</v>
       </c>
-      <c r="S26" s="2">
+      <c r="AQ26" s="2">
         <v>27079</v>
       </c>
-      <c r="T26" s="2">
+      <c r="AR26" s="2">
         <v>24553</v>
       </c>
-      <c r="U26" s="2">
+      <c r="AS26" s="2">
         <v>26240</v>
       </c>
-      <c r="V26" s="2">
+      <c r="AT26" s="2">
         <v>33285</v>
       </c>
-      <c r="W26" s="2">
+      <c r="AU26" s="2">
         <v>36451</v>
       </c>
-      <c r="X26" s="2">
+      <c r="AV26" s="2">
         <v>32678</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="AW26" s="2">
         <v>34950</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="AX26" s="2">
         <v>35764</v>
       </c>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.5">
+      <c r="B28" s="5"/>
+      <c r="P28" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBBDDF7-35B4-B648-A340-E1779CE946D4}">
-  <dimension ref="A1:Z26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <dimension ref="A1:AX28"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="2" max="7" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="3">
+        <v>44652</v>
+      </c>
+      <c r="C1" s="3">
+        <v>44682</v>
+      </c>
+      <c r="D1" s="3">
+        <v>44713</v>
+      </c>
+      <c r="E1" s="3">
+        <v>44743</v>
+      </c>
+      <c r="F1" s="3">
+        <v>44774</v>
+      </c>
+      <c r="G1" s="3">
+        <v>44805</v>
+      </c>
+      <c r="H1" s="3">
+        <v>44835</v>
+      </c>
+      <c r="I1" s="3">
+        <v>44866</v>
+      </c>
+      <c r="J1" s="3">
+        <v>44896</v>
+      </c>
+      <c r="K1" s="3">
+        <v>44927</v>
+      </c>
+      <c r="L1" s="3">
+        <v>44958</v>
+      </c>
+      <c r="M1" s="3">
+        <v>44986</v>
+      </c>
+      <c r="N1" s="3">
+        <v>45017</v>
+      </c>
+      <c r="O1" s="3">
+        <v>45047</v>
+      </c>
+      <c r="P1" s="3">
+        <v>45078</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>45108</v>
+      </c>
+      <c r="R1" s="3">
+        <v>45139</v>
+      </c>
+      <c r="S1" s="3">
+        <v>45170</v>
+      </c>
+      <c r="T1" s="3">
+        <v>45200</v>
+      </c>
+      <c r="U1" s="3">
+        <v>45231</v>
+      </c>
+      <c r="V1" s="3">
+        <v>45261</v>
+      </c>
+      <c r="W1" s="3">
+        <v>45292</v>
+      </c>
+      <c r="X1" s="3">
+        <v>45323</v>
+      </c>
+      <c r="Y1" s="3">
+        <v>45352</v>
+      </c>
+      <c r="Z1" s="1">
         <v>45383</v>
       </c>
-      <c r="C1" s="1">
+      <c r="AA1" s="1">
         <v>45413</v>
       </c>
-      <c r="D1" s="1">
+      <c r="AB1" s="1">
         <v>45444</v>
       </c>
-      <c r="E1" s="1">
+      <c r="AC1" s="1">
         <v>45474</v>
       </c>
-      <c r="F1" s="1">
+      <c r="AD1" s="1">
         <v>45505</v>
       </c>
-      <c r="G1" s="1">
+      <c r="AE1" s="1">
         <v>45536</v>
       </c>
-      <c r="H1" s="1">
+      <c r="AF1" s="1">
         <v>45566</v>
       </c>
-      <c r="I1" s="1">
+      <c r="AG1" s="1">
         <v>45597</v>
       </c>
-      <c r="J1" s="1">
+      <c r="AH1" s="1">
         <v>45627</v>
       </c>
-      <c r="K1" s="1">
+      <c r="AI1" s="1">
         <v>45658</v>
       </c>
-      <c r="L1" s="1">
+      <c r="AJ1" s="1">
         <v>45689</v>
       </c>
-      <c r="M1" s="1">
+      <c r="AK1" s="1">
         <v>45717</v>
       </c>
-      <c r="N1" s="1">
+      <c r="AL1" s="1">
         <v>45748</v>
       </c>
-      <c r="O1" s="1">
+      <c r="AM1" s="1">
         <v>45778</v>
       </c>
-      <c r="P1" s="1">
+      <c r="AN1" s="1">
         <v>45809</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="AO1" s="1">
         <v>45839</v>
       </c>
-      <c r="R1" s="1">
+      <c r="AP1" s="1">
         <v>45870</v>
       </c>
-      <c r="S1" s="1">
+      <c r="AQ1" s="1">
         <v>45901</v>
       </c>
-      <c r="T1" s="1">
+      <c r="AR1" s="1">
         <v>45931</v>
       </c>
-      <c r="U1" s="1">
+      <c r="AS1" s="1">
         <v>45962</v>
       </c>
-      <c r="V1" s="1">
+      <c r="AT1" s="1">
         <v>45992</v>
       </c>
-      <c r="W1" s="1">
+      <c r="AU1" s="1">
         <v>46023</v>
       </c>
-      <c r="X1" s="1">
+      <c r="AV1" s="1">
         <v>46054</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="AW1" s="1">
         <v>46082</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="AX1" s="1">
         <v>46113</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
+        <v>4049.0390000000002</v>
+      </c>
+      <c r="C2" s="6">
+        <v>3135.61</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3880.116</v>
+      </c>
+      <c r="E2" s="6">
+        <v>3147.49</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2627.4760000000001</v>
+      </c>
+      <c r="G2" s="6">
+        <v>3687.73</v>
+      </c>
+      <c r="H2" s="6">
+        <v>3053.3</v>
+      </c>
+      <c r="I2" s="6">
+        <v>3117.7939999999999</v>
+      </c>
+      <c r="J2" s="6">
+        <v>3440.4</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2924.74</v>
+      </c>
+      <c r="L2" s="6">
+        <v>3022.65</v>
+      </c>
+      <c r="M2" s="6">
+        <v>3553.9059999999999</v>
+      </c>
+      <c r="N2" s="6">
+        <v>3169.76</v>
+      </c>
+      <c r="O2" s="6">
+        <v>3141.56</v>
+      </c>
+      <c r="P2" s="6">
+        <v>3251.51</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>2602.77</v>
+      </c>
+      <c r="R2" s="6">
+        <v>2489.5100000000002</v>
+      </c>
+      <c r="S2" s="6">
+        <v>3094.14</v>
+      </c>
+      <c r="T2" s="6">
+        <v>3194.14</v>
+      </c>
+      <c r="U2" s="6">
+        <v>2751.57</v>
+      </c>
+      <c r="V2" s="6">
+        <v>2938.4360000000001</v>
+      </c>
+      <c r="W2" s="6">
+        <v>3171.58</v>
+      </c>
+      <c r="X2" s="6">
+        <v>2368.9340000000002</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>3277.11</v>
+      </c>
+      <c r="Z2" s="2">
         <v>2887</v>
       </c>
-      <c r="C2" s="2">
+      <c r="AA2" s="2">
         <v>3307</v>
       </c>
-      <c r="D2" s="2">
+      <c r="AB2" s="2">
         <v>2868</v>
       </c>
-      <c r="E2" s="2">
+      <c r="AC2" s="2">
         <v>2768</v>
       </c>
-      <c r="F2" s="2">
+      <c r="AD2" s="2">
         <v>2777</v>
       </c>
-      <c r="G2" s="2">
+      <c r="AE2" s="2">
         <v>2422</v>
       </c>
-      <c r="H2" s="2">
+      <c r="AF2" s="2">
         <v>2736</v>
       </c>
-      <c r="I2" s="2">
+      <c r="AG2" s="2">
         <v>2951</v>
       </c>
-      <c r="J2" s="2">
+      <c r="AH2" s="2">
         <v>3279</v>
       </c>
-      <c r="K2" s="2">
+      <c r="AI2" s="2">
         <v>2370</v>
       </c>
-      <c r="L2" s="2">
+      <c r="AJ2" s="2">
         <v>2732</v>
       </c>
-      <c r="M2" s="2">
+      <c r="AK2" s="2">
         <v>3070</v>
       </c>
-      <c r="N2" s="2">
+      <c r="AL2" s="2">
         <v>2824</v>
       </c>
-      <c r="O2" s="2">
+      <c r="AM2" s="2">
         <v>3166</v>
       </c>
-      <c r="P2" s="2">
+      <c r="AN2" s="2">
         <v>2603</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="AO2" s="2">
         <v>2751</v>
       </c>
-      <c r="R2" s="2">
+      <c r="AP2" s="2">
         <v>2240</v>
       </c>
-      <c r="S2" s="2">
+      <c r="AQ2" s="2">
         <v>2504</v>
       </c>
-      <c r="T2" s="2">
+      <c r="AR2" s="2">
         <v>3030</v>
       </c>
-      <c r="U2" s="2">
+      <c r="AS2" s="2">
         <v>2707</v>
       </c>
-      <c r="V2" s="2">
+      <c r="AT2" s="2">
         <v>2408</v>
       </c>
-      <c r="W2" s="2">
+      <c r="AU2" s="2">
         <v>3051</v>
       </c>
-      <c r="X2" s="2">
+      <c r="AV2" s="2">
         <v>2705</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="AW2" s="2">
         <v>2123</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="AX2" s="2">
         <v>1830</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="6">
+        <v>2813.692</v>
+      </c>
+      <c r="C3" s="6">
+        <v>3074.1419999999998</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3603.9969999999998</v>
+      </c>
+      <c r="E3" s="6">
+        <v>2956.181</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3109.2330000000002</v>
+      </c>
+      <c r="G3" s="6">
+        <v>3356.547</v>
+      </c>
+      <c r="H3" s="6">
+        <v>3168.0120000000002</v>
+      </c>
+      <c r="I3" s="6">
+        <v>3000.1289999999999</v>
+      </c>
+      <c r="J3" s="6">
+        <v>3280.6320000000001</v>
+      </c>
+      <c r="K3" s="6">
+        <v>3278.2849999999999</v>
+      </c>
+      <c r="L3" s="6">
+        <v>3404.3029999999999</v>
+      </c>
+      <c r="M3" s="6">
+        <v>3757.8739999999998</v>
+      </c>
+      <c r="N3" s="6">
+        <v>2423.4409999999998</v>
+      </c>
+      <c r="O3" s="6">
+        <v>2986.8229999999999</v>
+      </c>
+      <c r="P3" s="6">
+        <v>4270.9920000000002</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>2991.44</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3291.453</v>
+      </c>
+      <c r="S3" s="6">
+        <v>3579.038</v>
+      </c>
+      <c r="T3" s="6">
+        <v>3606.922</v>
+      </c>
+      <c r="U3" s="6">
+        <v>2830.893</v>
+      </c>
+      <c r="V3" s="6">
+        <v>3042.5509999999999</v>
+      </c>
+      <c r="W3" s="6">
+        <v>3828.5680000000002</v>
+      </c>
+      <c r="X3" s="6">
+        <v>3710.5430000000001</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>3890.4589999999998</v>
+      </c>
+      <c r="Z3" s="2">
         <v>3144</v>
       </c>
-      <c r="C3" s="2">
+      <c r="AA3" s="2">
         <v>3555</v>
       </c>
-      <c r="D3" s="2">
+      <c r="AB3" s="2">
         <v>3596</v>
       </c>
-      <c r="E3" s="2">
+      <c r="AC3" s="2">
         <v>3069</v>
       </c>
-      <c r="F3" s="2">
+      <c r="AD3" s="2">
         <v>3663</v>
       </c>
-      <c r="G3" s="2">
+      <c r="AE3" s="2">
         <v>2735</v>
       </c>
-      <c r="H3" s="2">
+      <c r="AF3" s="2">
         <v>3559</v>
       </c>
-      <c r="I3" s="2">
+      <c r="AG3" s="2">
         <v>2874</v>
       </c>
-      <c r="J3" s="2">
+      <c r="AH3" s="2">
         <v>3533</v>
       </c>
-      <c r="K3" s="2">
+      <c r="AI3" s="2">
         <v>3852</v>
       </c>
-      <c r="L3" s="2">
+      <c r="AJ3" s="2">
         <v>3005</v>
       </c>
-      <c r="M3" s="2">
+      <c r="AK3" s="2">
         <v>3456</v>
       </c>
-      <c r="N3" s="2">
+      <c r="AL3" s="2">
         <v>3167</v>
       </c>
-      <c r="O3" s="2">
+      <c r="AM3" s="2">
         <v>3791</v>
       </c>
-      <c r="P3" s="2">
+      <c r="AN3" s="2">
         <v>3504</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="AO3" s="2">
         <v>3921</v>
       </c>
-      <c r="R3" s="2">
+      <c r="AP3" s="2">
         <v>3167</v>
       </c>
-      <c r="S3" s="2">
+      <c r="AQ3" s="2">
         <v>3109</v>
       </c>
-      <c r="T3" s="2">
+      <c r="AR3" s="2">
         <v>2563</v>
       </c>
-      <c r="U3" s="2">
+      <c r="AS3" s="2">
         <v>1869</v>
       </c>
-      <c r="V3" s="2">
+      <c r="AT3" s="2">
         <v>3055</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AU3" s="2">
         <v>2632</v>
       </c>
-      <c r="X3" s="2">
+      <c r="AV3" s="2">
         <v>2691</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="AW3" s="2">
         <v>2906</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="AX3" s="2">
         <v>2262</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="6">
+        <v>14839.36</v>
+      </c>
+      <c r="C4" s="6">
+        <v>13532.862999999999</v>
+      </c>
+      <c r="D4" s="6">
+        <v>14498.724</v>
+      </c>
+      <c r="E4" s="6">
+        <v>14811.48</v>
+      </c>
+      <c r="F4" s="6">
+        <v>15872.235000000001</v>
+      </c>
+      <c r="G4" s="6">
+        <v>16590.394</v>
+      </c>
+      <c r="H4" s="6">
+        <v>15291.65</v>
+      </c>
+      <c r="I4" s="6">
+        <v>15431.225</v>
+      </c>
+      <c r="J4" s="6">
+        <v>15701.668</v>
+      </c>
+      <c r="K4" s="6">
+        <v>13382.527</v>
+      </c>
+      <c r="L4" s="6">
+        <v>13211.643</v>
+      </c>
+      <c r="M4" s="6">
+        <v>15197.226000000001</v>
+      </c>
+      <c r="N4" s="6">
+        <v>14336.537</v>
+      </c>
+      <c r="O4" s="6">
+        <v>13414.03</v>
+      </c>
+      <c r="P4" s="6">
+        <v>14173.745999999999</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>13520.78</v>
+      </c>
+      <c r="R4" s="6">
+        <v>12801.312</v>
+      </c>
+      <c r="S4" s="6">
+        <v>11191.31</v>
+      </c>
+      <c r="T4" s="6">
+        <v>15373.862999999999</v>
+      </c>
+      <c r="U4" s="6">
+        <v>14406.797</v>
+      </c>
+      <c r="V4" s="6">
+        <v>14304.528</v>
+      </c>
+      <c r="W4" s="6">
+        <v>12965.04</v>
+      </c>
+      <c r="X4" s="6">
+        <v>11918.031999999999</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>10496.11</v>
+      </c>
+      <c r="Z4" s="2">
         <v>13846</v>
       </c>
-      <c r="C4" s="2">
+      <c r="AA4" s="2">
         <v>12812</v>
       </c>
-      <c r="D4" s="2">
+      <c r="AB4" s="2">
         <v>13530</v>
       </c>
-      <c r="E4" s="2">
+      <c r="AC4" s="2">
         <v>15294</v>
       </c>
-      <c r="F4" s="2">
+      <c r="AD4" s="2">
         <v>17122</v>
       </c>
-      <c r="G4" s="2">
+      <c r="AE4" s="2">
         <v>17619</v>
       </c>
-      <c r="H4" s="2">
+      <c r="AF4" s="2">
         <v>16449</v>
       </c>
-      <c r="I4" s="2">
+      <c r="AG4" s="2">
         <v>17440</v>
       </c>
-      <c r="J4" s="2">
+      <c r="AH4" s="2">
         <v>18089</v>
       </c>
-      <c r="K4" s="2">
+      <c r="AI4" s="2">
         <v>16808</v>
       </c>
-      <c r="L4" s="2">
+      <c r="AJ4" s="2">
         <v>17415</v>
       </c>
-      <c r="M4" s="2">
+      <c r="AK4" s="2">
         <v>16372</v>
       </c>
-      <c r="N4" s="2">
+      <c r="AL4" s="2">
         <v>16400</v>
       </c>
-      <c r="O4" s="2">
+      <c r="AM4" s="2">
         <v>16324</v>
       </c>
-      <c r="P4" s="2">
+      <c r="AN4" s="2">
         <v>18516</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="AO4" s="2">
         <v>16247</v>
       </c>
-      <c r="R4" s="2">
+      <c r="AP4" s="2">
         <v>19018</v>
       </c>
-      <c r="S4" s="2">
+      <c r="AQ4" s="2">
         <v>15406</v>
       </c>
-      <c r="T4" s="2">
+      <c r="AR4" s="2">
         <v>21727</v>
       </c>
-      <c r="U4" s="2">
+      <c r="AS4" s="2">
         <v>19337</v>
       </c>
-      <c r="V4" s="2">
+      <c r="AT4" s="2">
         <v>20920</v>
       </c>
-      <c r="W4" s="2">
+      <c r="AU4" s="2">
         <v>15664</v>
       </c>
-      <c r="X4" s="2">
+      <c r="AV4" s="2">
         <v>18397</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="AW4" s="2">
         <v>20458</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="AX4" s="2">
         <v>18617</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="6">
+        <v>22041.382000000001</v>
+      </c>
+      <c r="C5" s="6">
+        <v>20770.275000000001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>23802.254000000001</v>
+      </c>
+      <c r="E5" s="6">
+        <v>21466.789000000001</v>
+      </c>
+      <c r="F5" s="6">
+        <v>21108.192999999999</v>
+      </c>
+      <c r="G5" s="6">
+        <v>21457.714</v>
+      </c>
+      <c r="H5" s="6">
+        <v>23226.550999999999</v>
+      </c>
+      <c r="I5" s="6">
+        <v>23636.442999999999</v>
+      </c>
+      <c r="J5" s="6">
+        <v>23661.402999999998</v>
+      </c>
+      <c r="K5" s="6">
+        <v>22023.96</v>
+      </c>
+      <c r="L5" s="6">
+        <v>22749.143</v>
+      </c>
+      <c r="M5" s="6">
+        <v>23743.844000000001</v>
+      </c>
+      <c r="N5" s="6">
+        <v>23820.240000000002</v>
+      </c>
+      <c r="O5" s="6">
+        <v>22357.33</v>
+      </c>
+      <c r="P5" s="6">
+        <v>23419.788</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>21186.892</v>
+      </c>
+      <c r="R5" s="6">
+        <v>21751.522000000001</v>
+      </c>
+      <c r="S5" s="6">
+        <v>21581.847000000002</v>
+      </c>
+      <c r="T5" s="6">
+        <v>22213.200000000001</v>
+      </c>
+      <c r="U5" s="6">
+        <v>22220.673999999999</v>
+      </c>
+      <c r="V5" s="6">
+        <v>22687.710999999999</v>
+      </c>
+      <c r="W5" s="6">
+        <v>22456.264999999999</v>
+      </c>
+      <c r="X5" s="6">
+        <v>20882.741999999998</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>22921.355</v>
+      </c>
+      <c r="Z5" s="2">
         <v>24115</v>
       </c>
-      <c r="C5" s="2">
+      <c r="AA5" s="2">
         <v>23555</v>
       </c>
-      <c r="D5" s="2">
+      <c r="AB5" s="2">
         <v>23002</v>
       </c>
-      <c r="E5" s="2">
+      <c r="AC5" s="2">
         <v>23156</v>
       </c>
-      <c r="F5" s="2">
+      <c r="AD5" s="2">
         <v>21561</v>
       </c>
-      <c r="G5" s="2">
+      <c r="AE5" s="2">
         <v>20254</v>
       </c>
-      <c r="H5" s="2">
+      <c r="AF5" s="2">
         <v>23713</v>
       </c>
-      <c r="I5" s="2">
+      <c r="AG5" s="2">
         <v>22334</v>
       </c>
-      <c r="J5" s="2">
+      <c r="AH5" s="2">
         <v>22481</v>
       </c>
-      <c r="K5" s="2">
+      <c r="AI5" s="2">
         <v>21888</v>
       </c>
-      <c r="L5" s="2">
+      <c r="AJ5" s="2">
         <v>20985</v>
       </c>
-      <c r="M5" s="2">
+      <c r="AK5" s="2">
         <v>21291</v>
       </c>
-      <c r="N5" s="2">
+      <c r="AL5" s="2">
         <v>21448</v>
       </c>
-      <c r="O5" s="2">
+      <c r="AM5" s="2">
         <v>21460</v>
       </c>
-      <c r="P5" s="2">
+      <c r="AN5" s="2">
         <v>23276</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="AO5" s="2">
         <v>22738</v>
       </c>
-      <c r="R5" s="2">
+      <c r="AP5" s="2">
         <v>20006</v>
       </c>
-      <c r="S5" s="2">
+      <c r="AQ5" s="2">
         <v>21703</v>
       </c>
-      <c r="T5" s="2">
+      <c r="AR5" s="2">
         <v>23291</v>
       </c>
-      <c r="U5" s="2">
+      <c r="AS5" s="2">
         <v>20533</v>
       </c>
-      <c r="V5" s="2">
+      <c r="AT5" s="2">
         <v>22281</v>
       </c>
-      <c r="W5" s="2">
+      <c r="AU5" s="2">
         <v>22340</v>
       </c>
-      <c r="X5" s="2">
+      <c r="AV5" s="2">
         <v>19678</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="AW5" s="2">
         <v>23100</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="AX5" s="2">
         <v>24948</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="6">
+        <v>6625.5140000000001</v>
+      </c>
+      <c r="C6" s="6">
+        <v>5646.78</v>
+      </c>
+      <c r="D6" s="6">
+        <v>6839.0720000000001</v>
+      </c>
+      <c r="E6" s="6">
+        <v>6618.6019999999999</v>
+      </c>
+      <c r="F6" s="6">
+        <v>5860.4939999999997</v>
+      </c>
+      <c r="G6" s="6">
+        <v>6245.2979999999998</v>
+      </c>
+      <c r="H6" s="6">
+        <v>7256.0919999999996</v>
+      </c>
+      <c r="I6" s="6">
+        <v>6322.78</v>
+      </c>
+      <c r="J6" s="6">
+        <v>5632.9080000000004</v>
+      </c>
+      <c r="K6" s="6">
+        <v>5795.6480000000001</v>
+      </c>
+      <c r="L6" s="6">
+        <v>7351.5450000000001</v>
+      </c>
+      <c r="M6" s="6">
+        <v>6121.1940000000004</v>
+      </c>
+      <c r="N6" s="6">
+        <v>7763.0540000000001</v>
+      </c>
+      <c r="O6" s="6">
+        <v>7583.8909999999996</v>
+      </c>
+      <c r="P6" s="6">
+        <v>8532.5480000000007</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>7891.0940000000001</v>
+      </c>
+      <c r="R6" s="6">
+        <v>7472.3010000000004</v>
+      </c>
+      <c r="S6" s="6">
+        <v>7225.3829999999998</v>
+      </c>
+      <c r="T6" s="6">
+        <v>10260.541999999999</v>
+      </c>
+      <c r="U6" s="6">
+        <v>6766.3580000000002</v>
+      </c>
+      <c r="V6" s="6">
+        <v>8077.9520000000002</v>
+      </c>
+      <c r="W6" s="6">
+        <v>7626.8339999999998</v>
+      </c>
+      <c r="X6" s="6">
+        <v>6422.4769999999999</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>6292.8850000000002</v>
+      </c>
+      <c r="Z6" s="2">
         <v>7144</v>
       </c>
-      <c r="C6" s="2">
+      <c r="AA6" s="2">
         <v>7677</v>
       </c>
-      <c r="D6" s="2">
+      <c r="AB6" s="2">
         <v>7493</v>
       </c>
-      <c r="E6" s="2">
+      <c r="AC6" s="2">
         <v>7495</v>
       </c>
-      <c r="F6" s="2">
+      <c r="AD6" s="2">
         <v>8266</v>
       </c>
-      <c r="G6" s="2">
+      <c r="AE6" s="2">
         <v>7471</v>
       </c>
-      <c r="H6" s="2">
+      <c r="AF6" s="2">
         <v>9570</v>
       </c>
-      <c r="I6" s="2">
+      <c r="AG6" s="2">
         <v>7882</v>
       </c>
-      <c r="J6" s="2">
+      <c r="AH6" s="2">
         <v>9246</v>
       </c>
-      <c r="K6" s="2">
+      <c r="AI6" s="2">
         <v>6676</v>
       </c>
-      <c r="L6" s="2">
+      <c r="AJ6" s="2">
         <v>6929</v>
       </c>
-      <c r="M6" s="2">
+      <c r="AK6" s="2">
         <v>9033</v>
       </c>
-      <c r="N6" s="2">
+      <c r="AL6" s="2">
         <v>9884</v>
       </c>
-      <c r="O6" s="2">
+      <c r="AM6" s="2">
         <v>7074</v>
       </c>
-      <c r="P6" s="2">
+      <c r="AN6" s="2">
         <v>8471</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="AO6" s="2">
         <v>10918</v>
       </c>
-      <c r="R6" s="2">
+      <c r="AP6" s="2">
         <v>7493</v>
       </c>
-      <c r="S6" s="2">
+      <c r="AQ6" s="2">
         <v>10307</v>
       </c>
-      <c r="T6" s="2">
+      <c r="AR6" s="2">
         <v>10085</v>
       </c>
-      <c r="U6" s="2">
+      <c r="AS6" s="2">
         <v>8719</v>
       </c>
-      <c r="V6" s="2">
+      <c r="AT6" s="2">
         <v>7684</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AU6" s="2">
         <v>9054</v>
       </c>
-      <c r="X6" s="2">
+      <c r="AV6" s="2">
         <v>8122</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AW6" s="2">
         <v>7508</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AX6" s="2">
         <v>9225</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="6">
+        <v>6490.91</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6369.2889999999998</v>
+      </c>
+      <c r="D7" s="6">
+        <v>8240.56</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6995.4430000000002</v>
+      </c>
+      <c r="F7" s="6">
+        <v>8054.1130000000003</v>
+      </c>
+      <c r="G7" s="6">
+        <v>7214.2190000000001</v>
+      </c>
+      <c r="H7" s="6">
+        <v>7249.7280000000001</v>
+      </c>
+      <c r="I7" s="6">
+        <v>7874.4949999999999</v>
+      </c>
+      <c r="J7" s="6">
+        <v>7139.0320000000002</v>
+      </c>
+      <c r="K7" s="6">
+        <v>7920.56</v>
+      </c>
+      <c r="L7" s="6">
+        <v>7778.9049999999997</v>
+      </c>
+      <c r="M7" s="6">
+        <v>8358.7559999999994</v>
+      </c>
+      <c r="N7" s="6">
+        <v>8011.8440000000001</v>
+      </c>
+      <c r="O7" s="6">
+        <v>7148.0879999999997</v>
+      </c>
+      <c r="P7" s="6">
+        <v>8535.41</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>7681.7860000000001</v>
+      </c>
+      <c r="R7" s="6">
+        <v>8199.2270000000008</v>
+      </c>
+      <c r="S7" s="6">
+        <v>7805.8209999999999</v>
+      </c>
+      <c r="T7" s="6">
+        <v>8457.0820000000003</v>
+      </c>
+      <c r="U7" s="6">
+        <v>7659.4949999999999</v>
+      </c>
+      <c r="V7" s="6">
+        <v>7217.2169999999996</v>
+      </c>
+      <c r="W7" s="6">
+        <v>7960.0370000000003</v>
+      </c>
+      <c r="X7" s="6">
+        <v>8856.2739999999994</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>8244.1919999999991</v>
+      </c>
+      <c r="Z7" s="2">
         <v>7671</v>
       </c>
-      <c r="C7" s="2">
+      <c r="AA7" s="2">
         <v>8404</v>
       </c>
-      <c r="D7" s="2">
+      <c r="AB7" s="2">
         <v>8807</v>
       </c>
-      <c r="E7" s="2">
+      <c r="AC7" s="2">
         <v>10707</v>
       </c>
-      <c r="F7" s="2">
+      <c r="AD7" s="2">
         <v>11494</v>
       </c>
-      <c r="G7" s="2">
+      <c r="AE7" s="2">
         <v>8281</v>
       </c>
-      <c r="H7" s="2">
+      <c r="AF7" s="2">
         <v>9749</v>
       </c>
-      <c r="I7" s="2">
+      <c r="AG7" s="2">
         <v>7726</v>
       </c>
-      <c r="J7" s="2">
+      <c r="AH7" s="2">
         <v>8291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="AI7" s="2">
         <v>7578</v>
       </c>
-      <c r="L7" s="2">
+      <c r="AJ7" s="2">
         <v>7344</v>
       </c>
-      <c r="M7" s="2">
+      <c r="AK7" s="2">
         <v>8044</v>
       </c>
-      <c r="N7" s="2">
+      <c r="AL7" s="2">
         <v>9198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="AM7" s="2">
         <v>9515</v>
       </c>
-      <c r="P7" s="2">
+      <c r="AN7" s="2">
         <v>9539</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="AO7" s="2">
         <v>11266</v>
       </c>
-      <c r="R7" s="2">
+      <c r="AP7" s="2">
         <v>9529</v>
       </c>
-      <c r="S7" s="2">
+      <c r="AQ7" s="2">
         <v>9606</v>
       </c>
-      <c r="T7" s="2">
+      <c r="AR7" s="2">
         <v>10199</v>
       </c>
-      <c r="U7" s="2">
+      <c r="AS7" s="2">
         <v>8249</v>
       </c>
-      <c r="V7" s="2">
+      <c r="AT7" s="2">
         <v>9526</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AU7" s="2">
         <v>8892</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AV7" s="2">
         <v>8667</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AW7" s="2">
         <v>10031</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AX7" s="2">
         <v>8850</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="6">
+        <v>6221.6530000000002</v>
+      </c>
+      <c r="C8" s="6">
+        <v>5869.33</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6938.1469999999999</v>
+      </c>
+      <c r="E8" s="6">
+        <v>6213.3940000000002</v>
+      </c>
+      <c r="F8" s="6">
+        <v>6132.7759999999998</v>
+      </c>
+      <c r="G8" s="6">
+        <v>6743.384</v>
+      </c>
+      <c r="H8" s="6">
+        <v>6599.9279999999999</v>
+      </c>
+      <c r="I8" s="6">
+        <v>6704.5940000000001</v>
+      </c>
+      <c r="J8" s="6">
+        <v>6850.3419999999996</v>
+      </c>
+      <c r="K8" s="6">
+        <v>6927.2749999999996</v>
+      </c>
+      <c r="L8" s="6">
+        <v>6231.2520000000004</v>
+      </c>
+      <c r="M8" s="6">
+        <v>6938.3180000000002</v>
+      </c>
+      <c r="N8" s="6">
+        <v>7029.835</v>
+      </c>
+      <c r="O8" s="6">
+        <v>7451.4759999999997</v>
+      </c>
+      <c r="P8" s="6">
+        <v>7877.9660000000003</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>7698.9610000000002</v>
+      </c>
+      <c r="R8" s="6">
+        <v>7187.6679999999997</v>
+      </c>
+      <c r="S8" s="6">
+        <v>7435.674</v>
+      </c>
+      <c r="T8" s="6">
+        <v>7018.4920000000002</v>
+      </c>
+      <c r="U8" s="6">
+        <v>7601.3040000000001</v>
+      </c>
+      <c r="V8" s="6">
+        <v>7528.7849999999999</v>
+      </c>
+      <c r="W8" s="6">
+        <v>7094.5280000000002</v>
+      </c>
+      <c r="X8" s="6">
+        <v>7465.4409999999998</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>7685.8770000000004</v>
+      </c>
+      <c r="Z8" s="2">
         <v>7741</v>
       </c>
-      <c r="C8" s="2">
+      <c r="AA8" s="2">
         <v>7561</v>
       </c>
-      <c r="D8" s="2">
+      <c r="AB8" s="2">
         <v>7344</v>
       </c>
-      <c r="E8" s="2">
+      <c r="AC8" s="2">
         <v>7953</v>
       </c>
-      <c r="F8" s="2">
+      <c r="AD8" s="2">
         <v>7793</v>
       </c>
-      <c r="G8" s="2">
+      <c r="AE8" s="2">
         <v>7909</v>
       </c>
-      <c r="H8" s="2">
+      <c r="AF8" s="2">
         <v>8641</v>
       </c>
-      <c r="I8" s="2">
+      <c r="AG8" s="2">
         <v>8755</v>
       </c>
-      <c r="J8" s="2">
+      <c r="AH8" s="2">
         <v>8067</v>
       </c>
-      <c r="K8" s="2">
+      <c r="AI8" s="2">
         <v>7426</v>
       </c>
-      <c r="L8" s="2">
+      <c r="AJ8" s="2">
         <v>7597</v>
       </c>
-      <c r="M8" s="2">
+      <c r="AK8" s="2">
         <v>7584</v>
       </c>
-      <c r="N8" s="2">
+      <c r="AL8" s="2">
         <v>8555</v>
       </c>
-      <c r="O8" s="2">
+      <c r="AM8" s="2">
         <v>7416</v>
       </c>
-      <c r="P8" s="2">
+      <c r="AN8" s="2">
         <v>8691</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="AO8" s="2">
         <v>8668</v>
       </c>
-      <c r="R8" s="2">
+      <c r="AP8" s="2">
         <v>8899</v>
       </c>
-      <c r="S8" s="2">
+      <c r="AQ8" s="2">
         <v>8482</v>
       </c>
-      <c r="T8" s="2">
+      <c r="AR8" s="2">
         <v>8711</v>
       </c>
-      <c r="U8" s="2">
+      <c r="AS8" s="2">
         <v>7750</v>
       </c>
-      <c r="V8" s="2">
+      <c r="AT8" s="2">
         <v>8357</v>
       </c>
-      <c r="W8" s="2">
+      <c r="AU8" s="2">
         <v>9000</v>
       </c>
-      <c r="X8" s="2">
+      <c r="AV8" s="2">
         <v>8403</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="AW8" s="2">
         <v>9013</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="AX8" s="2">
         <v>9191</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="6">
+        <v>18483.825000000001</v>
+      </c>
+      <c r="C9" s="6">
+        <v>17893.259999999998</v>
+      </c>
+      <c r="D9" s="6">
+        <v>19784.517</v>
+      </c>
+      <c r="E9" s="6">
+        <v>20315.603999999999</v>
+      </c>
+      <c r="F9" s="6">
+        <v>19480.829000000002</v>
+      </c>
+      <c r="G9" s="6">
+        <v>20658.092000000001</v>
+      </c>
+      <c r="H9" s="6">
+        <v>19128.656999999999</v>
+      </c>
+      <c r="I9" s="6">
+        <v>21155.991999999998</v>
+      </c>
+      <c r="J9" s="6">
+        <v>19594.84</v>
+      </c>
+      <c r="K9" s="6">
+        <v>21774.78</v>
+      </c>
+      <c r="L9" s="6">
+        <v>18380.594000000001</v>
+      </c>
+      <c r="M9" s="6">
+        <v>21210.050999999999</v>
+      </c>
+      <c r="N9" s="6">
+        <v>20268.472000000002</v>
+      </c>
+      <c r="O9" s="6">
+        <v>20129.205000000002</v>
+      </c>
+      <c r="P9" s="6">
+        <v>22054.392</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>21271.46</v>
+      </c>
+      <c r="R9" s="6">
+        <v>20047.092000000001</v>
+      </c>
+      <c r="S9" s="6">
+        <v>18287.388999999999</v>
+      </c>
+      <c r="T9" s="6">
+        <v>23926.224999999999</v>
+      </c>
+      <c r="U9" s="6">
+        <v>23800.827000000001</v>
+      </c>
+      <c r="V9" s="6">
+        <v>21168.564999999999</v>
+      </c>
+      <c r="W9" s="6">
+        <v>20570.017</v>
+      </c>
+      <c r="X9" s="6">
+        <v>20565.919999999998</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>20310.315999999999</v>
+      </c>
+      <c r="Z9" s="2">
         <v>22683</v>
       </c>
-      <c r="C9" s="2">
+      <c r="AA9" s="2">
         <v>22244</v>
       </c>
-      <c r="D9" s="2">
+      <c r="AB9" s="2">
         <v>21589</v>
       </c>
-      <c r="E9" s="2">
+      <c r="AC9" s="2">
         <v>22933</v>
       </c>
-      <c r="F9" s="2">
+      <c r="AD9" s="2">
         <v>21197</v>
       </c>
-      <c r="G9" s="2">
+      <c r="AE9" s="2">
         <v>21548</v>
       </c>
-      <c r="H9" s="2">
+      <c r="AF9" s="2">
         <v>24826</v>
       </c>
-      <c r="I9" s="2">
+      <c r="AG9" s="2">
         <v>23611</v>
       </c>
-      <c r="J9" s="2">
+      <c r="AH9" s="2">
         <v>23726</v>
       </c>
-      <c r="K9" s="2">
+      <c r="AI9" s="2">
         <v>22800</v>
       </c>
-      <c r="L9" s="2">
+      <c r="AJ9" s="2">
         <v>20400</v>
       </c>
-      <c r="M9" s="2">
+      <c r="AK9" s="2">
         <v>23758</v>
       </c>
-      <c r="N9" s="2">
+      <c r="AL9" s="2">
         <v>24717</v>
       </c>
-      <c r="O9" s="2">
+      <c r="AM9" s="2">
         <v>25493</v>
       </c>
-      <c r="P9" s="2">
+      <c r="AN9" s="2">
         <v>25552</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="AO9" s="2">
         <v>24079</v>
       </c>
-      <c r="R9" s="2">
+      <c r="AP9" s="2">
         <v>22525</v>
       </c>
-      <c r="S9" s="2">
+      <c r="AQ9" s="2">
         <v>25175</v>
       </c>
-      <c r="T9" s="2">
+      <c r="AR9" s="2">
         <v>24712</v>
       </c>
-      <c r="U9" s="2">
+      <c r="AS9" s="2">
         <v>21648</v>
       </c>
-      <c r="V9" s="2">
+      <c r="AT9" s="2">
         <v>23814</v>
       </c>
-      <c r="W9" s="2">
+      <c r="AU9" s="2">
         <v>23431</v>
       </c>
-      <c r="X9" s="2">
+      <c r="AV9" s="2">
         <v>20928</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="AW9" s="2">
         <v>27090</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="AX9" s="2">
         <v>25974</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="6">
+        <v>33004.548000000003</v>
+      </c>
+      <c r="C10" s="6">
+        <v>35727.536</v>
+      </c>
+      <c r="D10" s="6">
+        <v>39766.813000000002</v>
+      </c>
+      <c r="E10" s="6">
+        <v>36476.764999999999</v>
+      </c>
+      <c r="F10" s="6">
+        <v>34721.034</v>
+      </c>
+      <c r="G10" s="6">
+        <v>36559.527999999998</v>
+      </c>
+      <c r="H10" s="6">
+        <v>34012.919000000002</v>
+      </c>
+      <c r="I10" s="6">
+        <v>35494.877</v>
+      </c>
+      <c r="J10" s="6">
+        <v>38038.813999999998</v>
+      </c>
+      <c r="K10" s="6">
+        <v>36395.597000000002</v>
+      </c>
+      <c r="L10" s="6">
+        <v>38837.476000000002</v>
+      </c>
+      <c r="M10" s="6">
+        <v>40721.061000000002</v>
+      </c>
+      <c r="N10" s="6">
+        <v>35858.180999999997</v>
+      </c>
+      <c r="O10" s="6">
+        <v>35753.432999999997</v>
+      </c>
+      <c r="P10" s="6">
+        <v>42477.116000000002</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>37764.129000000001</v>
+      </c>
+      <c r="R10" s="6">
+        <v>35219.857000000004</v>
+      </c>
+      <c r="S10" s="6">
+        <v>35180.557000000001</v>
+      </c>
+      <c r="T10" s="6">
+        <v>37143.273000000001</v>
+      </c>
+      <c r="U10" s="6">
+        <v>38698.622000000003</v>
+      </c>
+      <c r="V10" s="6">
+        <v>37563.688999999998</v>
+      </c>
+      <c r="W10" s="6">
+        <v>34755.072999999997</v>
+      </c>
+      <c r="X10" s="6">
+        <v>35146.728999999999</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>37279.932999999997</v>
+      </c>
+      <c r="Z10" s="2">
         <v>35256</v>
       </c>
-      <c r="C10" s="2">
+      <c r="AA10" s="2">
         <v>38480</v>
       </c>
-      <c r="D10" s="2">
+      <c r="AB10" s="2">
         <v>36121</v>
       </c>
-      <c r="E10" s="2">
+      <c r="AC10" s="2">
         <v>40031</v>
       </c>
-      <c r="F10" s="2">
+      <c r="AD10" s="2">
         <v>35546</v>
       </c>
-      <c r="G10" s="2">
+      <c r="AE10" s="2">
         <v>33977</v>
       </c>
-      <c r="H10" s="2">
+      <c r="AF10" s="2">
         <v>38569</v>
       </c>
-      <c r="I10" s="2">
+      <c r="AG10" s="2">
         <v>35121</v>
       </c>
-      <c r="J10" s="2">
+      <c r="AH10" s="2">
         <v>34432</v>
       </c>
-      <c r="K10" s="2">
+      <c r="AI10" s="2">
         <v>34132</v>
       </c>
-      <c r="L10" s="2">
+      <c r="AJ10" s="2">
         <v>38217</v>
       </c>
-      <c r="M10" s="2">
+      <c r="AK10" s="2">
         <v>37129</v>
       </c>
-      <c r="N10" s="2">
+      <c r="AL10" s="2">
         <v>36364</v>
       </c>
-      <c r="O10" s="2">
+      <c r="AM10" s="2">
         <v>36671</v>
       </c>
-      <c r="P10" s="2">
+      <c r="AN10" s="2">
         <v>38880</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="AO10" s="2">
         <v>36523</v>
       </c>
-      <c r="R10" s="2">
+      <c r="AP10" s="2">
         <v>30736</v>
       </c>
-      <c r="S10" s="2">
+      <c r="AQ10" s="2">
         <v>32656</v>
       </c>
-      <c r="T10" s="2">
+      <c r="AR10" s="2">
         <v>35538</v>
       </c>
-      <c r="U10" s="2">
+      <c r="AS10" s="2">
         <v>32719</v>
       </c>
-      <c r="V10" s="2">
+      <c r="AT10" s="2">
         <v>33071</v>
       </c>
-      <c r="W10" s="2">
+      <c r="AU10" s="2">
         <v>34892</v>
       </c>
-      <c r="X10" s="2">
+      <c r="AV10" s="2">
         <v>35342</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="AW10" s="2">
         <v>34632</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="AX10" s="2">
         <v>35864</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="6">
+        <v>17526.982</v>
+      </c>
+      <c r="C11" s="6">
+        <v>17108.827000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>21669.659</v>
+      </c>
+      <c r="E11" s="6">
+        <v>20668.651999999998</v>
+      </c>
+      <c r="F11" s="6">
+        <v>18834.093000000001</v>
+      </c>
+      <c r="G11" s="6">
+        <v>21353.69</v>
+      </c>
+      <c r="H11" s="6">
+        <v>22005.571</v>
+      </c>
+      <c r="I11" s="6">
+        <v>20486.388999999999</v>
+      </c>
+      <c r="J11" s="6">
+        <v>21070.473000000002</v>
+      </c>
+      <c r="K11" s="6">
+        <v>19892.555</v>
+      </c>
+      <c r="L11" s="6">
+        <v>18934.544000000002</v>
+      </c>
+      <c r="M11" s="6">
+        <v>19138.683000000001</v>
+      </c>
+      <c r="N11" s="6">
+        <v>17700.439999999999</v>
+      </c>
+      <c r="O11" s="6">
+        <v>17859.144</v>
+      </c>
+      <c r="P11" s="6">
+        <v>20474.395</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>18736.669999999998</v>
+      </c>
+      <c r="R11" s="6">
+        <v>20209.775000000001</v>
+      </c>
+      <c r="S11" s="6">
+        <v>17457.830999999998</v>
+      </c>
+      <c r="T11" s="6">
+        <v>18621.038</v>
+      </c>
+      <c r="U11" s="6">
+        <v>18581.276000000002</v>
+      </c>
+      <c r="V11" s="6">
+        <v>18989.66</v>
+      </c>
+      <c r="W11" s="6">
+        <v>19286.473999999998</v>
+      </c>
+      <c r="X11" s="6">
+        <v>17877.401000000002</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>16682.61</v>
+      </c>
+      <c r="Z11" s="2">
         <v>19623</v>
       </c>
-      <c r="C11" s="2">
+      <c r="AA11" s="2">
         <v>18261</v>
       </c>
-      <c r="D11" s="2">
+      <c r="AB11" s="2">
         <v>20062</v>
       </c>
-      <c r="E11" s="2">
+      <c r="AC11" s="2">
         <v>20408</v>
       </c>
-      <c r="F11" s="2">
+      <c r="AD11" s="2">
         <v>19255</v>
       </c>
-      <c r="G11" s="2">
+      <c r="AE11" s="2">
         <v>17180</v>
       </c>
-      <c r="H11" s="2">
+      <c r="AF11" s="2">
         <v>20539</v>
       </c>
-      <c r="I11" s="2">
+      <c r="AG11" s="2">
         <v>17285</v>
       </c>
-      <c r="J11" s="2">
+      <c r="AH11" s="2">
         <v>19189</v>
       </c>
-      <c r="K11" s="2">
+      <c r="AI11" s="2">
         <v>18429</v>
       </c>
-      <c r="L11" s="2">
+      <c r="AJ11" s="2">
         <v>16121</v>
       </c>
-      <c r="M11" s="2">
+      <c r="AK11" s="2">
         <v>19812</v>
       </c>
-      <c r="N11" s="2">
+      <c r="AL11" s="2">
         <v>19392</v>
       </c>
-      <c r="O11" s="2">
+      <c r="AM11" s="2">
         <v>16917</v>
       </c>
-      <c r="P11" s="2">
+      <c r="AN11" s="2">
         <v>18324</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="AO11" s="2">
         <v>20035</v>
       </c>
-      <c r="R11" s="2">
+      <c r="AP11" s="2">
         <v>19088</v>
       </c>
-      <c r="S11" s="2">
+      <c r="AQ11" s="2">
         <v>18381</v>
       </c>
-      <c r="T11" s="2">
+      <c r="AR11" s="2">
         <v>17277</v>
       </c>
-      <c r="U11" s="2">
+      <c r="AS11" s="2">
         <v>16552</v>
       </c>
-      <c r="V11" s="2">
+      <c r="AT11" s="2">
         <v>17587</v>
       </c>
-      <c r="W11" s="2">
+      <c r="AU11" s="2">
         <v>18919</v>
       </c>
-      <c r="X11" s="2">
+      <c r="AV11" s="2">
         <v>17126</v>
       </c>
-      <c r="Y11" s="2">
+      <c r="AW11" s="2">
         <v>19351</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="AX11" s="2">
         <v>17514</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="6">
+        <v>14950.757</v>
+      </c>
+      <c r="C12" s="6">
+        <v>13334.091</v>
+      </c>
+      <c r="D12" s="6">
+        <v>14394.648999999999</v>
+      </c>
+      <c r="E12" s="6">
+        <v>18790.998</v>
+      </c>
+      <c r="F12" s="6">
+        <v>16335.471</v>
+      </c>
+      <c r="G12" s="6">
+        <v>14629.76</v>
+      </c>
+      <c r="H12" s="6">
+        <v>11768.084999999999</v>
+      </c>
+      <c r="I12" s="6">
+        <v>13917.507</v>
+      </c>
+      <c r="J12" s="6">
+        <v>20134.493999999999</v>
+      </c>
+      <c r="K12" s="6">
+        <v>16221.661</v>
+      </c>
+      <c r="L12" s="6">
+        <v>10717.623</v>
+      </c>
+      <c r="M12" s="6">
+        <v>12776.504999999999</v>
+      </c>
+      <c r="N12" s="6">
+        <v>11765.81</v>
+      </c>
+      <c r="O12" s="6">
+        <v>11496.849</v>
+      </c>
+      <c r="P12" s="6">
+        <v>13652.156000000001</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>12012.477999999999</v>
+      </c>
+      <c r="R12" s="6">
+        <v>12163.391</v>
+      </c>
+      <c r="S12" s="6">
+        <v>10621.620999999999</v>
+      </c>
+      <c r="T12" s="6">
+        <v>11632.806</v>
+      </c>
+      <c r="U12" s="6">
+        <v>11504.013000000001</v>
+      </c>
+      <c r="V12" s="6">
+        <v>11782.841</v>
+      </c>
+      <c r="W12" s="6">
+        <v>11529.744000000001</v>
+      </c>
+      <c r="X12" s="6">
+        <v>10016.700999999999</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>11197.569</v>
+      </c>
+      <c r="Z12" s="2">
         <v>11663</v>
       </c>
-      <c r="C12" s="2">
+      <c r="AA12" s="2">
         <v>11994</v>
       </c>
-      <c r="D12" s="2">
+      <c r="AB12" s="2">
         <v>10622</v>
       </c>
-      <c r="E12" s="2">
+      <c r="AC12" s="2">
         <v>10887</v>
       </c>
-      <c r="F12" s="2">
+      <c r="AD12" s="2">
         <v>12586</v>
       </c>
-      <c r="G12" s="2">
+      <c r="AE12" s="2">
         <v>11698</v>
       </c>
-      <c r="H12" s="2">
+      <c r="AF12" s="2">
         <v>11348</v>
       </c>
-      <c r="I12" s="2">
+      <c r="AG12" s="2">
         <v>10382</v>
       </c>
-      <c r="J12" s="2">
+      <c r="AH12" s="2">
         <v>10453</v>
       </c>
-      <c r="K12" s="2">
+      <c r="AI12" s="2">
         <v>9585</v>
       </c>
-      <c r="L12" s="2">
+      <c r="AJ12" s="2">
         <v>9332</v>
       </c>
-      <c r="M12" s="2">
+      <c r="AK12" s="2">
         <v>10671</v>
       </c>
-      <c r="N12" s="2">
+      <c r="AL12" s="2">
         <v>11179</v>
       </c>
-      <c r="O12" s="2">
+      <c r="AM12" s="2">
         <v>11775</v>
       </c>
-      <c r="P12" s="2">
+      <c r="AN12" s="2">
         <v>11969</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="AO12" s="2">
         <v>13097</v>
       </c>
-      <c r="R12" s="2">
+      <c r="AP12" s="2">
         <v>10317</v>
       </c>
-      <c r="S12" s="2">
+      <c r="AQ12" s="2">
         <v>11576</v>
       </c>
-      <c r="T12" s="2">
+      <c r="AR12" s="2">
         <v>13059</v>
       </c>
-      <c r="U12" s="2">
+      <c r="AS12" s="2">
         <v>10071</v>
       </c>
-      <c r="V12" s="2">
+      <c r="AT12" s="2">
         <v>10849</v>
       </c>
-      <c r="W12" s="2">
+      <c r="AU12" s="2">
         <v>10479</v>
       </c>
-      <c r="X12" s="2">
+      <c r="AV12" s="2">
         <v>9694</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="AW12" s="2">
         <v>10832</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="AX12" s="2">
         <v>11192</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="6">
+        <v>3623.87</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2763.74</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3488.02</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2860.21</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3044.3760000000002</v>
+      </c>
+      <c r="G13" s="6">
+        <v>3677.04</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3452.72</v>
+      </c>
+      <c r="I13" s="6">
+        <v>3191.98</v>
+      </c>
+      <c r="J13" s="6">
+        <v>3031.01</v>
+      </c>
+      <c r="K13" s="6">
+        <v>2985.2539999999999</v>
+      </c>
+      <c r="L13" s="6">
+        <v>2454.44</v>
+      </c>
+      <c r="M13" s="6">
+        <v>3761.0610000000001</v>
+      </c>
+      <c r="N13" s="6">
+        <v>3321.0219999999999</v>
+      </c>
+      <c r="O13" s="6">
+        <v>3106.56</v>
+      </c>
+      <c r="P13" s="6">
+        <v>3120.192</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2499.797</v>
+      </c>
+      <c r="R13" s="6">
+        <v>2115.8119999999999</v>
+      </c>
+      <c r="S13" s="6">
+        <v>2859.57</v>
+      </c>
+      <c r="T13" s="6">
+        <v>3777.1370000000002</v>
+      </c>
+      <c r="U13" s="6">
+        <v>3419.46</v>
+      </c>
+      <c r="V13" s="6">
+        <v>3866.53</v>
+      </c>
+      <c r="W13" s="6">
+        <v>3501.5070000000001</v>
+      </c>
+      <c r="X13" s="6">
+        <v>3125.2240000000002</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>3499.0250000000001</v>
+      </c>
+      <c r="Z13" s="2">
         <v>3618</v>
       </c>
-      <c r="C13" s="2">
+      <c r="AA13" s="2">
         <v>3292</v>
       </c>
-      <c r="D13" s="2">
+      <c r="AB13" s="2">
         <v>2861</v>
       </c>
-      <c r="E13" s="2">
+      <c r="AC13" s="2">
         <v>2412</v>
       </c>
-      <c r="F13" s="2">
+      <c r="AD13" s="2">
         <v>2431</v>
       </c>
-      <c r="G13" s="2">
+      <c r="AE13" s="2">
         <v>3028</v>
       </c>
-      <c r="H13" s="2">
+      <c r="AF13" s="2">
         <v>2642</v>
       </c>
-      <c r="I13" s="2">
+      <c r="AG13" s="2">
         <v>2811</v>
       </c>
-      <c r="J13" s="2">
+      <c r="AH13" s="2">
         <v>2685</v>
       </c>
-      <c r="K13" s="2">
+      <c r="AI13" s="2">
         <v>2217</v>
       </c>
-      <c r="L13" s="2">
+      <c r="AJ13" s="2">
         <v>3031</v>
       </c>
-      <c r="M13" s="2">
+      <c r="AK13" s="2">
         <v>3134</v>
       </c>
-      <c r="N13" s="2">
+      <c r="AL13" s="2">
         <v>2771</v>
       </c>
-      <c r="O13" s="2">
+      <c r="AM13" s="2">
         <v>2238</v>
       </c>
-      <c r="P13" s="2">
+      <c r="AN13" s="2">
         <v>2932</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="AO13" s="2">
         <v>2105</v>
       </c>
-      <c r="R13" s="2">
+      <c r="AP13" s="2">
         <v>1938</v>
       </c>
-      <c r="S13" s="2">
+      <c r="AQ13" s="2">
         <v>2715</v>
       </c>
-      <c r="T13" s="2">
+      <c r="AR13" s="2">
         <v>2389</v>
       </c>
-      <c r="U13" s="2">
+      <c r="AS13" s="2">
         <v>2020</v>
       </c>
-      <c r="V13" s="2">
+      <c r="AT13" s="2">
         <v>2525</v>
       </c>
-      <c r="W13" s="2">
+      <c r="AU13" s="2">
         <v>2212</v>
       </c>
-      <c r="X13" s="2">
+      <c r="AV13" s="2">
         <v>2153</v>
       </c>
-      <c r="Y13" s="2">
+      <c r="AW13" s="2">
         <v>3389</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="AX13" s="2">
         <v>2286</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="6">
+        <v>37218.25</v>
+      </c>
+      <c r="C14" s="6">
+        <v>34934.15</v>
+      </c>
+      <c r="D14" s="6">
+        <v>37968.6</v>
+      </c>
+      <c r="E14" s="6">
+        <v>39983.910000000003</v>
+      </c>
+      <c r="F14" s="6">
+        <v>42343.23</v>
+      </c>
+      <c r="G14" s="6">
+        <v>45181.661999999997</v>
+      </c>
+      <c r="H14" s="6">
+        <v>40585.15</v>
+      </c>
+      <c r="I14" s="6">
+        <v>39057.51</v>
+      </c>
+      <c r="J14" s="6">
+        <v>42427.98</v>
+      </c>
+      <c r="K14" s="6">
+        <v>37933.199999999997</v>
+      </c>
+      <c r="L14" s="6">
+        <v>36731.56</v>
+      </c>
+      <c r="M14" s="6">
+        <v>42411.38</v>
+      </c>
+      <c r="N14" s="6">
+        <v>36422.53</v>
+      </c>
+      <c r="O14" s="6">
+        <v>42214.216</v>
+      </c>
+      <c r="P14" s="6">
+        <v>47837.29</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>51157.135000000002</v>
+      </c>
+      <c r="R14" s="6">
+        <v>43991.07</v>
+      </c>
+      <c r="S14" s="6">
+        <v>39462.453999999998</v>
+      </c>
+      <c r="T14" s="6">
+        <v>35234.110999999997</v>
+      </c>
+      <c r="U14" s="6">
+        <v>32306.42</v>
+      </c>
+      <c r="V14" s="6">
+        <v>33668.28</v>
+      </c>
+      <c r="W14" s="6">
+        <v>41913.39</v>
+      </c>
+      <c r="X14" s="6">
+        <v>43060.3</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>43074.79</v>
+      </c>
+      <c r="Z14" s="2">
         <v>47073</v>
       </c>
-      <c r="C14" s="2">
+      <c r="AA14" s="2">
         <v>42069</v>
       </c>
-      <c r="D14" s="2">
+      <c r="AB14" s="2">
         <v>45219</v>
       </c>
-      <c r="E14" s="2">
+      <c r="AC14" s="2">
         <v>48039</v>
       </c>
-      <c r="F14" s="2">
+      <c r="AD14" s="2">
         <v>46627</v>
       </c>
-      <c r="G14" s="2">
+      <c r="AE14" s="2">
         <v>39728</v>
       </c>
-      <c r="H14" s="2">
+      <c r="AF14" s="2">
         <v>45824</v>
       </c>
-      <c r="I14" s="2">
+      <c r="AG14" s="2">
         <v>42784</v>
       </c>
-      <c r="J14" s="2">
+      <c r="AH14" s="2">
         <v>42526</v>
       </c>
-      <c r="K14" s="2">
+      <c r="AI14" s="2">
         <v>37097</v>
       </c>
-      <c r="L14" s="2">
+      <c r="AJ14" s="2">
         <v>38587</v>
       </c>
-      <c r="M14" s="2">
+      <c r="AK14" s="2">
         <v>36242</v>
       </c>
-      <c r="N14" s="2">
+      <c r="AL14" s="2">
         <v>45951</v>
       </c>
-      <c r="O14" s="2">
+      <c r="AM14" s="2">
         <v>48111</v>
       </c>
-      <c r="P14" s="2">
+      <c r="AN14" s="2">
         <v>35244</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="AO14" s="2">
         <v>48406</v>
       </c>
-      <c r="R14" s="2">
+      <c r="AP14" s="2">
         <v>41046</v>
       </c>
-      <c r="S14" s="2">
+      <c r="AQ14" s="2">
         <v>39594</v>
       </c>
-      <c r="T14" s="2">
+      <c r="AR14" s="2">
         <v>41521</v>
       </c>
-      <c r="U14" s="2">
+      <c r="AS14" s="2">
         <v>38058</v>
       </c>
-      <c r="V14" s="2">
+      <c r="AT14" s="2">
         <v>41368</v>
       </c>
-      <c r="W14" s="2">
+      <c r="AU14" s="2">
         <v>35319</v>
       </c>
-      <c r="X14" s="2">
+      <c r="AV14" s="2">
         <v>42122</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="AW14" s="2">
         <v>43712</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="AX14" s="2">
         <v>45558</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="6">
+        <v>14704.085999999999</v>
+      </c>
+      <c r="C15" s="6">
+        <v>14314.424999999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>16596.882000000001</v>
+      </c>
+      <c r="E15" s="6">
+        <v>13888.662</v>
+      </c>
+      <c r="F15" s="6">
+        <v>12417.528</v>
+      </c>
+      <c r="G15" s="6">
+        <v>13724.291999999999</v>
+      </c>
+      <c r="H15" s="6">
+        <v>13415.547</v>
+      </c>
+      <c r="I15" s="6">
+        <v>12074.484</v>
+      </c>
+      <c r="J15" s="6">
+        <v>13947.072</v>
+      </c>
+      <c r="K15" s="6">
+        <v>14268.617</v>
+      </c>
+      <c r="L15" s="6">
+        <v>13472.019</v>
+      </c>
+      <c r="M15" s="6">
+        <v>17033.778999999999</v>
+      </c>
+      <c r="N15" s="6">
+        <v>12965.397999999999</v>
+      </c>
+      <c r="O15" s="6">
+        <v>15118.821</v>
+      </c>
+      <c r="P15" s="6">
+        <v>13945.386</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>13733.263000000001</v>
+      </c>
+      <c r="R15" s="6">
+        <v>12839.659</v>
+      </c>
+      <c r="S15" s="6">
+        <v>12390.276</v>
+      </c>
+      <c r="T15" s="6">
+        <v>14171.629000000001</v>
+      </c>
+      <c r="U15" s="6">
+        <v>12537.880999999999</v>
+      </c>
+      <c r="V15" s="6">
+        <v>11954.804</v>
+      </c>
+      <c r="W15" s="6">
+        <v>12931.674999999999</v>
+      </c>
+      <c r="X15" s="6">
+        <v>12128.757</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>13331.499</v>
+      </c>
+      <c r="Z15" s="2">
         <v>14254</v>
       </c>
-      <c r="C15" s="2">
+      <c r="AA15" s="2">
         <v>14996</v>
       </c>
-      <c r="D15" s="2">
+      <c r="AB15" s="2">
         <v>15479</v>
       </c>
-      <c r="E15" s="2">
+      <c r="AC15" s="2">
         <v>15215</v>
       </c>
-      <c r="F15" s="2">
+      <c r="AD15" s="2">
         <v>15508</v>
       </c>
-      <c r="G15" s="2">
+      <c r="AE15" s="2">
         <v>12665</v>
       </c>
-      <c r="H15" s="2">
+      <c r="AF15" s="2">
         <v>13443</v>
       </c>
-      <c r="I15" s="2">
+      <c r="AG15" s="2">
         <v>14346</v>
       </c>
-      <c r="J15" s="2">
+      <c r="AH15" s="2">
         <v>14468</v>
       </c>
-      <c r="K15" s="2">
+      <c r="AI15" s="2">
         <v>15235</v>
       </c>
-      <c r="L15" s="2">
+      <c r="AJ15" s="2">
         <v>13617</v>
       </c>
-      <c r="M15" s="2">
+      <c r="AK15" s="2">
         <v>16401</v>
       </c>
-      <c r="N15" s="2">
+      <c r="AL15" s="2">
         <v>15233</v>
       </c>
-      <c r="O15" s="2">
+      <c r="AM15" s="2">
         <v>15399</v>
       </c>
-      <c r="P15" s="2">
+      <c r="AN15" s="2">
         <v>15238</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="AO15" s="2">
         <v>15648</v>
       </c>
-      <c r="R15" s="2">
+      <c r="AP15" s="2">
         <v>15145</v>
       </c>
-      <c r="S15" s="2">
+      <c r="AQ15" s="2">
         <v>14183</v>
       </c>
-      <c r="T15" s="2">
+      <c r="AR15" s="2">
         <v>16286</v>
       </c>
-      <c r="U15" s="2">
+      <c r="AS15" s="2">
         <v>14200</v>
       </c>
-      <c r="V15" s="2">
+      <c r="AT15" s="2">
         <v>15490</v>
       </c>
-      <c r="W15" s="2">
+      <c r="AU15" s="2">
         <v>16336</v>
       </c>
-      <c r="X15" s="2">
+      <c r="AV15" s="2">
         <v>13667</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="AW15" s="2">
         <v>17914</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="AX15" s="2">
         <v>16472</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="6">
+        <v>25716.662</v>
+      </c>
+      <c r="C16" s="6">
+        <v>24342.93</v>
+      </c>
+      <c r="D16" s="6">
+        <v>26286.773000000001</v>
+      </c>
+      <c r="E16" s="6">
+        <v>23159.55</v>
+      </c>
+      <c r="F16" s="6">
+        <v>22054.542000000001</v>
+      </c>
+      <c r="G16" s="6">
+        <v>24939.761999999999</v>
+      </c>
+      <c r="H16" s="6">
+        <v>24785.087</v>
+      </c>
+      <c r="I16" s="6">
+        <v>24836.853999999999</v>
+      </c>
+      <c r="J16" s="6">
+        <v>24104.618999999999</v>
+      </c>
+      <c r="K16" s="6">
+        <v>25322.374</v>
+      </c>
+      <c r="L16" s="6">
+        <v>21506.743999999999</v>
+      </c>
+      <c r="M16" s="6">
+        <v>25839.032999999999</v>
+      </c>
+      <c r="N16" s="6">
+        <v>24190.822</v>
+      </c>
+      <c r="O16" s="6">
+        <v>23325.146000000001</v>
+      </c>
+      <c r="P16" s="6">
+        <v>23561.782999999999</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>21979.598000000002</v>
+      </c>
+      <c r="R16" s="6">
+        <v>22358.021000000001</v>
+      </c>
+      <c r="S16" s="6">
+        <v>22598.87</v>
+      </c>
+      <c r="T16" s="6">
+        <v>23753.319</v>
+      </c>
+      <c r="U16" s="6">
+        <v>23407.526000000002</v>
+      </c>
+      <c r="V16" s="6">
+        <v>23717.917000000001</v>
+      </c>
+      <c r="W16" s="6">
+        <v>23800.42</v>
+      </c>
+      <c r="X16" s="6">
+        <v>22615.955000000002</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>25500.045999999998</v>
+      </c>
+      <c r="Z16" s="2">
         <v>25398</v>
       </c>
-      <c r="C16" s="2">
+      <c r="AA16" s="2">
         <v>24543</v>
       </c>
-      <c r="D16" s="2">
+      <c r="AB16" s="2">
         <v>22828</v>
       </c>
-      <c r="E16" s="2">
+      <c r="AC16" s="2">
         <v>26377</v>
       </c>
-      <c r="F16" s="2">
+      <c r="AD16" s="2">
         <v>24669</v>
       </c>
-      <c r="G16" s="2">
+      <c r="AE16" s="2">
         <v>23515</v>
       </c>
-      <c r="H16" s="2">
+      <c r="AF16" s="2">
         <v>27261</v>
       </c>
-      <c r="I16" s="2">
+      <c r="AG16" s="2">
         <v>26721</v>
       </c>
-      <c r="J16" s="2">
+      <c r="AH16" s="2">
         <v>23861</v>
       </c>
-      <c r="K16" s="2">
+      <c r="AI16" s="2">
         <v>21602</v>
       </c>
-      <c r="L16" s="2">
+      <c r="AJ16" s="2">
         <v>20974</v>
       </c>
-      <c r="M16" s="2">
+      <c r="AK16" s="2">
         <v>24310</v>
       </c>
-      <c r="N16" s="2">
+      <c r="AL16" s="2">
         <v>26109</v>
       </c>
-      <c r="O16" s="2">
+      <c r="AM16" s="2">
         <v>24631</v>
       </c>
-      <c r="P16" s="2">
+      <c r="AN16" s="2">
         <v>25959</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="AO16" s="2">
         <v>25910</v>
       </c>
-      <c r="R16" s="2">
+      <c r="AP16" s="2">
         <v>22212</v>
       </c>
-      <c r="S16" s="2">
+      <c r="AQ16" s="2">
         <v>23995</v>
       </c>
-      <c r="T16" s="2">
+      <c r="AR16" s="2">
         <v>27794</v>
       </c>
-      <c r="U16" s="2">
+      <c r="AS16" s="2">
         <v>25224</v>
       </c>
-      <c r="V16" s="2">
+      <c r="AT16" s="2">
         <v>26420</v>
       </c>
-      <c r="W16" s="2">
+      <c r="AU16" s="2">
         <v>26862</v>
       </c>
-      <c r="X16" s="2">
+      <c r="AV16" s="2">
         <v>24526</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="AW16" s="2">
         <v>28192</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="AX16" s="2">
         <v>26709</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="6">
+        <v>2130.893</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2658.9369999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3168.1190000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2668.6010000000001</v>
+      </c>
+      <c r="F17" s="6">
+        <v>2540.7910000000002</v>
+      </c>
+      <c r="G17" s="6">
+        <v>2832.81</v>
+      </c>
+      <c r="H17" s="6">
+        <v>2565.2289999999998</v>
+      </c>
+      <c r="I17" s="6">
+        <v>3075.585</v>
+      </c>
+      <c r="J17" s="6">
+        <v>3511.973</v>
+      </c>
+      <c r="K17" s="6">
+        <v>2871.2930000000001</v>
+      </c>
+      <c r="L17" s="6">
+        <v>2789.2330000000002</v>
+      </c>
+      <c r="M17" s="6">
+        <v>3453.3719999999998</v>
+      </c>
+      <c r="N17" s="6">
+        <v>2534.7130000000002</v>
+      </c>
+      <c r="O17" s="6">
+        <v>2970.66</v>
+      </c>
+      <c r="P17" s="6">
+        <v>3046.8040000000001</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>2913.9290000000001</v>
+      </c>
+      <c r="R17" s="6">
+        <v>2409.3389999999999</v>
+      </c>
+      <c r="S17" s="6">
+        <v>2840.7820000000002</v>
+      </c>
+      <c r="T17" s="6">
+        <v>2504.971</v>
+      </c>
+      <c r="U17" s="6">
+        <v>2562.6149999999998</v>
+      </c>
+      <c r="V17" s="6">
+        <v>2952.57</v>
+      </c>
+      <c r="W17" s="6">
+        <v>2520.9059999999999</v>
+      </c>
+      <c r="X17" s="6">
+        <v>2361.2310000000002</v>
+      </c>
+      <c r="Y17" s="6">
+        <v>2693.6959999999999</v>
+      </c>
+      <c r="Z17" s="2">
         <v>2728</v>
       </c>
-      <c r="C17" s="2">
+      <c r="AA17" s="2">
         <v>2570</v>
       </c>
-      <c r="D17" s="2">
+      <c r="AB17" s="2">
         <v>2823</v>
       </c>
-      <c r="E17" s="2">
+      <c r="AC17" s="2">
         <v>2939</v>
       </c>
-      <c r="F17" s="2">
+      <c r="AD17" s="2">
         <v>2345</v>
       </c>
-      <c r="G17" s="2">
+      <c r="AE17" s="2">
         <v>2653</v>
       </c>
-      <c r="H17" s="2">
+      <c r="AF17" s="2">
         <v>2994</v>
       </c>
-      <c r="I17" s="2">
+      <c r="AG17" s="2">
         <v>2544</v>
       </c>
-      <c r="J17" s="2">
+      <c r="AH17" s="2">
         <v>2430</v>
       </c>
-      <c r="K17" s="2">
+      <c r="AI17" s="2">
         <v>3113</v>
       </c>
-      <c r="L17" s="2">
+      <c r="AJ17" s="2">
         <v>2395</v>
       </c>
-      <c r="M17" s="2">
+      <c r="AK17" s="2">
         <v>2517</v>
       </c>
-      <c r="N17" s="2">
+      <c r="AL17" s="2">
         <v>3236</v>
       </c>
-      <c r="O17" s="2">
+      <c r="AM17" s="2">
         <v>2792</v>
       </c>
-      <c r="P17" s="2">
+      <c r="AN17" s="2">
         <v>3034</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="AO17" s="2">
         <v>3049</v>
       </c>
-      <c r="R17" s="2">
+      <c r="AP17" s="2">
         <v>2542</v>
       </c>
-      <c r="S17" s="2">
+      <c r="AQ17" s="2">
         <v>2946</v>
       </c>
-      <c r="T17" s="2">
+      <c r="AR17" s="2">
         <v>2827</v>
       </c>
-      <c r="U17" s="2">
+      <c r="AS17" s="2">
         <v>2691</v>
       </c>
-      <c r="V17" s="2">
+      <c r="AT17" s="2">
         <v>2832</v>
       </c>
-      <c r="W17" s="2">
+      <c r="AU17" s="2">
         <v>3129</v>
       </c>
-      <c r="X17" s="2">
+      <c r="AV17" s="2">
         <v>2642</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="AW17" s="2">
         <v>3373</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="AX17" s="2">
         <v>3057</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="6">
+        <v>21501.763999999999</v>
+      </c>
+      <c r="C18" s="6">
+        <v>20179.547999999999</v>
+      </c>
+      <c r="D18" s="6">
+        <v>20988.736000000001</v>
+      </c>
+      <c r="E18" s="6">
+        <v>20285.114000000001</v>
+      </c>
+      <c r="F18" s="6">
+        <v>23233.31</v>
+      </c>
+      <c r="G18" s="6">
+        <v>22159.113000000001</v>
+      </c>
+      <c r="H18" s="6">
+        <v>21038.580999999998</v>
+      </c>
+      <c r="I18" s="6">
+        <v>24588.754000000001</v>
+      </c>
+      <c r="J18" s="6">
+        <v>23381.674999999999</v>
+      </c>
+      <c r="K18" s="6">
+        <v>21898.959999999999</v>
+      </c>
+      <c r="L18" s="6">
+        <v>23312.322</v>
+      </c>
+      <c r="M18" s="6">
+        <v>24569.758999999998</v>
+      </c>
+      <c r="N18" s="6">
+        <v>21841.755000000001</v>
+      </c>
+      <c r="O18" s="6">
+        <v>20763.225999999999</v>
+      </c>
+      <c r="P18" s="6">
+        <v>21679.493999999999</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>21420.593000000001</v>
+      </c>
+      <c r="R18" s="6">
+        <v>22357.954000000002</v>
+      </c>
+      <c r="S18" s="6">
+        <v>22393.126</v>
+      </c>
+      <c r="T18" s="6">
+        <v>25674.419000000002</v>
+      </c>
+      <c r="U18" s="6">
+        <v>26102.280999999999</v>
+      </c>
+      <c r="V18" s="6">
+        <v>28696.364000000001</v>
+      </c>
+      <c r="W18" s="6">
+        <v>22466.607</v>
+      </c>
+      <c r="X18" s="6">
+        <v>23591.982</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>26313.574000000001</v>
+      </c>
+      <c r="Z18" s="2">
         <v>26163</v>
       </c>
-      <c r="C18" s="2">
+      <c r="AA18" s="2">
         <v>26117</v>
       </c>
-      <c r="D18" s="2">
+      <c r="AB18" s="2">
         <v>27735</v>
       </c>
-      <c r="E18" s="2">
+      <c r="AC18" s="2">
         <v>29142</v>
       </c>
-      <c r="F18" s="2">
+      <c r="AD18" s="2">
         <v>33262</v>
       </c>
-      <c r="G18" s="2">
+      <c r="AE18" s="2">
         <v>28368</v>
       </c>
-      <c r="H18" s="2">
+      <c r="AF18" s="2">
         <v>29196</v>
       </c>
-      <c r="I18" s="2">
+      <c r="AG18" s="2">
         <v>27791</v>
       </c>
-      <c r="J18" s="2">
+      <c r="AH18" s="2">
         <v>30270</v>
       </c>
-      <c r="K18" s="2">
+      <c r="AI18" s="2">
         <v>27303</v>
       </c>
-      <c r="L18" s="2">
+      <c r="AJ18" s="2">
         <v>24395</v>
       </c>
-      <c r="M18" s="2">
+      <c r="AK18" s="2">
         <v>31594</v>
       </c>
-      <c r="N18" s="2">
+      <c r="AL18" s="2">
         <v>27353</v>
       </c>
-      <c r="O18" s="2">
+      <c r="AM18" s="2">
         <v>27274</v>
       </c>
-      <c r="P18" s="2">
+      <c r="AN18" s="2">
         <v>28279</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="AO18" s="2">
         <v>26255</v>
       </c>
-      <c r="R18" s="2">
+      <c r="AP18" s="2">
         <v>25047</v>
       </c>
-      <c r="S18" s="2">
+      <c r="AQ18" s="2">
         <v>27227</v>
       </c>
-      <c r="T18" s="2">
+      <c r="AR18" s="2">
         <v>29333</v>
       </c>
-      <c r="U18" s="2">
+      <c r="AS18" s="2">
         <v>23771</v>
       </c>
-      <c r="V18" s="2">
+      <c r="AT18" s="2">
         <v>27497</v>
       </c>
-      <c r="W18" s="2">
+      <c r="AU18" s="2">
         <v>25640</v>
       </c>
-      <c r="X18" s="2">
+      <c r="AV18" s="2">
         <v>23782</v>
       </c>
-      <c r="Y18" s="2">
+      <c r="AW18" s="2">
         <v>29075</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="AX18" s="2">
         <v>25784</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="6">
+        <v>28108.206999999999</v>
+      </c>
+      <c r="C19" s="6">
+        <v>25353.019</v>
+      </c>
+      <c r="D19" s="6">
+        <v>27654.986000000001</v>
+      </c>
+      <c r="E19" s="6">
+        <v>26873.069</v>
+      </c>
+      <c r="F19" s="6">
+        <v>25369.323</v>
+      </c>
+      <c r="G19" s="6">
+        <v>25035.692999999999</v>
+      </c>
+      <c r="H19" s="6">
+        <v>25659.973999999998</v>
+      </c>
+      <c r="I19" s="6">
+        <v>25342.987000000001</v>
+      </c>
+      <c r="J19" s="6">
+        <v>27287.253000000001</v>
+      </c>
+      <c r="K19" s="6">
+        <v>25493.45</v>
+      </c>
+      <c r="L19" s="6">
+        <v>25503.917000000001</v>
+      </c>
+      <c r="M19" s="6">
+        <v>28429.967000000001</v>
+      </c>
+      <c r="N19" s="6">
+        <v>24261.291000000001</v>
+      </c>
+      <c r="O19" s="6">
+        <v>25523.591</v>
+      </c>
+      <c r="P19" s="6">
+        <v>26674.472000000002</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>26144.791000000001</v>
+      </c>
+      <c r="R19" s="6">
+        <v>23230.2</v>
+      </c>
+      <c r="S19" s="6">
+        <v>23967.535</v>
+      </c>
+      <c r="T19" s="6">
+        <v>25006.517</v>
+      </c>
+      <c r="U19" s="6">
+        <v>24354.903999999999</v>
+      </c>
+      <c r="V19" s="6">
+        <v>25618.412</v>
+      </c>
+      <c r="W19" s="6">
+        <v>24277.03</v>
+      </c>
+      <c r="X19" s="6">
+        <v>22724.394</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>26411.941999999999</v>
+      </c>
+      <c r="Z19" s="2">
         <v>25640</v>
       </c>
-      <c r="C19" s="2">
+      <c r="AA19" s="2">
         <v>26134</v>
       </c>
-      <c r="D19" s="2">
+      <c r="AB19" s="2">
         <v>25407</v>
       </c>
-      <c r="E19" s="2">
+      <c r="AC19" s="2">
         <v>27045</v>
       </c>
-      <c r="F19" s="2">
+      <c r="AD19" s="2">
         <v>23720</v>
       </c>
-      <c r="G19" s="2">
+      <c r="AE19" s="2">
         <v>25180</v>
       </c>
-      <c r="H19" s="2">
+      <c r="AF19" s="2">
         <v>28026</v>
       </c>
-      <c r="I19" s="2">
+      <c r="AG19" s="2">
         <v>25863</v>
       </c>
-      <c r="J19" s="2">
+      <c r="AH19" s="2">
         <v>25985</v>
       </c>
-      <c r="K19" s="2">
+      <c r="AI19" s="2">
         <v>24730</v>
       </c>
-      <c r="L19" s="2">
+      <c r="AJ19" s="2">
         <v>24335</v>
       </c>
-      <c r="M19" s="2">
+      <c r="AK19" s="2">
         <v>26654</v>
       </c>
-      <c r="N19" s="2">
+      <c r="AL19" s="2">
         <v>28692</v>
       </c>
-      <c r="O19" s="2">
+      <c r="AM19" s="2">
         <v>27244</v>
       </c>
-      <c r="P19" s="2">
+      <c r="AN19" s="2">
         <v>26239</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="AO19" s="2">
         <v>28887</v>
       </c>
-      <c r="R19" s="2">
+      <c r="AP19" s="2">
         <v>23894</v>
       </c>
-      <c r="S19" s="2">
+      <c r="AQ19" s="2">
         <v>27489</v>
       </c>
-      <c r="T19" s="2">
+      <c r="AR19" s="2">
         <v>28531</v>
       </c>
-      <c r="U19" s="2">
+      <c r="AS19" s="2">
         <v>23884</v>
       </c>
-      <c r="V19" s="2">
+      <c r="AT19" s="2">
         <v>28130</v>
       </c>
-      <c r="W19" s="2">
+      <c r="AU19" s="2">
         <v>27693</v>
       </c>
-      <c r="X19" s="2">
+      <c r="AV19" s="2">
         <v>22269</v>
       </c>
-      <c r="Y19" s="2">
+      <c r="AW19" s="2">
         <v>28619</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="AX19" s="2">
         <v>26861</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>14154</v>
-      </c>
-      <c r="C20" s="2">
-        <v>12923</v>
-      </c>
-      <c r="D20" s="2">
-        <v>12038</v>
-      </c>
-      <c r="E20" s="2">
-        <v>14053</v>
-      </c>
-      <c r="F20" s="2">
-        <v>13455</v>
-      </c>
-      <c r="G20" s="2">
-        <v>12581</v>
-      </c>
-      <c r="H20" s="2">
-        <v>13201</v>
-      </c>
-      <c r="I20" s="2">
-        <v>10947</v>
-      </c>
-      <c r="J20" s="2">
-        <v>13685</v>
-      </c>
-      <c r="K20" s="2">
-        <v>12295</v>
-      </c>
-      <c r="L20" s="2">
-        <v>10636</v>
-      </c>
-      <c r="M20" s="2">
-        <v>15468</v>
-      </c>
-      <c r="N20" s="2">
-        <v>12738</v>
-      </c>
-      <c r="O20" s="2">
-        <v>15066</v>
-      </c>
-      <c r="P20" s="2">
-        <v>14531</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>14063</v>
-      </c>
-      <c r="R20" s="2">
-        <v>12504</v>
-      </c>
-      <c r="S20" s="2">
-        <v>14636</v>
-      </c>
-      <c r="T20" s="2">
-        <v>14316</v>
-      </c>
-      <c r="U20" s="2">
-        <v>13033</v>
-      </c>
-      <c r="V20" s="2">
-        <v>14757</v>
-      </c>
-      <c r="W20" s="2">
-        <v>14007</v>
-      </c>
-      <c r="X20" s="2">
-        <v>13022</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>14497</v>
+      <c r="B20" s="6">
+        <v>12173.362999999999</v>
+      </c>
+      <c r="C20" s="6">
+        <v>10238.848</v>
+      </c>
+      <c r="D20" s="6">
+        <v>13983.465</v>
+      </c>
+      <c r="E20" s="6">
+        <v>11225.797</v>
+      </c>
+      <c r="F20" s="6">
+        <v>11602.468000000001</v>
+      </c>
+      <c r="G20" s="6">
+        <v>12497.225</v>
+      </c>
+      <c r="H20" s="6">
+        <v>11548.823</v>
+      </c>
+      <c r="I20" s="6">
+        <v>10171.66</v>
+      </c>
+      <c r="J20" s="6">
+        <v>12795.374</v>
+      </c>
+      <c r="K20" s="6">
+        <v>11221.266</v>
+      </c>
+      <c r="L20" s="6">
+        <v>12612.566999999999</v>
+      </c>
+      <c r="M20" s="6">
+        <v>14356.812</v>
+      </c>
+      <c r="N20" s="6">
+        <v>11499.15</v>
+      </c>
+      <c r="O20" s="6">
+        <v>11980.558000000001</v>
+      </c>
+      <c r="P20" s="6">
+        <v>13891.121999999999</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>12061.21</v>
+      </c>
+      <c r="R20" s="6">
+        <v>11078.102000000001</v>
+      </c>
+      <c r="S20" s="6">
+        <v>11620.9</v>
+      </c>
+      <c r="T20" s="6">
+        <v>12049.892</v>
+      </c>
+      <c r="U20" s="6">
+        <v>11899.288</v>
+      </c>
+      <c r="V20" s="6">
+        <v>12061.013000000001</v>
+      </c>
+      <c r="W20" s="6">
+        <v>12717.772000000001</v>
+      </c>
+      <c r="X20" s="6">
+        <v>13238.39</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>13469.492</v>
       </c>
       <c r="Z20" s="2">
         <v>14154</v>
       </c>
+      <c r="AA20" s="2">
+        <v>12923</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>12038</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>14053</v>
+      </c>
+      <c r="AD20" s="2">
+        <v>13455</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>12581</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>13201</v>
+      </c>
+      <c r="AG20" s="2">
+        <v>10947</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>13685</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>12295</v>
+      </c>
+      <c r="AJ20" s="2">
+        <v>10636</v>
+      </c>
+      <c r="AK20" s="2">
+        <v>15468</v>
+      </c>
+      <c r="AL20" s="2">
+        <v>12738</v>
+      </c>
+      <c r="AM20" s="2">
+        <v>15066</v>
+      </c>
+      <c r="AN20" s="2">
+        <v>14531</v>
+      </c>
+      <c r="AO20" s="2">
+        <v>14063</v>
+      </c>
+      <c r="AP20" s="2">
+        <v>12504</v>
+      </c>
+      <c r="AQ20" s="2">
+        <v>14636</v>
+      </c>
+      <c r="AR20" s="2">
+        <v>14316</v>
+      </c>
+      <c r="AS20" s="2">
+        <v>13033</v>
+      </c>
+      <c r="AT20" s="2">
+        <v>14757</v>
+      </c>
+      <c r="AU20" s="2">
+        <v>14007</v>
+      </c>
+      <c r="AV20" s="2">
+        <v>13022</v>
+      </c>
+      <c r="AW20" s="2">
+        <v>14497</v>
+      </c>
+      <c r="AX20" s="2">
+        <v>14154</v>
+      </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="6">
+        <v>21823.758999999998</v>
+      </c>
+      <c r="C21" s="6">
+        <v>19101.313999999998</v>
+      </c>
+      <c r="D21" s="6">
+        <v>21470.436000000002</v>
+      </c>
+      <c r="E21" s="6">
+        <v>20055.364000000001</v>
+      </c>
+      <c r="F21" s="6">
+        <v>18533.214</v>
+      </c>
+      <c r="G21" s="6">
+        <v>20496.538</v>
+      </c>
+      <c r="H21" s="6">
+        <v>21168.685000000001</v>
+      </c>
+      <c r="I21" s="6">
+        <v>20824.29</v>
+      </c>
+      <c r="J21" s="6">
+        <v>18937.059000000001</v>
+      </c>
+      <c r="K21" s="6">
+        <v>19928.876</v>
+      </c>
+      <c r="L21" s="6">
+        <v>17801.223000000002</v>
+      </c>
+      <c r="M21" s="6">
+        <v>20351.696</v>
+      </c>
+      <c r="N21" s="6">
+        <v>18854.3</v>
+      </c>
+      <c r="O21" s="6">
+        <v>18299.114000000001</v>
+      </c>
+      <c r="P21" s="6">
+        <v>20655.305</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>17907.493999999999</v>
+      </c>
+      <c r="R21" s="6">
+        <v>17217.838</v>
+      </c>
+      <c r="S21" s="6">
+        <v>16893.313999999998</v>
+      </c>
+      <c r="T21" s="6">
+        <v>18830.490000000002</v>
+      </c>
+      <c r="U21" s="6">
+        <v>19660.468000000001</v>
+      </c>
+      <c r="V21" s="6">
+        <v>18093.576000000001</v>
+      </c>
+      <c r="W21" s="6">
+        <v>18372.668000000001</v>
+      </c>
+      <c r="X21" s="6">
+        <v>18414.111000000001</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>19206.472000000002</v>
+      </c>
+      <c r="Z21" s="2">
         <v>18216</v>
       </c>
-      <c r="C21" s="2">
+      <c r="AA21" s="2">
         <v>19631</v>
       </c>
-      <c r="D21" s="2">
+      <c r="AB21" s="2">
         <v>17941</v>
       </c>
-      <c r="E21" s="2">
+      <c r="AC21" s="2">
         <v>21404</v>
       </c>
-      <c r="F21" s="2">
+      <c r="AD21" s="2">
         <v>21378</v>
       </c>
-      <c r="G21" s="2">
+      <c r="AE21" s="2">
         <v>18767</v>
       </c>
-      <c r="H21" s="2">
+      <c r="AF21" s="2">
         <v>20901</v>
       </c>
-      <c r="I21" s="2">
+      <c r="AG21" s="2">
         <v>16377</v>
       </c>
-      <c r="J21" s="2">
+      <c r="AH21" s="2">
         <v>18686</v>
       </c>
-      <c r="K21" s="2">
+      <c r="AI21" s="2">
         <v>19105</v>
       </c>
-      <c r="L21" s="2">
+      <c r="AJ21" s="2">
         <v>16900</v>
       </c>
-      <c r="M21" s="2">
+      <c r="AK21" s="2">
         <v>19162</v>
       </c>
-      <c r="N21" s="2">
+      <c r="AL21" s="2">
         <v>18910</v>
       </c>
-      <c r="O21" s="2">
+      <c r="AM21" s="2">
         <v>19262</v>
       </c>
-      <c r="P21" s="2">
+      <c r="AN21" s="2">
         <v>17863</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="AO21" s="2">
         <v>20148</v>
       </c>
-      <c r="R21" s="2">
+      <c r="AP21" s="2">
         <v>18247</v>
       </c>
-      <c r="S21" s="2">
+      <c r="AQ21" s="2">
         <v>18042</v>
       </c>
-      <c r="T21" s="2">
+      <c r="AR21" s="2">
         <v>21432</v>
       </c>
-      <c r="U21" s="2">
+      <c r="AS21" s="2">
         <v>18499</v>
       </c>
-      <c r="V21" s="2">
+      <c r="AT21" s="2">
         <v>21043</v>
       </c>
-      <c r="W21" s="2">
+      <c r="AU21" s="2">
         <v>20851</v>
       </c>
-      <c r="X21" s="2">
+      <c r="AV21" s="2">
         <v>17693</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="AW21" s="2">
         <v>21332</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="AX21" s="2">
         <v>19928</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="6">
+        <v>3628.4</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4339.3140000000003</v>
+      </c>
+      <c r="D22" s="6">
+        <v>5176.0010000000002</v>
+      </c>
+      <c r="E22" s="6">
+        <v>5754.0680000000002</v>
+      </c>
+      <c r="F22" s="6">
+        <v>6055.2849999999999</v>
+      </c>
+      <c r="G22" s="6">
+        <v>4417.95</v>
+      </c>
+      <c r="H22" s="6">
+        <v>7804.2839999999997</v>
+      </c>
+      <c r="I22" s="6">
+        <v>4450.0820000000003</v>
+      </c>
+      <c r="J22" s="6">
+        <v>6334.567</v>
+      </c>
+      <c r="K22" s="6">
+        <v>5898.3980000000001</v>
+      </c>
+      <c r="L22" s="6">
+        <v>5639.5789999999997</v>
+      </c>
+      <c r="M22" s="6">
+        <v>6255.357</v>
+      </c>
+      <c r="N22" s="6">
+        <v>4212.0789999999997</v>
+      </c>
+      <c r="O22" s="6">
+        <v>6205.6109999999999</v>
+      </c>
+      <c r="P22" s="6">
+        <v>6192.5739999999996</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>7026.6459999999997</v>
+      </c>
+      <c r="R22" s="6">
+        <v>5943.7749999999996</v>
+      </c>
+      <c r="S22" s="6">
+        <v>5592.884</v>
+      </c>
+      <c r="T22" s="6">
+        <v>6000.3130000000001</v>
+      </c>
+      <c r="U22" s="6">
+        <v>4235.7629999999999</v>
+      </c>
+      <c r="V22" s="6">
+        <v>6266.6629999999996</v>
+      </c>
+      <c r="W22" s="6">
+        <v>5162.2969999999996</v>
+      </c>
+      <c r="X22" s="6">
+        <v>4721.95</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>5252.5379999999996</v>
+      </c>
+      <c r="Z22" s="2">
         <v>5268</v>
       </c>
-      <c r="C22" s="2">
+      <c r="AA22" s="2">
         <v>5254</v>
       </c>
-      <c r="D22" s="2">
+      <c r="AB22" s="2">
         <v>5400</v>
       </c>
-      <c r="E22" s="2">
+      <c r="AC22" s="2">
         <v>7130</v>
       </c>
-      <c r="F22" s="2">
+      <c r="AD22" s="2">
         <v>9434</v>
       </c>
-      <c r="G22" s="2">
+      <c r="AE22" s="2">
         <v>5028</v>
       </c>
-      <c r="H22" s="2">
+      <c r="AF22" s="2">
         <v>4955</v>
       </c>
-      <c r="I22" s="2">
+      <c r="AG22" s="2">
         <v>5113</v>
       </c>
-      <c r="J22" s="2">
+      <c r="AH22" s="2">
         <v>6886</v>
       </c>
-      <c r="K22" s="2">
+      <c r="AI22" s="2">
         <v>6391</v>
       </c>
-      <c r="L22" s="2">
+      <c r="AJ22" s="2">
         <v>4592</v>
       </c>
-      <c r="M22" s="2">
+      <c r="AK22" s="2">
         <v>6246</v>
       </c>
-      <c r="N22" s="2">
+      <c r="AL22" s="2">
         <v>4943</v>
       </c>
-      <c r="O22" s="2">
+      <c r="AM22" s="2">
         <v>4891</v>
       </c>
-      <c r="P22" s="2">
+      <c r="AN22" s="2">
         <v>5925</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="AO22" s="2">
         <v>5969</v>
       </c>
-      <c r="R22" s="2">
+      <c r="AP22" s="2">
         <v>5796</v>
       </c>
-      <c r="S22" s="2">
+      <c r="AQ22" s="2">
         <v>4851</v>
       </c>
-      <c r="T22" s="2">
+      <c r="AR22" s="2">
         <v>5872</v>
       </c>
-      <c r="U22" s="2">
+      <c r="AS22" s="2">
         <v>5205</v>
       </c>
-      <c r="V22" s="2">
+      <c r="AT22" s="2">
         <v>5381</v>
       </c>
-      <c r="W22" s="2">
+      <c r="AU22" s="2">
         <v>5160</v>
       </c>
-      <c r="X22" s="2">
+      <c r="AV22" s="2">
         <v>4146</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="AW22" s="2">
         <v>5398</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AX22" s="2">
         <v>4572</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="6">
+        <v>1182.2629999999999</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1613.9380000000001</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1158.886</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2668.991</v>
+      </c>
+      <c r="F23" s="6">
+        <v>3305.9479999999999</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1273.08</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1460.8510000000001</v>
+      </c>
+      <c r="I23" s="6">
+        <v>2264.1640000000002</v>
+      </c>
+      <c r="J23" s="6">
+        <v>2504.9839999999999</v>
+      </c>
+      <c r="K23" s="6">
+        <v>3525.9679999999998</v>
+      </c>
+      <c r="L23" s="6">
+        <v>3328.348</v>
+      </c>
+      <c r="M23" s="6">
+        <v>3029.2379999999998</v>
+      </c>
+      <c r="N23" s="6">
+        <v>3080.0239999999999</v>
+      </c>
+      <c r="O23" s="6">
+        <v>2993.5929999999998</v>
+      </c>
+      <c r="P23" s="6">
+        <v>3629.8150000000001</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>2775.817</v>
+      </c>
+      <c r="R23" s="6">
+        <v>3766.8670000000002</v>
+      </c>
+      <c r="S23" s="6">
+        <v>3745.2469999999998</v>
+      </c>
+      <c r="T23" s="6">
+        <v>3726.49</v>
+      </c>
+      <c r="U23" s="6">
+        <v>3025.6529999999998</v>
+      </c>
+      <c r="V23" s="6">
+        <v>3900.5520000000001</v>
+      </c>
+      <c r="W23" s="6">
+        <v>3244.0569999999998</v>
+      </c>
+      <c r="X23" s="6">
+        <v>3661.8209999999999</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>3607.7170000000001</v>
+      </c>
+      <c r="Z23" s="2">
         <v>3943</v>
       </c>
-      <c r="C23" s="2">
+      <c r="AA23" s="2">
         <v>5146</v>
       </c>
-      <c r="D23" s="2">
+      <c r="AB23" s="2">
         <v>5214</v>
       </c>
-      <c r="E23" s="2">
+      <c r="AC23" s="2">
         <v>5434</v>
       </c>
-      <c r="F23" s="2">
+      <c r="AD23" s="2">
         <v>7928</v>
       </c>
-      <c r="G23" s="2">
+      <c r="AE23" s="2">
         <v>4790</v>
       </c>
-      <c r="H23" s="2">
+      <c r="AF23" s="2">
         <v>5812</v>
       </c>
-      <c r="I23" s="2">
+      <c r="AG23" s="2">
         <v>4778</v>
       </c>
-      <c r="J23" s="2">
+      <c r="AH23" s="2">
         <v>5796</v>
       </c>
-      <c r="K23" s="2">
+      <c r="AI23" s="2">
         <v>5482</v>
       </c>
-      <c r="L23" s="2">
+      <c r="AJ23" s="2">
         <v>4507</v>
       </c>
-      <c r="M23" s="2">
+      <c r="AK23" s="2">
         <v>5310</v>
       </c>
-      <c r="N23" s="2">
+      <c r="AL23" s="2">
         <v>4221</v>
       </c>
-      <c r="O23" s="2">
+      <c r="AM23" s="2">
         <v>5650</v>
       </c>
-      <c r="P23" s="2">
+      <c r="AN23" s="2">
         <v>3601</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="AO23" s="2">
         <v>4630</v>
       </c>
-      <c r="R23" s="2">
+      <c r="AP23" s="2">
         <v>4260</v>
       </c>
-      <c r="S23" s="2">
+      <c r="AQ23" s="2">
         <v>4713</v>
       </c>
-      <c r="T23" s="2">
+      <c r="AR23" s="2">
         <v>4326</v>
       </c>
-      <c r="U23" s="2">
+      <c r="AS23" s="2">
         <v>4354</v>
       </c>
-      <c r="V23" s="2">
+      <c r="AT23" s="2">
         <v>4096</v>
       </c>
-      <c r="W23" s="2">
+      <c r="AU23" s="2">
         <v>5444</v>
       </c>
-      <c r="X23" s="2">
+      <c r="AV23" s="2">
         <v>4425</v>
       </c>
-      <c r="Y23" s="2">
+      <c r="AW23" s="2">
         <v>4047</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="AX23" s="2">
         <v>4855</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="6">
+        <v>3988.971</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3798.5079999999998</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3935.8470000000002</v>
+      </c>
+      <c r="E24" s="6">
+        <v>3479.6260000000002</v>
+      </c>
+      <c r="F24" s="6">
+        <v>3679.1759999999999</v>
+      </c>
+      <c r="G24" s="6">
+        <v>3315.8580000000002</v>
+      </c>
+      <c r="H24" s="6">
+        <v>3105.864</v>
+      </c>
+      <c r="I24" s="6">
+        <v>3613.355</v>
+      </c>
+      <c r="J24" s="6">
+        <v>3092.7420000000002</v>
+      </c>
+      <c r="K24" s="6">
+        <v>3305.855</v>
+      </c>
+      <c r="L24" s="6">
+        <v>2708.7060000000001</v>
+      </c>
+      <c r="M24" s="6">
+        <v>3146.1570000000002</v>
+      </c>
+      <c r="N24" s="6">
+        <v>2266.7890000000002</v>
+      </c>
+      <c r="O24" s="6">
+        <v>2042.7260000000001</v>
+      </c>
+      <c r="P24" s="6">
+        <v>1960.3620000000001</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>1693.221</v>
+      </c>
+      <c r="R24" s="6">
+        <v>1982.1379999999999</v>
+      </c>
+      <c r="S24" s="6">
+        <v>1728.7049999999999</v>
+      </c>
+      <c r="T24" s="6">
+        <v>1889.1469999999999</v>
+      </c>
+      <c r="U24" s="6">
+        <v>1694.963</v>
+      </c>
+      <c r="V24" s="6">
+        <v>1833.3320000000001</v>
+      </c>
+      <c r="W24" s="6">
+        <v>1703.7650000000001</v>
+      </c>
+      <c r="X24" s="6">
+        <v>1543.2940000000001</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>1655.0250000000001</v>
+      </c>
+      <c r="Z24" s="2">
         <v>1484</v>
       </c>
-      <c r="C24" s="2">
+      <c r="AA24" s="2">
         <v>1567</v>
       </c>
-      <c r="D24" s="2">
+      <c r="AB24" s="2">
         <v>1361</v>
       </c>
-      <c r="E24" s="2">
+      <c r="AC24" s="2">
         <v>1458</v>
       </c>
-      <c r="F24" s="2">
+      <c r="AD24" s="2">
         <v>1576</v>
       </c>
-      <c r="G24" s="2">
+      <c r="AE24" s="2">
         <v>1454</v>
       </c>
-      <c r="H24" s="2">
+      <c r="AF24" s="2">
         <v>1482</v>
       </c>
-      <c r="I24" s="2">
+      <c r="AG24" s="2">
         <v>1269</v>
       </c>
-      <c r="J24" s="2">
+      <c r="AH24" s="2">
         <v>1341</v>
       </c>
-      <c r="K24" s="2">
+      <c r="AI24" s="2">
         <v>1385</v>
       </c>
-      <c r="L24" s="2">
+      <c r="AJ24" s="2">
         <v>1175</v>
       </c>
-      <c r="M24" s="2">
+      <c r="AK24" s="2">
         <v>1133</v>
       </c>
-      <c r="N24" s="2">
+      <c r="AL24" s="2">
         <v>1290</v>
       </c>
-      <c r="O24" s="2">
+      <c r="AM24" s="2">
         <v>1218</v>
       </c>
-      <c r="P24" s="2">
+      <c r="AN24" s="2">
         <v>1332</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="AO24" s="2">
         <v>1277</v>
       </c>
-      <c r="R24" s="2">
+      <c r="AP24" s="2">
         <v>1262</v>
       </c>
-      <c r="S24" s="2">
+      <c r="AQ24" s="2">
         <v>1169</v>
       </c>
-      <c r="T24" s="2">
+      <c r="AR24" s="2">
         <v>1346</v>
       </c>
-      <c r="U24" s="2">
+      <c r="AS24" s="2">
         <v>1132</v>
       </c>
-      <c r="V24" s="2">
+      <c r="AT24" s="2">
         <v>1263</v>
       </c>
-      <c r="W24" s="2">
+      <c r="AU24" s="2">
         <v>1234</v>
       </c>
-      <c r="X24" s="2">
+      <c r="AV24" s="2">
         <v>1236</v>
       </c>
-      <c r="Y24" s="2">
+      <c r="AW24" s="2">
         <v>1293</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="AX24" s="2">
         <v>1296</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="6">
+        <v>16166.221</v>
+      </c>
+      <c r="C25" s="6">
+        <v>14132.901</v>
+      </c>
+      <c r="D25" s="6">
+        <v>19791.800999999999</v>
+      </c>
+      <c r="E25" s="6">
+        <v>17481.023000000001</v>
+      </c>
+      <c r="F25" s="6">
+        <v>16560.969000000001</v>
+      </c>
+      <c r="G25" s="6">
+        <v>17854.990000000002</v>
+      </c>
+      <c r="H25" s="6">
+        <v>17938.733</v>
+      </c>
+      <c r="I25" s="6">
+        <v>16617.055</v>
+      </c>
+      <c r="J25" s="6">
+        <v>17189.605</v>
+      </c>
+      <c r="K25" s="6">
+        <v>15231.262000000001</v>
+      </c>
+      <c r="L25" s="6">
+        <v>14905.201999999999</v>
+      </c>
+      <c r="M25" s="6">
+        <v>17755.902999999998</v>
+      </c>
+      <c r="N25" s="6">
+        <v>16842.234</v>
+      </c>
+      <c r="O25" s="6">
+        <v>16160.905000000001</v>
+      </c>
+      <c r="P25" s="6">
+        <v>17357.171999999999</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>16018.364</v>
+      </c>
+      <c r="R25" s="6">
+        <v>18311.565999999999</v>
+      </c>
+      <c r="S25" s="6">
+        <v>14857.662</v>
+      </c>
+      <c r="T25" s="6">
+        <v>15794.55</v>
+      </c>
+      <c r="U25" s="6">
+        <v>17627.275000000001</v>
+      </c>
+      <c r="V25" s="6">
+        <v>18205.517</v>
+      </c>
+      <c r="W25" s="6">
+        <v>17837.475999999999</v>
+      </c>
+      <c r="X25" s="6">
+        <v>17037.607</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>17698.171999999999</v>
+      </c>
+      <c r="Z25" s="2">
         <v>16723</v>
       </c>
-      <c r="C25" s="2">
+      <c r="AA25" s="2">
         <v>16273</v>
       </c>
-      <c r="D25" s="2">
+      <c r="AB25" s="2">
         <v>16740</v>
       </c>
-      <c r="E25" s="2">
+      <c r="AC25" s="2">
         <v>22117</v>
       </c>
-      <c r="F25" s="2">
+      <c r="AD25" s="2">
         <v>20093</v>
       </c>
-      <c r="G25" s="2">
+      <c r="AE25" s="2">
         <v>16081</v>
       </c>
-      <c r="H25" s="2">
+      <c r="AF25" s="2">
         <v>18510</v>
       </c>
-      <c r="I25" s="2">
+      <c r="AG25" s="2">
         <v>16034</v>
       </c>
-      <c r="J25" s="2">
+      <c r="AH25" s="2">
         <v>18212</v>
       </c>
-      <c r="K25" s="2">
+      <c r="AI25" s="2">
         <v>15118</v>
       </c>
-      <c r="L25" s="2">
+      <c r="AJ25" s="2">
         <v>14091</v>
       </c>
-      <c r="M25" s="2">
+      <c r="AK25" s="2">
         <v>16988</v>
       </c>
-      <c r="N25" s="2">
+      <c r="AL25" s="2">
         <v>17103</v>
       </c>
-      <c r="O25" s="2">
+      <c r="AM25" s="2">
         <v>15925</v>
       </c>
-      <c r="P25" s="2">
+      <c r="AN25" s="2">
         <v>17368</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="AO25" s="2">
         <v>19444</v>
       </c>
-      <c r="R25" s="2">
+      <c r="AP25" s="2">
         <v>15914</v>
       </c>
-      <c r="S25" s="2">
+      <c r="AQ25" s="2">
         <v>17720</v>
       </c>
-      <c r="T25" s="2">
+      <c r="AR25" s="2">
         <v>17424</v>
       </c>
-      <c r="U25" s="2">
+      <c r="AS25" s="2">
         <v>13841</v>
       </c>
-      <c r="V25" s="2">
+      <c r="AT25" s="2">
         <v>17571</v>
       </c>
-      <c r="W25" s="2">
+      <c r="AU25" s="2">
         <v>16049</v>
       </c>
-      <c r="X25" s="2">
+      <c r="AV25" s="2">
         <v>14401</v>
       </c>
-      <c r="Y25" s="2">
+      <c r="AW25" s="2">
         <v>17556</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="AX25" s="2">
         <v>16746</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="6">
+        <v>4740.8630000000003</v>
+      </c>
+      <c r="C26" s="6">
+        <v>4624.0659999999998</v>
+      </c>
+      <c r="D26" s="6">
+        <v>4634.9399999999996</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4975.9369999999999</v>
+      </c>
+      <c r="F26" s="6">
+        <v>4523.57</v>
+      </c>
+      <c r="G26" s="6">
+        <v>4558.7039999999997</v>
+      </c>
+      <c r="H26" s="6">
+        <v>5487.8819999999996</v>
+      </c>
+      <c r="I26" s="6">
+        <v>4868.1629999999996</v>
+      </c>
+      <c r="J26" s="6">
+        <v>5191.3209999999999</v>
+      </c>
+      <c r="K26" s="6">
+        <v>4134.3919999999998</v>
+      </c>
+      <c r="L26" s="6">
+        <v>4120.3159999999998</v>
+      </c>
+      <c r="M26" s="6">
+        <v>5107.4129999999996</v>
+      </c>
+      <c r="N26" s="6">
+        <v>5564.7939999999999</v>
+      </c>
+      <c r="O26" s="6">
+        <v>3868.5419999999999</v>
+      </c>
+      <c r="P26" s="6">
+        <v>4935.1390000000001</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>5620.8540000000003</v>
+      </c>
+      <c r="R26" s="6">
+        <v>4239.4110000000001</v>
+      </c>
+      <c r="S26" s="6">
+        <v>4562.1260000000002</v>
+      </c>
+      <c r="T26" s="6">
+        <v>5216.0789999999997</v>
+      </c>
+      <c r="U26" s="6">
+        <v>4218.6620000000003</v>
+      </c>
+      <c r="V26" s="6">
+        <v>5092.79</v>
+      </c>
+      <c r="W26" s="6">
+        <v>4272.0420000000004</v>
+      </c>
+      <c r="X26" s="6">
+        <v>4578.9120000000003</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>5098.13</v>
+      </c>
+      <c r="Z26" s="2">
         <v>4681</v>
       </c>
-      <c r="C26" s="2">
+      <c r="AA26" s="2">
         <v>4314</v>
       </c>
-      <c r="D26" s="2">
+      <c r="AB26" s="2">
         <v>4883</v>
       </c>
-      <c r="E26" s="2">
+      <c r="AC26" s="2">
         <v>5418</v>
       </c>
-      <c r="F26" s="2">
+      <c r="AD26" s="2">
         <v>6045</v>
       </c>
-      <c r="G26" s="2">
+      <c r="AE26" s="2">
         <v>5510</v>
       </c>
-      <c r="H26" s="2">
+      <c r="AF26" s="2">
         <v>6799</v>
       </c>
-      <c r="I26" s="2">
+      <c r="AG26" s="2">
         <v>6328</v>
       </c>
-      <c r="J26" s="2">
+      <c r="AH26" s="2">
         <v>8453</v>
       </c>
-      <c r="K26" s="2">
+      <c r="AI26" s="2">
         <v>8521</v>
       </c>
-      <c r="L26" s="2">
+      <c r="AJ26" s="2">
         <v>5712</v>
       </c>
-      <c r="M26" s="2">
+      <c r="AK26" s="2">
         <v>5398</v>
       </c>
-      <c r="N26" s="2">
+      <c r="AL26" s="2">
         <v>4945</v>
       </c>
-      <c r="O26" s="2">
+      <c r="AM26" s="2">
         <v>5114</v>
       </c>
-      <c r="P26" s="2">
+      <c r="AN26" s="2">
         <v>4242</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="AO26" s="2">
         <v>5420</v>
       </c>
-      <c r="R26" s="2">
+      <c r="AP26" s="2">
         <v>3677</v>
       </c>
-      <c r="S26" s="2">
+      <c r="AQ26" s="2">
         <v>4960</v>
       </c>
-      <c r="T26" s="2">
+      <c r="AR26" s="2">
         <v>5129</v>
       </c>
-      <c r="U26" s="2">
+      <c r="AS26" s="2">
         <v>5902</v>
       </c>
-      <c r="V26" s="2">
+      <c r="AT26" s="2">
         <v>4398</v>
       </c>
-      <c r="W26" s="2">
+      <c r="AU26" s="2">
         <v>4460</v>
       </c>
-      <c r="X26" s="2">
+      <c r="AV26" s="2">
         <v>4177</v>
       </c>
-      <c r="Y26" s="2">
+      <c r="AW26" s="2">
         <v>5368</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="AX26" s="2">
         <v>4744</v>
       </c>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.5">
+      <c r="B28" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
